--- a/research/traditional_assets/database/data/hong_kong/hong_kong_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ47"/>
+  <dimension ref="A1:AQ48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04345</v>
+        <v>-0.08105000000000001</v>
       </c>
       <c r="E2">
-        <v>0.061</v>
+        <v>-0.234</v>
       </c>
       <c r="F2">
-        <v>2.214</v>
+        <v>1.09265</v>
       </c>
       <c r="G2">
-        <v>0.01849565726629036</v>
+        <v>0.04294082379021653</v>
       </c>
       <c r="H2">
-        <v>0.006565154517668353</v>
+        <v>0.0164090280778953</v>
       </c>
       <c r="I2">
-        <v>0.01487228324115037</v>
+        <v>0.003093664527632569</v>
       </c>
       <c r="J2">
-        <v>0.01321265852337919</v>
+        <v>0.002848913458053613</v>
       </c>
       <c r="K2">
-        <v>755.179</v>
+        <v>-844.64</v>
       </c>
       <c r="L2">
-        <v>0.115954506244551</v>
+        <v>-0.2515695546750674</v>
       </c>
       <c r="M2">
-        <v>811.9748</v>
+        <v>743.5690000000001</v>
       </c>
       <c r="N2">
-        <v>0.04429908703949615</v>
+        <v>0.05210554124469884</v>
       </c>
       <c r="O2">
-        <v>1.075208394301219</v>
+        <v>-0.8803383690092822</v>
       </c>
       <c r="P2">
-        <v>809.3027999999999</v>
+        <v>720.4920000000001</v>
       </c>
       <c r="Q2">
-        <v>0.04415331015015237</v>
+        <v>0.05048842222103875</v>
       </c>
       <c r="R2">
-        <v>1.071670160319606</v>
+        <v>-0.8530166698238304</v>
       </c>
       <c r="S2">
-        <v>2.672000000000001</v>
+        <v>23.07700000000001</v>
       </c>
       <c r="T2">
-        <v>0.003290742520580689</v>
+        <v>0.03103545198898825</v>
       </c>
       <c r="U2">
-        <v>8041.592</v>
+        <v>6217.263</v>
       </c>
       <c r="V2">
-        <v>0.4387268963816561</v>
+        <v>0.4356742328898058</v>
       </c>
       <c r="W2">
-        <v>0.02815533980582524</v>
+        <v>-0.05100424831548719</v>
       </c>
       <c r="X2">
-        <v>0.04772762955066239</v>
+        <v>0.08176606821095345</v>
       </c>
       <c r="Y2">
-        <v>-0.01957228974483715</v>
+        <v>-0.1327703165264406</v>
       </c>
       <c r="Z2">
-        <v>0.09654933899844698</v>
+        <v>0.05171635707578631</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03947545646851618</v>
+        <v>0.07261274276349294</v>
       </c>
       <c r="AC2">
-        <v>-0.03819128382595855</v>
+        <v>-0.07171333957764961</v>
       </c>
       <c r="AD2">
-        <v>48275.268</v>
+        <v>39434.269</v>
       </c>
       <c r="AE2">
-        <v>0.900066171308233</v>
+        <v>1.755400640498401</v>
       </c>
       <c r="AF2">
-        <v>48276.16806617131</v>
+        <v>39436.0244006405</v>
       </c>
       <c r="AG2">
-        <v>40234.57606617131</v>
+        <v>33218.7614006405</v>
       </c>
       <c r="AH2">
-        <v>0.7248070088427151</v>
+        <v>0.7342882247182554</v>
       </c>
       <c r="AI2">
-        <v>0.6372068760766622</v>
+        <v>0.6086778015017571</v>
       </c>
       <c r="AJ2">
-        <v>0.6870194359942202</v>
+        <v>0.6995013691721603</v>
       </c>
       <c r="AK2">
-        <v>0.5941263991629544</v>
+        <v>0.5671402619268375</v>
       </c>
       <c r="AL2">
-        <v>151.628</v>
+        <v>67.636</v>
       </c>
       <c r="AM2">
-        <v>135.724</v>
+        <v>50.212</v>
       </c>
       <c r="AN2">
-        <v>425.0705996301839</v>
+        <v>1723.977835096616</v>
       </c>
       <c r="AO2">
-        <v>0.6357401007729443</v>
+        <v>0.1436513099532794</v>
       </c>
       <c r="AP2">
-        <v>354.2711637419328</v>
+        <v>1452.249777067434</v>
       </c>
       <c r="AQ2">
-        <v>0.7102354778815831</v>
+        <v>0.1934995618577234</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zhongjin Technology Services Group Company Limited (SEHK:8295)</t>
+          <t>Da Yu Financial Holdings Limited (SEHK:1073)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,29 +724,23 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.204</v>
-      </c>
-      <c r="E3">
-        <v>-0.198</v>
-      </c>
       <c r="G3">
-        <v>0.0893719806763285</v>
+        <v>0.3314285714285714</v>
       </c>
       <c r="H3">
-        <v>0.05893719806763285</v>
+        <v>0.3314285714285714</v>
       </c>
       <c r="I3">
-        <v>0.1120772946859903</v>
+        <v>0.4342857142857143</v>
       </c>
       <c r="J3">
-        <v>0.08247739378174161</v>
+        <v>0.3443417366946779</v>
       </c>
       <c r="K3">
-        <v>8.99</v>
+        <v>3.24</v>
       </c>
       <c r="L3">
-        <v>0.08685990338164251</v>
+        <v>0.3085714285714286</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -770,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14.1</v>
+        <v>11</v>
       </c>
       <c r="V3">
-        <v>0.05251396648044693</v>
+        <v>0.4182509505703422</v>
       </c>
       <c r="W3">
-        <v>0.09988888888888889</v>
+        <v>0.05436241610738255</v>
       </c>
       <c r="X3">
-        <v>0.03720586868668319</v>
+        <v>0.07079090523976678</v>
       </c>
       <c r="Y3">
-        <v>0.0626830202022057</v>
+        <v>-0.01642848913238423</v>
       </c>
       <c r="Z3">
-        <v>27.65161635052101</v>
+        <v>1.552106430155211</v>
       </c>
       <c r="AA3">
-        <v>2.280633250443566</v>
+        <v>0.5344550236946219</v>
       </c>
       <c r="AB3">
-        <v>0.03657708080838685</v>
+        <v>0.07062921770085014</v>
       </c>
       <c r="AC3">
-        <v>2.244056169635179</v>
+        <v>0.4638258059937718</v>
       </c>
       <c r="AD3">
-        <v>18.9</v>
+        <v>0.276</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18.9</v>
+        <v>0.276</v>
       </c>
       <c r="AG3">
-        <v>4.799999999999999</v>
+        <v>-10.724</v>
       </c>
       <c r="AH3">
-        <v>0.06576200417536535</v>
+        <v>0.01038531005418423</v>
       </c>
       <c r="AI3">
-        <v>0.1062394603709949</v>
+        <v>0.004417696395415839</v>
       </c>
       <c r="AJ3">
-        <v>0.01756311745334796</v>
+        <v>-0.6884951206985105</v>
       </c>
       <c r="AK3">
-        <v>0.0293040293040293</v>
+        <v>-0.208330095578522</v>
       </c>
       <c r="AL3">
-        <v>2.15</v>
+        <v>0.017</v>
       </c>
       <c r="AM3">
-        <v>1</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="AN3">
-        <v>1.067796610169492</v>
+        <v>0.04775086505190312</v>
       </c>
       <c r="AO3">
-        <v>5.395348837209302</v>
+        <v>268.235294117647</v>
       </c>
       <c r="AP3">
-        <v>0.271186440677966</v>
+        <v>-1.855363321799308</v>
       </c>
       <c r="AQ3">
-        <v>11.6</v>
+        <v>-651.4285714285714</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Worldsec Limited (LSE:WSL)</t>
+          <t>eBullion, Inc. (OTCPK:EBML)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,9 +849,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.797</v>
-      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -865,16 +856,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.8333333333333333</v>
+        <v>0.3379273951899556</v>
       </c>
       <c r="J4">
-        <v>0.8333333333333333</v>
+        <v>0.3379273951899556</v>
       </c>
       <c r="K4">
-        <v>1.22</v>
+        <v>-0.665</v>
       </c>
       <c r="L4">
-        <v>0.6777777777777777</v>
+        <v>-0.6333333333333333</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,7 +874,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -892,73 +883,76 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="V4">
-        <v>0.3680555555555556</v>
+        <v>0.41015625</v>
       </c>
       <c r="W4">
-        <v>0.2747747747747747</v>
+        <v>-0.2782426778242678</v>
       </c>
       <c r="X4">
-        <v>0.03686853699930318</v>
+        <v>0.07802144944121166</v>
       </c>
       <c r="Y4">
-        <v>0.2379062377754716</v>
+        <v>-0.3562641272654794</v>
       </c>
       <c r="Z4">
-        <v>0.5714285714285715</v>
+        <v>0.4691938122592319</v>
       </c>
       <c r="AA4">
-        <v>0.4761904761904762</v>
+        <v>0.1585534428160073</v>
       </c>
       <c r="AB4">
-        <v>0.03654412575883995</v>
+        <v>0.07298485059073122</v>
       </c>
       <c r="AC4">
-        <v>0.4396463504316362</v>
+        <v>0.08556859222527609</v>
       </c>
       <c r="AD4">
-        <v>0.147</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.7258811752527329</v>
       </c>
       <c r="AF4">
-        <v>0.147</v>
+        <v>0.7258811752527329</v>
       </c>
       <c r="AG4">
-        <v>-0.913</v>
+        <v>-0.3241188247472672</v>
       </c>
       <c r="AH4">
-        <v>0.04856293359762141</v>
+        <v>0.2209091371652847</v>
       </c>
       <c r="AI4">
-        <v>0.02527075812274368</v>
+        <v>0.3081145105609421</v>
       </c>
       <c r="AJ4">
-        <v>-0.4641586171835282</v>
+        <v>-0.1449624552210966</v>
       </c>
       <c r="AK4">
-        <v>-0.1919276855160816</v>
+        <v>-0.2481993238661543</v>
       </c>
       <c r="AL4">
-        <v>0.007</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.007</v>
-      </c>
-      <c r="AO4">
-        <v>214.2857142857143</v>
+        <v>-0.048</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>-0.6482376494945343</v>
       </c>
       <c r="AQ4">
-        <v>214.2857142857143</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eBullion, Inc. (OTCPK:EBML)</t>
+          <t>Magic Empire Global Limited (NasdaqCM:MEGL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,16 +978,16 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.3324700252517279</v>
+        <v>0.05835074596364428</v>
       </c>
       <c r="J5">
-        <v>0.3324700252517279</v>
+        <v>0.05479277364878792</v>
       </c>
       <c r="K5">
-        <v>-0.665</v>
+        <v>0.384</v>
       </c>
       <c r="L5">
-        <v>-0.6333333333333333</v>
+        <v>0.1737556561085973</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1002,7 +996,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1011,76 +1005,73 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1.05</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="V5">
-        <v>0.1019417475728155</v>
+        <v>0.03147286821705426</v>
       </c>
       <c r="W5">
-        <v>-0.2782426778242678</v>
+        <v>0.7514677103718199</v>
       </c>
       <c r="X5">
-        <v>0.0372558076845465</v>
+        <v>0.07248900629893952</v>
       </c>
       <c r="Y5">
-        <v>-0.3154984855088143</v>
+        <v>0.6789787040728804</v>
       </c>
       <c r="Z5">
-        <v>0.4632627422794377</v>
+        <v>1.808178807742361</v>
       </c>
       <c r="AA5">
-        <v>0.1540209756238294</v>
+        <v>0.09907513212916239</v>
       </c>
       <c r="AB5">
-        <v>0.03677341251936825</v>
+        <v>0.07128999738837584</v>
       </c>
       <c r="AC5">
-        <v>0.1172475631044611</v>
+        <v>0.02778513474078655</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE5">
-        <v>0.7545323674284287</v>
+        <v>0.6652242571017307</v>
       </c>
       <c r="AF5">
-        <v>0.7545323674284287</v>
+        <v>1.925224257101731</v>
       </c>
       <c r="AG5">
-        <v>-0.2954676325715714</v>
+        <v>1.113224257101731</v>
       </c>
       <c r="AH5">
-        <v>0.0682554758853135</v>
+        <v>0.06943944760369576</v>
       </c>
       <c r="AI5">
-        <v>0.3164278152542527</v>
+        <v>0.8351570356639578</v>
       </c>
       <c r="AJ5">
-        <v>-0.02953337764526804</v>
+        <v>0.04136346676515276</v>
       </c>
       <c r="AK5">
-        <v>-0.2214016233573424</v>
+        <v>0.7455171263172753</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.048</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>4.809160305343512</v>
       </c>
       <c r="AP5">
-        <v>-0.5909352651431428</v>
-      </c>
-      <c r="AQ5">
-        <v>-0</v>
+        <v>4.248947546189811</v>
       </c>
     </row>
     <row r="6">
@@ -1091,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Planetree International Development Limited (SEHK:613)</t>
+          <t>Kingwisoft Technology Group Company Limited (SEHK:8295)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1099,23 +1090,26 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.903</v>
+      </c>
       <c r="G6">
-        <v>0.2762057877813505</v>
+        <v>0.1441358024691358</v>
       </c>
       <c r="H6">
-        <v>0.2762057877813505</v>
+        <v>0.1118827160493827</v>
       </c>
       <c r="I6">
-        <v>0.5401929260450161</v>
+        <v>0.04938271604938272</v>
       </c>
       <c r="J6">
-        <v>0.4797497175632224</v>
+        <v>0.04772625644016721</v>
       </c>
       <c r="K6">
-        <v>16.5</v>
+        <v>13.4</v>
       </c>
       <c r="L6">
-        <v>0.5305466237942122</v>
+        <v>0.1033950617283951</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1139,73 +1133,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>17</v>
+        <v>30.8</v>
       </c>
       <c r="V6">
-        <v>0.293103448275862</v>
+        <v>0.3515981735159818</v>
       </c>
       <c r="W6">
-        <v>0.0791746641074856</v>
+        <v>0.08486383787207093</v>
       </c>
       <c r="X6">
-        <v>0.04685972959369798</v>
+        <v>0.08039780635832447</v>
       </c>
       <c r="Y6">
-        <v>0.03231493451378761</v>
+        <v>0.004466031513746457</v>
       </c>
       <c r="Z6">
-        <v>0.1531265386509109</v>
+        <v>1.820224719101123</v>
       </c>
       <c r="AA6">
-        <v>0.07346241366920836</v>
+        <v>0.08687251172255153</v>
       </c>
       <c r="AB6">
-        <v>0.03947545646851618</v>
+        <v>0.07355451703648565</v>
       </c>
       <c r="AC6">
-        <v>0.03398695720069218</v>
+        <v>0.01331799468606588</v>
       </c>
       <c r="AD6">
-        <v>36.2</v>
+        <v>32.7</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>36.2</v>
+        <v>32.7</v>
       </c>
       <c r="AG6">
-        <v>19.2</v>
+        <v>1.900000000000002</v>
       </c>
       <c r="AH6">
-        <v>0.3842887473460722</v>
+        <v>0.2718204488778055</v>
       </c>
       <c r="AI6">
-        <v>0.1254766031195841</v>
+        <v>0.1507607192254495</v>
       </c>
       <c r="AJ6">
-        <v>0.2487046632124353</v>
+        <v>0.02122905027932963</v>
       </c>
       <c r="AK6">
-        <v>0.0707182320441989</v>
+        <v>0.01020956475013435</v>
       </c>
       <c r="AL6">
-        <v>0.594</v>
+        <v>2.99</v>
       </c>
       <c r="AM6">
-        <v>-0.576</v>
+        <v>2.696</v>
       </c>
       <c r="AN6">
-        <v>2.045197740112994</v>
+        <v>2.794871794871795</v>
       </c>
       <c r="AO6">
-        <v>28.28282828282828</v>
+        <v>2.140468227424749</v>
       </c>
       <c r="AP6">
-        <v>1.084745762711865</v>
+        <v>0.1623931623931626</v>
       </c>
       <c r="AQ6">
-        <v>-29.16666666666667</v>
+        <v>2.373887240356083</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gemini Investments (Holdings) Limited (SEHK:174)</t>
+          <t>TOP Financial Group Limited (NasdaqCM:TOP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1224,119 +1218,107 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D7">
-        <v>0.8859999999999999</v>
-      </c>
       <c r="G7">
-        <v>0.2359477124183007</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0.2359477124183007</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>0.4241830065359478</v>
+        <v>0.00793093984139864</v>
       </c>
       <c r="J7">
-        <v>0.2120915032679739</v>
+        <v>0.00773377401852588</v>
       </c>
       <c r="K7">
-        <v>-11.1</v>
+        <v>3.49</v>
       </c>
       <c r="L7">
-        <v>-0.07254901960784313</v>
+        <v>0.4462915601023018</v>
       </c>
       <c r="M7">
-        <v>0.029</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.0005471698113207547</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>-0.002612612612612613</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>0.029</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.0005471698113207547</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>-0.002612612612612613</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>159.2</v>
+        <v>6.2</v>
       </c>
       <c r="V7">
-        <v>3.00377358490566</v>
+        <v>0.03625730994152047</v>
       </c>
       <c r="W7">
-        <v>-0.02659956865564342</v>
+        <v>0.5170370370370371</v>
       </c>
       <c r="X7">
-        <v>0.3910342346338402</v>
+        <v>0.0705850049965534</v>
       </c>
       <c r="Y7">
-        <v>-0.4176338032894837</v>
+        <v>0.4464520320404837</v>
       </c>
       <c r="Z7">
-        <v>0.2033492822966507</v>
+        <v>3.706336350185842</v>
       </c>
       <c r="AA7">
-        <v>0.04312865497076024</v>
+        <v>0.0286639677689853</v>
       </c>
       <c r="AB7">
-        <v>0.04465213046486285</v>
+        <v>0.07054335070836062</v>
       </c>
       <c r="AC7">
-        <v>-0.001523475494102616</v>
+        <v>-0.04187938293937532</v>
       </c>
       <c r="AD7">
-        <v>1079.4</v>
+        <v>0.245</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>0.2199002522013132</v>
       </c>
       <c r="AF7">
-        <v>1079.4</v>
+        <v>0.4649002522013131</v>
       </c>
       <c r="AG7">
-        <v>920.2</v>
+        <v>-5.735099747798687</v>
       </c>
       <c r="AH7">
-        <v>0.953196750264924</v>
+        <v>0.002711343554963778</v>
       </c>
       <c r="AI7">
-        <v>0.5377104712563515</v>
+        <v>0.04359161747484271</v>
       </c>
       <c r="AJ7">
-        <v>0.945540484997945</v>
+        <v>-0.03470246700325768</v>
       </c>
       <c r="AK7">
-        <v>0.4978898387620387</v>
+        <v>-1.284485525734003</v>
       </c>
       <c r="AL7">
-        <v>51.7</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>50.58000000000001</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>16.42922374429224</v>
-      </c>
-      <c r="AO7">
-        <v>1.25531914893617</v>
+        <v>2.311320754716981</v>
       </c>
       <c r="AP7">
-        <v>14.00608828006088</v>
-      </c>
-      <c r="AQ7">
-        <v>1.283115856069593</v>
+        <v>-54.10471460187441</v>
       </c>
     </row>
     <row r="8">
@@ -1347,7 +1329,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oriental Explorer Holdings Limited (SEHK:430)</t>
+          <t>Planetree International Development Limited (SEHK:613)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1355,113 +1337,116 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.258</v>
+      </c>
       <c r="G8">
-        <v>0.2014925373134328</v>
+        <v>0.3677570093457944</v>
       </c>
       <c r="H8">
-        <v>0.2014925373134328</v>
+        <v>0.3677570093457944</v>
       </c>
       <c r="I8">
-        <v>0.591044776119403</v>
+        <v>0.2841121495327103</v>
       </c>
       <c r="J8">
-        <v>0.5151674062121824</v>
+        <v>0.2841121495327103</v>
       </c>
       <c r="K8">
-        <v>2.72</v>
+        <v>-3.96</v>
       </c>
       <c r="L8">
-        <v>0.8119402985074627</v>
+        <v>-0.1850467289719626</v>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.05291005291005291</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.3676470588235294</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.05291005291005291</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.3676470588235294</v>
+        <v>0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>32.3</v>
+        <v>35.6</v>
       </c>
       <c r="V8">
-        <v>1.708994708994709</v>
+        <v>0.586490939044481</v>
       </c>
       <c r="W8">
-        <v>0.01596244131455399</v>
+        <v>-0.01727748691099476</v>
       </c>
       <c r="X8">
-        <v>0.08219185244566261</v>
+        <v>0.08521463209143235</v>
       </c>
       <c r="Y8">
-        <v>-0.06622941113110863</v>
+        <v>-0.1024921190024271</v>
       </c>
       <c r="Z8">
-        <v>0.02221485411140584</v>
+        <v>0.08642518769208402</v>
       </c>
       <c r="AA8">
-        <v>0.01144436877195498</v>
+        <v>0.02455444584896593</v>
       </c>
       <c r="AB8">
-        <v>0.04443276127003391</v>
+        <v>0.07107951817797035</v>
       </c>
       <c r="AC8">
-        <v>-0.03298839249807893</v>
+        <v>-0.04652507232900442</v>
       </c>
       <c r="AD8">
-        <v>50.1</v>
+        <v>33.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>50.1</v>
+        <v>33.7</v>
       </c>
       <c r="AG8">
-        <v>17.8</v>
+        <v>-1.899999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.7260869565217392</v>
+        <v>0.3569915254237288</v>
       </c>
       <c r="AI8">
-        <v>0.2046568627450981</v>
+        <v>0.110891740704179</v>
       </c>
       <c r="AJ8">
-        <v>0.4850136239782017</v>
+        <v>-0.032312925170068</v>
       </c>
       <c r="AK8">
-        <v>0.08376470588235296</v>
+        <v>-0.007081625046589633</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="AM8">
-        <v>-0.006</v>
+        <v>0.73</v>
       </c>
       <c r="AN8">
-        <v>25.3030303030303</v>
+        <v>4.87698986975398</v>
+      </c>
+      <c r="AO8">
+        <v>8.328767123287671</v>
       </c>
       <c r="AP8">
-        <v>8.989898989898991</v>
+        <v>-0.2749638205499274</v>
       </c>
       <c r="AQ8">
-        <v>-330</v>
+        <v>8.328767123287671</v>
       </c>
     </row>
     <row r="9">
@@ -1472,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Future World Holdings Limited (SEHK:572)</t>
+          <t>Gemini Investments (Holdings) Limited (SEHK:174)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1481,115 +1466,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>1.728</v>
+        <v>0.473</v>
       </c>
       <c r="G9">
-        <v>-0.01763157894736842</v>
+        <v>0.4952658412235979</v>
       </c>
       <c r="H9">
-        <v>-0.01763157894736842</v>
+        <v>0.4952658412235979</v>
       </c>
       <c r="I9">
-        <v>0.09517543859649122</v>
+        <v>0.4304442825928623</v>
       </c>
       <c r="J9">
-        <v>0.06915737032799389</v>
+        <v>0.2152221412964312</v>
       </c>
       <c r="K9">
-        <v>1.19</v>
+        <v>-22.4</v>
       </c>
       <c r="L9">
-        <v>0.05219298245614035</v>
+        <v>-0.1631463947560087</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>0.029</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.001003460207612457</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>-0.001294642857142857</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>0.029</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.001003460207612457</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>-0.001294642857142857</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>0</v>
+        <v>101.3</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>3.505190311418685</v>
       </c>
       <c r="W9">
-        <v>0.01003372681281619</v>
+        <v>-0.05509099852434825</v>
       </c>
       <c r="X9">
-        <v>0.1825979842009498</v>
+        <v>0.8137041667669607</v>
       </c>
       <c r="Y9">
-        <v>-0.1725642573881336</v>
+        <v>-0.868795165291309</v>
       </c>
       <c r="Z9">
-        <v>0.1291784702549575</v>
+        <v>0.08486309413437172</v>
       </c>
       <c r="AA9">
-        <v>0.00893364330582584</v>
+        <v>0.01826441683664009</v>
       </c>
       <c r="AB9">
-        <v>0.04411103504621758</v>
+        <v>0.07825359899350258</v>
       </c>
       <c r="AC9">
-        <v>-0.03517739174039174</v>
+        <v>-0.05998918215686249</v>
       </c>
       <c r="AD9">
-        <v>56.6</v>
+        <v>811.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>56.6</v>
+        <v>811.1</v>
       </c>
       <c r="AG9">
-        <v>56.6</v>
+        <v>709.8000000000001</v>
       </c>
       <c r="AH9">
-        <v>0.893731249013106</v>
+        <v>0.9655952380952382</v>
       </c>
       <c r="AI9">
-        <v>0.3236134934248142</v>
+        <v>0.4712683748765325</v>
       </c>
       <c r="AJ9">
-        <v>0.893731249013106</v>
+        <v>0.9608772167320969</v>
       </c>
       <c r="AK9">
-        <v>0.3236134934248142</v>
+        <v>0.4382022471910113</v>
       </c>
       <c r="AL9">
-        <v>2.42</v>
+        <v>48.8</v>
       </c>
       <c r="AM9">
-        <v>2.42</v>
+        <v>47.894</v>
       </c>
       <c r="AN9">
-        <v>24.82456140350877</v>
+        <v>13.63193277310924</v>
       </c>
       <c r="AO9">
-        <v>0.8966942148760331</v>
+        <v>1.211065573770492</v>
       </c>
       <c r="AP9">
-        <v>24.82456140350877</v>
+        <v>11.92941176470588</v>
       </c>
       <c r="AQ9">
-        <v>0.8966942148760331</v>
+        <v>1.233975028187247</v>
       </c>
     </row>
     <row r="10">
@@ -1600,7 +1588,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pinestone Capital Limited (SEHK:804)</t>
+          <t>Oriental Explorer Holdings Limited (SEHK:430)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1609,106 +1597,121 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0827</v>
+        <v>-0.335</v>
+      </c>
+      <c r="E10">
+        <v>-0.374</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>0.6305732484076433</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>0.6305732484076433</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.5859872611464968</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>0.501707818407897</v>
       </c>
       <c r="K10">
-        <v>-2.3</v>
+        <v>2.15</v>
       </c>
       <c r="L10">
-        <v>-0.6666666666666666</v>
+        <v>0.6847133757961783</v>
       </c>
       <c r="M10">
-        <v>0.252</v>
+        <v>1.48</v>
       </c>
       <c r="N10">
-        <v>0.007777777777777778</v>
+        <v>0.07081339712918661</v>
       </c>
       <c r="O10">
-        <v>-0.1095652173913044</v>
+        <v>0.6883720930232559</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>1.48</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.07081339712918661</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>0.6883720930232559</v>
       </c>
       <c r="S10">
-        <v>0.252</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>5.26</v>
+        <v>22.2</v>
       </c>
       <c r="V10">
-        <v>0.1623456790123457</v>
+        <v>1.062200956937799</v>
       </c>
       <c r="W10">
-        <v>-0.0812720848056537</v>
+        <v>0.01104262968669748</v>
       </c>
       <c r="X10">
-        <v>0.0360271184816388</v>
+        <v>0.1208130366240062</v>
       </c>
       <c r="Y10">
-        <v>-0.1172992032872925</v>
+        <v>-0.1097704069373087</v>
       </c>
       <c r="Z10">
-        <v>0.138849760534471</v>
+        <v>0.0147764705882353</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>0.007413470822591985</v>
       </c>
       <c r="AB10">
-        <v>0.0360109445071766</v>
+        <v>0.07576467288440494</v>
       </c>
       <c r="AC10">
-        <v>-0.0360109445071766</v>
+        <v>-0.06835120206181296</v>
       </c>
       <c r="AD10">
-        <v>0.09</v>
+        <v>39.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.09</v>
+        <v>39.7</v>
       </c>
       <c r="AG10">
-        <v>-5.17</v>
+        <v>17.5</v>
       </c>
       <c r="AH10">
-        <v>0.002770083102493074</v>
+        <v>0.6551155115511551</v>
       </c>
       <c r="AI10">
-        <v>0.003462870334744132</v>
+        <v>0.1703862660944206</v>
       </c>
       <c r="AJ10">
-        <v>-0.1898641204553801</v>
+        <v>0.4557291666666667</v>
       </c>
       <c r="AK10">
-        <v>-0.2493970091654607</v>
+        <v>0.08301707779886149</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>-0.01900000000000002</v>
+      </c>
+      <c r="AN10">
+        <v>21.57608695652174</v>
+      </c>
+      <c r="AO10">
+        <v>10.57471264367816</v>
+      </c>
+      <c r="AP10">
+        <v>9.510869565217392</v>
+      </c>
+      <c r="AQ10">
+        <v>-96.84210526315782</v>
       </c>
     </row>
     <row r="11">
@@ -1719,7 +1722,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Get Nice Financial Group Limited (SEHK:1469)</t>
+          <t>CLSA Premium Limited (SEHK:6877)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1728,10 +1731,7 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.025</v>
-      </c>
-      <c r="E11">
-        <v>0.146</v>
+        <v>-0.329</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1740,97 +1740,100 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.01071544487762077</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.01071544487762077</v>
       </c>
       <c r="K11">
-        <v>73.90000000000001</v>
+        <v>-5.61</v>
       </c>
       <c r="L11">
-        <v>1.511247443762781</v>
+        <v>-4.921052631578948</v>
       </c>
       <c r="M11">
-        <v>19.3</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.07000362713093944</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.2611637347767253</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>19.3</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.07000362713093944</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.2611637347767253</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>155</v>
+        <v>28.2</v>
       </c>
       <c r="V11">
-        <v>0.5622052956111716</v>
+        <v>0.746031746031746</v>
       </c>
       <c r="W11">
-        <v>0.1443641336198477</v>
+        <v>-0.1464751958224543</v>
       </c>
       <c r="X11">
-        <v>0.03613614502209473</v>
+        <v>0.07064956282436816</v>
       </c>
       <c r="Y11">
-        <v>0.1082279885977529</v>
+        <v>-0.2171247586468225</v>
       </c>
       <c r="Z11">
-        <v>0.09044802290610053</v>
+        <v>0.178043712913323</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>0.00190781759152965</v>
       </c>
       <c r="AB11">
-        <v>0.0360829076663664</v>
+        <v>0.07061882246051489</v>
       </c>
       <c r="AC11">
-        <v>-0.0360829076663664</v>
+        <v>-0.06871100486898524</v>
       </c>
       <c r="AD11">
-        <v>2.49</v>
+        <v>0.181</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>0.01392196419756161</v>
       </c>
       <c r="AF11">
-        <v>2.49</v>
+        <v>0.1949219641975616</v>
       </c>
       <c r="AG11">
-        <v>-152.51</v>
+        <v>-28.00507803580244</v>
       </c>
       <c r="AH11">
-        <v>0.008950717135770517</v>
+        <v>0.005130210936641367</v>
       </c>
       <c r="AI11">
-        <v>0.004407937828603799</v>
+        <v>0.006188996575992243</v>
       </c>
       <c r="AJ11">
-        <v>-1.238006331682766</v>
+        <v>-2.859142537139828</v>
       </c>
       <c r="AK11">
-        <v>-0.3720754348727707</v>
+        <v>-8.499466251432976</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>12.06666666666667</v>
+      </c>
+      <c r="AP11">
+        <v>-1867.005202386829</v>
       </c>
     </row>
     <row r="12">
@@ -1841,7 +1844,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Innovax Holdings Limited (SEHK:2680)</t>
+          <t>Hatcher Group Limited (SEHK:8365)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1849,6 +1852,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.0142</v>
+      </c>
       <c r="G12">
         <v>0</v>
       </c>
@@ -1856,16 +1862,16 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>0.0004605478180712254</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>0.0004605478180712254</v>
       </c>
       <c r="K12">
-        <v>0.907</v>
+        <v>-1.05</v>
       </c>
       <c r="L12">
-        <v>0.08721153846153847</v>
+        <v>-0.1190476190476191</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1874,7 +1880,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1883,67 +1889,73 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>6.76</v>
+        <v>2.14</v>
       </c>
       <c r="V12">
-        <v>0.2693227091633466</v>
+        <v>0.02628992628992629</v>
       </c>
       <c r="W12">
-        <v>0.03171328671328671</v>
+        <v>-0.2192066805845511</v>
       </c>
       <c r="X12">
-        <v>0.03614677746060763</v>
+        <v>0.07234604247868281</v>
       </c>
       <c r="Y12">
-        <v>-0.004433490747320912</v>
+        <v>-0.291552723063234</v>
       </c>
       <c r="Z12">
-        <v>0.4496130733647486</v>
+        <v>2.903522235979438</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>0.001337210830501616</v>
       </c>
       <c r="AB12">
-        <v>0.03608987791716681</v>
+        <v>0.07123742167408731</v>
       </c>
       <c r="AC12">
-        <v>-0.03608987791716681</v>
+        <v>-0.06990021084358569</v>
       </c>
       <c r="AD12">
-        <v>0.242</v>
+        <v>5.63</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>0.004689841223058959</v>
       </c>
       <c r="AF12">
-        <v>0.242</v>
+        <v>5.634689841223059</v>
       </c>
       <c r="AG12">
-        <v>-6.518</v>
+        <v>3.494689841223059</v>
       </c>
       <c r="AH12">
-        <v>0.009549364691026753</v>
+        <v>0.0647407355791397</v>
       </c>
       <c r="AI12">
-        <v>0.008136641786026494</v>
+        <v>0.3895479200089519</v>
       </c>
       <c r="AJ12">
-        <v>-0.350769561941664</v>
+        <v>0.04116499922149561</v>
       </c>
       <c r="AK12">
-        <v>-0.2836132625533026</v>
+        <v>0.2835519502920212</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>1126</v>
+      </c>
+      <c r="AP12">
+        <v>698.9379682446117</v>
       </c>
     </row>
     <row r="13">
@@ -1954,7 +1966,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLSA Premium Limited (SEHK:6877)</t>
+          <t>Get Nice Financial Group Limited (SEHK:1469)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1963,7 +1975,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.472</v>
+        <v>-0.0273</v>
+      </c>
+      <c r="E13">
+        <v>-0.186</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1972,94 +1987,103 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.0001632066330289905</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>0.0001280033418349466</v>
       </c>
       <c r="K13">
-        <v>-10.4</v>
+        <v>13.5</v>
       </c>
       <c r="L13">
-        <v>-28.49315068493151</v>
+        <v>0.3013392857142858</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>19.1</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.08271979211779992</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.414814814814815</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>19.1</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.08271979211779992</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.414814814814815</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>32.6</v>
+        <v>199.4</v>
       </c>
       <c r="V13">
-        <v>1.105084745762712</v>
+        <v>0.8635773061931572</v>
       </c>
       <c r="W13">
-        <v>-0.2208067940552017</v>
+        <v>0.02400426742532006</v>
       </c>
       <c r="X13">
-        <v>0.0363858720050635</v>
+        <v>0.07066994979270666</v>
       </c>
       <c r="Y13">
-        <v>-0.2571926660602652</v>
+        <v>-0.04666568236738661</v>
       </c>
       <c r="Z13">
-        <v>0.02799079754601226</v>
+        <v>0.109363934987945</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.39989491546768e-05</v>
       </c>
       <c r="AB13">
-        <v>0.03609836180008848</v>
+        <v>0.07057893626503804</v>
       </c>
       <c r="AC13">
-        <v>-0.03609836180008848</v>
+        <v>-0.07056493731588337</v>
       </c>
       <c r="AD13">
-        <v>0.6889999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>0.008441714201506127</v>
       </c>
       <c r="AF13">
-        <v>0.6889999999999999</v>
+        <v>1.368441714201506</v>
       </c>
       <c r="AG13">
-        <v>-31.911</v>
+        <v>-198.0315582857985</v>
       </c>
       <c r="AH13">
-        <v>0.02282288250687336</v>
+        <v>0.005891638588962195</v>
       </c>
       <c r="AI13">
-        <v>0.01767165097848111</v>
+        <v>0.002472037079938908</v>
       </c>
       <c r="AJ13">
-        <v>13.23558689340522</v>
+        <v>-6.02497556798486</v>
       </c>
       <c r="AK13">
-        <v>-4.994678353419944</v>
+        <v>-0.5591451268986899</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
         <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>151.1111111111111</v>
+      </c>
+      <c r="AP13">
+        <v>-22003.50647619983</v>
       </c>
     </row>
     <row r="14">
@@ -2070,7 +2094,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Power Financial Group Limited (SEHK:397)</t>
+          <t>Get Nice Holdings Limited (SEHK:64)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2079,7 +2103,7 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.00795</v>
+        <v>-0.0696</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2088,94 +2112,103 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>0.0001532194756048348</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>7.66097378024174e-05</v>
       </c>
       <c r="K14">
-        <v>26.4</v>
+        <v>-2.53</v>
       </c>
       <c r="L14">
-        <v>2.4</v>
+        <v>-0.05315126050420167</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>12.3</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.06574024585783005</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>-4.861660079051384</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>12.3</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.06574024585783005</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>-4.861660079051384</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>14.7</v>
+        <v>270.6</v>
       </c>
       <c r="V14">
-        <v>0.2409836065573771</v>
+        <v>1.446285408872261</v>
       </c>
       <c r="W14">
-        <v>0.1478991596638655</v>
+        <v>-0.00338099692636643</v>
       </c>
       <c r="X14">
-        <v>0.03621018828720399</v>
+        <v>0.07217012762258541</v>
       </c>
       <c r="Y14">
-        <v>0.1116889713766616</v>
+        <v>-0.07555112454895184</v>
       </c>
       <c r="Z14">
-        <v>0.07497171521653195</v>
+        <v>0.08380745969231986</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>6.420467512915289e-06</v>
       </c>
       <c r="AB14">
-        <v>0.03613127357413167</v>
+        <v>0.0706064698767874</v>
       </c>
       <c r="AC14">
-        <v>-0.03613127357413167</v>
+        <v>-0.07060004940927449</v>
       </c>
       <c r="AD14">
-        <v>0.8100000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>0.008533764806049317</v>
       </c>
       <c r="AF14">
-        <v>0.8100000000000001</v>
+        <v>11.70853376480605</v>
       </c>
       <c r="AG14">
-        <v>-13.89</v>
+        <v>-258.891466235194</v>
       </c>
       <c r="AH14">
-        <v>0.0131046756188319</v>
+        <v>0.05889351700897029</v>
       </c>
       <c r="AI14">
-        <v>0.003939497106171879</v>
+        <v>0.01321044909166255</v>
       </c>
       <c r="AJ14">
-        <v>-0.2948418594778178</v>
+        <v>3.606159336362444</v>
       </c>
       <c r="AK14">
-        <v>-0.07275679639620762</v>
+        <v>-0.4204773070988289</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
         <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>1300</v>
+      </c>
+      <c r="AP14">
+        <v>-28765.71847057711</v>
       </c>
     </row>
     <row r="15">
@@ -2186,7 +2219,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Value Convergence Holdings Limited (SEHK:821)</t>
+          <t>Mason Group Holdings Limited (SEHK:273)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2195,7 +2228,7 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0721</v>
+        <v>-0.224</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2210,10 +2243,10 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>16</v>
+        <v>-105.2</v>
       </c>
       <c r="L15">
-        <v>1.495327102803738</v>
+        <v>-2.348214285714286</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2222,7 +2255,7 @@
         <v>-0</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2231,61 +2264,61 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>10.3</v>
+        <v>113.3</v>
       </c>
       <c r="V15">
-        <v>0.1072916666666667</v>
+        <v>0.6637375512595196</v>
       </c>
       <c r="W15">
-        <v>0.1698513800424628</v>
+        <v>-0.1583383503913305</v>
       </c>
       <c r="X15">
-        <v>0.03625654122854153</v>
+        <v>0.07105906331738263</v>
       </c>
       <c r="Y15">
-        <v>0.1335948388139213</v>
+        <v>-0.2293974137087132</v>
       </c>
       <c r="Z15">
-        <v>0.1177765547605944</v>
+        <v>0.0774483533581122</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.03616134602586063</v>
+        <v>0.07067497826549667</v>
       </c>
       <c r="AC15">
-        <v>-0.03616134602586063</v>
+        <v>-0.07067497826549667</v>
       </c>
       <c r="AD15">
-        <v>1.53</v>
+        <v>3.52</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>1.53</v>
+        <v>3.52</v>
       </c>
       <c r="AG15">
-        <v>-8.770000000000001</v>
+        <v>-109.78</v>
       </c>
       <c r="AH15">
-        <v>0.01568748077514611</v>
+        <v>0.02020433934106302</v>
       </c>
       <c r="AI15">
-        <v>0.01255848313223344</v>
+        <v>0.006538861643632041</v>
       </c>
       <c r="AJ15">
-        <v>-0.1005388054568383</v>
+        <v>-1.802035456336179</v>
       </c>
       <c r="AK15">
-        <v>-0.07863355151080428</v>
+        <v>-0.2582937273540069</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2302,7 +2335,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Get Nice Holdings Limited (SEHK:64)</t>
+          <t>DLC Asia Limited (SEHK:8210)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2310,12 +2343,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D16">
-        <v>-0.0388</v>
-      </c>
-      <c r="E16">
-        <v>-0.04480000000000001</v>
-      </c>
       <c r="G16">
         <v>0</v>
       </c>
@@ -2323,103 +2350,94 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0.0001280667718829691</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>0.0001008209179966583</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>27.5</v>
+        <v>-0.674</v>
       </c>
       <c r="L16">
-        <v>0.4372019077901431</v>
+        <v>-0.1278937381404175</v>
       </c>
       <c r="M16">
-        <v>12.4</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.06178375685102143</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>0.4509090909090909</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>12.4</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.06178375685102143</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>0.4509090909090909</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
-        <v>190.8</v>
+        <v>6.59</v>
       </c>
       <c r="V16">
-        <v>0.9506726457399104</v>
+        <v>1.734210526315789</v>
       </c>
       <c r="W16">
-        <v>0.03841855266834311</v>
+        <v>-0.06017857142857144</v>
       </c>
       <c r="X16">
-        <v>0.03708271539366938</v>
+        <v>0.07112624194604861</v>
       </c>
       <c r="Y16">
-        <v>0.001335837274673728</v>
+        <v>-0.13130481337462</v>
       </c>
       <c r="Z16">
-        <v>0.08837251949978425</v>
+        <v>1.129205056781659</v>
       </c>
       <c r="AA16">
-        <v>8.909798541645838e-06</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.03629096687016915</v>
+        <v>0.07069445332392621</v>
       </c>
       <c r="AC16">
-        <v>-0.03628205707162751</v>
+        <v>-0.07069445332392621</v>
       </c>
       <c r="AD16">
-        <v>12.7</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AE16">
-        <v>0.009723000242806208</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>12.70972300024281</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AG16">
-        <v>-178.0902769997572</v>
+        <v>-6.502</v>
       </c>
       <c r="AH16">
-        <v>0.05955550113444618</v>
+        <v>0.02263374485596708</v>
       </c>
       <c r="AI16">
-        <v>0.01387964185702922</v>
+        <v>0.008390541571319604</v>
       </c>
       <c r="AJ16">
-        <v>-7.876712023311604</v>
+        <v>2.406365655070318</v>
       </c>
       <c r="AK16">
-        <v>-0.2456723525002265</v>
+        <v>-1.668034889687019</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
         <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>1270</v>
-      </c>
-      <c r="AP16">
-        <v>-17809.02769997572</v>
       </c>
     </row>
     <row r="17">
@@ -2430,7 +2448,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mason Group Holdings Limited (SEHK:273)</t>
+          <t>Innovax Holdings Limited (SEHK:2680)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2451,10 +2469,10 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>-17.6</v>
+        <v>-3.81</v>
       </c>
       <c r="L17">
-        <v>-0.2141119221411192</v>
+        <v>-0.8619909502262444</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2478,55 +2496,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>83.3</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="V17">
-        <v>0.7319859402460457</v>
+        <v>0.8786407766990292</v>
       </c>
       <c r="W17">
-        <v>-0.0277733943506391</v>
+        <v>-0.1291525423728813</v>
       </c>
       <c r="X17">
-        <v>0.03669564890419041</v>
+        <v>0.07133056157673257</v>
       </c>
       <c r="Y17">
-        <v>-0.06446904325482951</v>
+        <v>-0.2004831039496139</v>
       </c>
       <c r="Z17">
-        <v>0.1500273772586238</v>
+        <v>0.1923244278130711</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.03633811759163899</v>
+        <v>0.07084812502781986</v>
       </c>
       <c r="AC17">
-        <v>-0.03633811759163899</v>
+        <v>-0.07084812502781986</v>
       </c>
       <c r="AD17">
-        <v>4.68</v>
+        <v>0.318</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>4.68</v>
+        <v>0.318</v>
       </c>
       <c r="AG17">
-        <v>-78.62</v>
+        <v>-8.732000000000001</v>
       </c>
       <c r="AH17">
-        <v>0.03950033760972316</v>
+        <v>0.02994914296477679</v>
       </c>
       <c r="AI17">
-        <v>0.006908972806991644</v>
+        <v>0.01199185458933555</v>
       </c>
       <c r="AJ17">
-        <v>-2.234792495736214</v>
+        <v>-5.56887755102041</v>
       </c>
       <c r="AK17">
-        <v>-0.1323390789119311</v>
+        <v>-0.4998855049232885</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2543,7 +2561,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DLC Asia Limited (SEHK:8210)</t>
+          <t>Imagi International Holdings Limited (SEHK:585)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2564,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>-0.542</v>
+        <v>-2.99</v>
       </c>
       <c r="L18">
-        <v>-0.09661319073083779</v>
+        <v>-2.669642857142857</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2591,55 +2609,55 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>6.83</v>
+        <v>20.5</v>
       </c>
       <c r="V18">
-        <v>1.147899159663865</v>
+        <v>0.5924855491329479</v>
       </c>
       <c r="W18">
-        <v>-0.04672413793103448</v>
+        <v>-0.02836812144212524</v>
       </c>
       <c r="X18">
-        <v>0.0368489118699812</v>
+        <v>0.07102807849847825</v>
       </c>
       <c r="Y18">
-        <v>-0.08357304980101568</v>
+        <v>-0.09939619994060349</v>
       </c>
       <c r="Z18">
-        <v>1.690268153058151</v>
+        <v>0.01054613935969868</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.03641129868965379</v>
+        <v>0.07090653013559396</v>
       </c>
       <c r="AC18">
-        <v>-0.03641129868965379</v>
+        <v>-0.07090653013559396</v>
       </c>
       <c r="AD18">
-        <v>0.297</v>
+        <v>0.673</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0.297</v>
+        <v>0.673</v>
       </c>
       <c r="AG18">
-        <v>-6.533</v>
+        <v>-19.827</v>
       </c>
       <c r="AH18">
-        <v>0.04754282055386586</v>
+        <v>0.01907974938338106</v>
       </c>
       <c r="AI18">
-        <v>0.02583282595459685</v>
+        <v>0.005338177087877658</v>
       </c>
       <c r="AJ18">
-        <v>11.20583190394511</v>
+        <v>-1.34211060718879</v>
       </c>
       <c r="AK18">
-        <v>-1.399828583672595</v>
+        <v>-0.1878036998096104</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2656,7 +2674,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PF Group Holdings Limited (SEHK:8221)</t>
+          <t>Sunwah Kingsway Capital Holdings Limited (SEHK:188)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2664,6 +2682,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D19">
+        <v>-0.194</v>
+      </c>
       <c r="G19">
         <v>0</v>
       </c>
@@ -2677,28 +2698,28 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>-2.08</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L19">
-        <v>-1.587786259541985</v>
+        <v>-1.742556917688266</v>
       </c>
       <c r="M19">
-        <v>6.42</v>
+        <v>1.78</v>
       </c>
       <c r="N19">
-        <v>0.4168831168831169</v>
+        <v>0.05953177257525084</v>
       </c>
       <c r="O19">
-        <v>-3.086538461538461</v>
+        <v>-0.1788944723618091</v>
       </c>
       <c r="P19">
-        <v>6.42</v>
+        <v>1.78</v>
       </c>
       <c r="Q19">
-        <v>0.4168831168831169</v>
+        <v>0.05953177257525084</v>
       </c>
       <c r="R19">
-        <v>-3.086538461538461</v>
+        <v>-0.1788944723618091</v>
       </c>
       <c r="S19">
         <v>0</v>
@@ -2707,55 +2728,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>13.3</v>
+        <v>20.7</v>
       </c>
       <c r="V19">
-        <v>0.8636363636363636</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="W19">
-        <v>-0.0859504132231405</v>
+        <v>-0.07761310452418096</v>
       </c>
       <c r="X19">
-        <v>0.03696697895649455</v>
+        <v>0.08282328262567012</v>
       </c>
       <c r="Y19">
-        <v>-0.122917392179635</v>
+        <v>-0.1604363871498511</v>
       </c>
       <c r="Z19">
-        <v>0.09116848771661215</v>
+        <v>0.04614066843364148</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.03646684387526988</v>
+        <v>0.07101661403330851</v>
       </c>
       <c r="AC19">
-        <v>-0.03646684387526988</v>
+        <v>-0.07101661403330851</v>
       </c>
       <c r="AD19">
-        <v>0.873</v>
+        <v>13.9</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0.873</v>
+        <v>13.9</v>
       </c>
       <c r="AG19">
-        <v>-12.427</v>
+        <v>-6.799999999999999</v>
       </c>
       <c r="AH19">
-        <v>0.05364714557856572</v>
+        <v>0.317351598173516</v>
       </c>
       <c r="AI19">
-        <v>0.0381672714554278</v>
+        <v>0.1069230769230769</v>
       </c>
       <c r="AJ19">
-        <v>-4.179952909519006</v>
+        <v>-0.2943722943722943</v>
       </c>
       <c r="AK19">
-        <v>-1.298130157735297</v>
+        <v>-0.06221408966148215</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2772,7 +2793,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fu Shek Financial Holdings Limited (SEHK:2263)</t>
+          <t>Power Financial Group Limited (SEHK:397)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2780,6 +2801,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D20">
+        <v>0.275</v>
+      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2793,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>1.62</v>
+        <v>-4.33</v>
       </c>
       <c r="L20">
-        <v>0.3266129032258065</v>
+        <v>-0.4369323915237134</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2805,7 +2829,7 @@
         <v>-0</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P20">
         <v>-0</v>
@@ -2814,61 +2838,61 @@
         <v>-0</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="U20">
-        <v>12.6</v>
+        <v>31.5</v>
       </c>
       <c r="V20">
-        <v>0.6395939086294417</v>
+        <v>0.4715568862275449</v>
       </c>
       <c r="W20">
-        <v>0.03884892086330935</v>
+        <v>-0.02117359413202934</v>
       </c>
       <c r="X20">
-        <v>0.03718223680015902</v>
+        <v>0.07188856434620605</v>
       </c>
       <c r="Y20">
-        <v>0.001666684063150327</v>
+        <v>-0.09306215847823539</v>
       </c>
       <c r="Z20">
-        <v>0.1278021128575109</v>
+        <v>0.05199588650100739</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.03656630170101874</v>
+        <v>0.07106555516844536</v>
       </c>
       <c r="AC20">
-        <v>-0.03656630170101874</v>
+        <v>-0.07106555516844536</v>
       </c>
       <c r="AD20">
-        <v>1.36</v>
+        <v>3.47</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>1.36</v>
+        <v>3.47</v>
       </c>
       <c r="AG20">
-        <v>-11.24</v>
+        <v>-28.03</v>
       </c>
       <c r="AH20">
-        <v>0.06457739791073125</v>
+        <v>0.04938095915753523</v>
       </c>
       <c r="AI20">
-        <v>0.03058929374718848</v>
+        <v>0.01707929320273662</v>
       </c>
       <c r="AJ20">
-        <v>-1.328605200945627</v>
+        <v>-0.7229816868712924</v>
       </c>
       <c r="AK20">
-        <v>-0.3527934714375393</v>
+        <v>-0.1632783829440205</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2885,7 +2909,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sunwah Kingsway Capital Holdings Limited (SEHK:188)</t>
+          <t>Pinestone Capital Limited (SEHK:804)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2894,7 +2918,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.24</v>
+        <v>-0.172</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2909,85 +2933,82 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>4.09</v>
+        <v>-1.03</v>
       </c>
       <c r="L21">
-        <v>0.1817777777777778</v>
+        <v>-0.4639639639639639</v>
       </c>
       <c r="M21">
-        <v>1.96</v>
+        <v>-0</v>
       </c>
       <c r="N21">
-        <v>0.05240641711229947</v>
+        <v>-0</v>
       </c>
       <c r="O21">
-        <v>0.4792176039119804</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>1.96</v>
+        <v>-0</v>
       </c>
       <c r="Q21">
-        <v>0.05240641711229947</v>
+        <v>-0</v>
       </c>
       <c r="R21">
-        <v>0.4792176039119804</v>
+        <v>0</v>
       </c>
       <c r="S21">
         <v>0</v>
       </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
       <c r="U21">
-        <v>21.7</v>
+        <v>8.68</v>
       </c>
       <c r="V21">
-        <v>0.5802139037433155</v>
+        <v>0.7233333333333333</v>
       </c>
       <c r="W21">
-        <v>0.03230647709320695</v>
+        <v>-0.03976833976833977</v>
       </c>
       <c r="X21">
-        <v>0.04408956074238441</v>
+        <v>0.07109116707611454</v>
       </c>
       <c r="Y21">
-        <v>-0.01178308364917746</v>
+        <v>-0.1108595068444543</v>
       </c>
       <c r="Z21">
-        <v>0.1931844525152616</v>
+        <v>0.1070911722141824</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.03764357756955148</v>
+        <v>0.0713337204556838</v>
       </c>
       <c r="AC21">
-        <v>-0.03764357756955148</v>
+        <v>-0.0713337204556838</v>
       </c>
       <c r="AD21">
-        <v>17.4</v>
+        <v>0.262</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>17.4</v>
+        <v>0.262</v>
       </c>
       <c r="AG21">
-        <v>-4.300000000000001</v>
+        <v>-8.417999999999999</v>
       </c>
       <c r="AH21">
-        <v>0.3175182481751825</v>
+        <v>0.02136682433534497</v>
       </c>
       <c r="AI21">
-        <v>0.1193415637860082</v>
+        <v>0.01053817070227657</v>
       </c>
       <c r="AJ21">
-        <v>-0.1299093655589124</v>
+        <v>-2.350083752093802</v>
       </c>
       <c r="AK21">
-        <v>-0.03464947622884771</v>
+        <v>-0.5202076381164256</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3004,7 +3025,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CL Group (Holdings) Limited (SEHK:8098)</t>
+          <t>Bright Smart Securities &amp; Commodities Group Limited (SEHK:1428)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3013,10 +3034,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>-0.174</v>
+        <v>0.0699</v>
       </c>
       <c r="E22">
-        <v>-0.24</v>
+        <v>0.0727</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3031,28 +3052,28 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0.87</v>
+        <v>63.4</v>
       </c>
       <c r="L22">
-        <v>0.2566371681415929</v>
+        <v>0.4847094801223241</v>
       </c>
       <c r="M22">
-        <v>2.83</v>
+        <v>21.6</v>
       </c>
       <c r="N22">
-        <v>0.1252212389380531</v>
+        <v>0.05114847264977505</v>
       </c>
       <c r="O22">
-        <v>3.252873563218391</v>
+        <v>0.3406940063091483</v>
       </c>
       <c r="P22">
-        <v>2.83</v>
+        <v>21.6</v>
       </c>
       <c r="Q22">
-        <v>0.1252212389380531</v>
+        <v>0.05114847264977505</v>
       </c>
       <c r="R22">
-        <v>3.252873563218391</v>
+        <v>0.3406940063091483</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3061,55 +3082,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>0.132</v>
+        <v>72.7</v>
       </c>
       <c r="V22">
-        <v>0.00584070796460177</v>
+        <v>0.1721524982240114</v>
       </c>
       <c r="W22">
-        <v>0.02815533980582524</v>
+        <v>0.2238700564971751</v>
       </c>
       <c r="X22">
-        <v>0.04004398523713289</v>
+        <v>0.1051952054039374</v>
       </c>
       <c r="Y22">
-        <v>-0.01188864543130764</v>
+        <v>0.1186748510932378</v>
       </c>
       <c r="Z22">
-        <v>0.1085494716618636</v>
+        <v>0.1102866779089376</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.0376993014242178</v>
+        <v>0.07141285662809255</v>
       </c>
       <c r="AC22">
-        <v>-0.0376993014242178</v>
+        <v>-0.07141285662809255</v>
       </c>
       <c r="AD22">
-        <v>5.27</v>
+        <v>553.1</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>5.27</v>
+        <v>553.1</v>
       </c>
       <c r="AG22">
-        <v>5.138</v>
+        <v>480.4</v>
       </c>
       <c r="AH22">
-        <v>0.1890922138500179</v>
+        <v>0.5670494156243592</v>
       </c>
       <c r="AI22">
-        <v>0.1494187694924865</v>
+        <v>0.6315368805663394</v>
       </c>
       <c r="AJ22">
-        <v>0.1852332540197563</v>
+        <v>0.5321812340755512</v>
       </c>
       <c r="AK22">
-        <v>0.1462234617792703</v>
+        <v>0.5981820445772631</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3126,7 +3147,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Imagi International Holdings Limited (SEHK:585)</t>
+          <t>GoFintech Innovation Limited (SEHK:290)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3134,6 +3155,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D23">
+        <v>-0.0737</v>
+      </c>
       <c r="G23">
         <v>0</v>
       </c>
@@ -3141,16 +3165,16 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>0.0001694645768646301</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>0.0001694645768646301</v>
       </c>
       <c r="K23">
-        <v>24.3</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="L23">
-        <v>1.004132231404959</v>
+        <v>-1.887265135699373</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3159,7 +3183,7 @@
         <v>-0</v>
       </c>
       <c r="O23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P23">
         <v>-0</v>
@@ -3168,67 +3192,73 @@
         <v>-0</v>
       </c>
       <c r="R23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
       <c r="U23">
-        <v>12.7</v>
+        <v>18</v>
       </c>
       <c r="V23">
-        <v>0.1892697466467958</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="W23">
-        <v>0.2739571589627959</v>
+        <v>-0.2404255319148936</v>
       </c>
       <c r="X23">
-        <v>0.03948621834402703</v>
+        <v>0.07407458068677203</v>
       </c>
       <c r="Y23">
-        <v>0.2344709406187689</v>
+        <v>-0.3145001126016656</v>
       </c>
       <c r="Z23">
-        <v>0.3121775025799794</v>
+        <v>0.125573662819179</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.12802876349939e-05</v>
       </c>
       <c r="AB23">
-        <v>0.03792887699559315</v>
+        <v>0.07146338117797854</v>
       </c>
       <c r="AC23">
-        <v>-0.03792887699559315</v>
+        <v>-0.07144210089034354</v>
       </c>
       <c r="AD23">
-        <v>13.5</v>
+        <v>5.11</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>0.0009413233840921099</v>
       </c>
       <c r="AF23">
-        <v>13.5</v>
+        <v>5.110941323384092</v>
       </c>
       <c r="AG23">
-        <v>0.8000000000000007</v>
+        <v>-12.88905867661591</v>
       </c>
       <c r="AH23">
-        <v>0.1674937965260546</v>
+        <v>0.1185532295629052</v>
       </c>
       <c r="AI23">
-        <v>0.1032110091743119</v>
+        <v>0.1303447749757565</v>
       </c>
       <c r="AJ23">
-        <v>0.01178203240058911</v>
+        <v>-0.5132845682934718</v>
       </c>
       <c r="AK23">
-        <v>0.006773920406435231</v>
+        <v>-0.6076608520153846</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
         <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>5110</v>
+      </c>
+      <c r="AP23">
+        <v>-12889.05867661591</v>
       </c>
     </row>
     <row r="24">
@@ -3239,7 +3269,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Scully Royalty Ltd. (NYSE:SRL)</t>
+          <t>Value Convergence Holdings Limited (SEHK:821)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3248,7 +3278,7 @@
         </is>
       </c>
       <c r="D24">
-        <v>-0.441</v>
+        <v>-0.08310000000000001</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3263,10 +3293,10 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>9.039999999999999</v>
+        <v>-18.8</v>
       </c>
       <c r="L24">
-        <v>0.136969696969697</v>
+        <v>-1.693693693693694</v>
       </c>
       <c r="M24">
         <v>-0</v>
@@ -3275,7 +3305,7 @@
         <v>-0</v>
       </c>
       <c r="O24">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P24">
         <v>-0</v>
@@ -3284,61 +3314,61 @@
         <v>-0</v>
       </c>
       <c r="R24">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
       <c r="U24">
-        <v>44.9</v>
+        <v>6.54</v>
       </c>
       <c r="V24">
-        <v>0.3704620462046204</v>
+        <v>0.1635</v>
       </c>
       <c r="W24">
-        <v>0.03424242424242424</v>
+        <v>-0.1557580778790389</v>
       </c>
       <c r="X24">
-        <v>0.04145908964005164</v>
+        <v>0.07310146814793225</v>
       </c>
       <c r="Y24">
-        <v>-0.0072166653976274</v>
+        <v>-0.2288595460269712</v>
       </c>
       <c r="Z24">
-        <v>0.2742002492729539</v>
+        <v>0.09940001790991314</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.03815498756105411</v>
+        <v>0.07150938020768809</v>
       </c>
       <c r="AC24">
-        <v>-0.03815498756105411</v>
+        <v>-0.07150938020768809</v>
       </c>
       <c r="AD24">
-        <v>38.1</v>
+        <v>3.91</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>38.1</v>
+        <v>3.91</v>
       </c>
       <c r="AG24">
-        <v>-6.799999999999997</v>
+        <v>-2.63</v>
       </c>
       <c r="AH24">
-        <v>0.2391713747645951</v>
+        <v>0.08904577544978366</v>
       </c>
       <c r="AI24">
-        <v>0.1127218934911243</v>
+        <v>0.03426518271842958</v>
       </c>
       <c r="AJ24">
-        <v>-0.05944055944055941</v>
+        <v>-0.07037730800107038</v>
       </c>
       <c r="AK24">
-        <v>-0.02320027294438757</v>
+        <v>-0.02444919587245514</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3355,7 +3385,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Glory Sun Financial Group Limited (SEHK:1282)</t>
+          <t>PF Group Holdings Limited (SEHK:8221)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3364,25 +3394,25 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.631</v>
+        <v>-0.346</v>
       </c>
       <c r="G25">
-        <v>-0.0004370420855341626</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>-0.0004370420855341626</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>0.002802862497870165</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>0.002802862497870165</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>-19.6</v>
+        <v>-3.29</v>
       </c>
       <c r="L25">
-        <v>-0.01669790424263077</v>
+        <v>-3.046296296296296</v>
       </c>
       <c r="M25">
         <v>-0</v>
@@ -3406,73 +3436,61 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>209.1</v>
+        <v>10.6</v>
       </c>
       <c r="V25">
-        <v>0.259751552795031</v>
+        <v>1.118143459915612</v>
       </c>
       <c r="W25">
-        <v>-0.01955892625486479</v>
+        <v>-0.1495454545454545</v>
       </c>
       <c r="X25">
-        <v>0.07652451390777436</v>
+        <v>0.07203814740009798</v>
       </c>
       <c r="Y25">
-        <v>-0.09608344016263914</v>
+        <v>-0.2215836019455525</v>
       </c>
       <c r="Z25">
-        <v>0.5188295615275813</v>
+        <v>0.11281729865246</v>
       </c>
       <c r="AA25">
-        <v>0.001454207920792079</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.03964549174675063</v>
+        <v>0.07163621102767598</v>
       </c>
       <c r="AC25">
-        <v>-0.03819128382595855</v>
+        <v>-0.07163621102767598</v>
       </c>
       <c r="AD25">
-        <v>1872.2</v>
+        <v>0.546</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>1872.2</v>
+        <v>0.546</v>
       </c>
       <c r="AG25">
-        <v>1663.1</v>
+        <v>-10.054</v>
       </c>
       <c r="AH25">
-        <v>0.6993127147766324</v>
+        <v>0.05445840813883902</v>
       </c>
       <c r="AI25">
-        <v>0.5590826290799416</v>
+        <v>0.02866743673212223</v>
       </c>
       <c r="AJ25">
-        <v>0.6738381751144604</v>
+        <v>17.51567944250872</v>
       </c>
       <c r="AK25">
-        <v>0.5297171614218371</v>
+        <v>-1.190385981529718</v>
       </c>
       <c r="AL25">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>2.76</v>
-      </c>
-      <c r="AN25">
-        <v>138.6814814814815</v>
-      </c>
-      <c r="AO25">
-        <v>0.2860869565217392</v>
-      </c>
-      <c r="AP25">
-        <v>123.1925925925926</v>
-      </c>
-      <c r="AQ25">
-        <v>1.192028985507247</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3483,7 +3501,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Altus Holdings Limited (SEHK:8149)</t>
+          <t>Cinda International Holdings Limited (SEHK:111)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3492,10 +3510,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>-0.00752</v>
-      </c>
-      <c r="E26">
-        <v>0.168</v>
+        <v>-0.079</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3510,28 +3525,28 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>1.36</v>
+        <v>-4.46</v>
       </c>
       <c r="L26">
-        <v>0.1997063142437592</v>
+        <v>-0.2372340425531915</v>
       </c>
       <c r="M26">
-        <v>0.159</v>
+        <v>4.09</v>
       </c>
       <c r="N26">
-        <v>0.008112244897959184</v>
+        <v>0.1381756756756757</v>
       </c>
       <c r="O26">
-        <v>0.1169117647058823</v>
+        <v>-0.9170403587443946</v>
       </c>
       <c r="P26">
-        <v>0.159</v>
+        <v>4.09</v>
       </c>
       <c r="Q26">
-        <v>0.008112244897959184</v>
+        <v>0.1381756756756757</v>
       </c>
       <c r="R26">
-        <v>0.1169117647058823</v>
+        <v>-0.9170403587443946</v>
       </c>
       <c r="S26">
         <v>0</v>
@@ -3540,55 +3555,55 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>4.44</v>
+        <v>105.2</v>
       </c>
       <c r="V26">
-        <v>0.226530612244898</v>
+        <v>3.554054054054054</v>
       </c>
       <c r="W26">
-        <v>0.02297297297297297</v>
+        <v>-0.03425499231950845</v>
       </c>
       <c r="X26">
-        <v>0.05803766824749211</v>
+        <v>0.1798339803211876</v>
       </c>
       <c r="Y26">
-        <v>-0.03506469527451914</v>
+        <v>-0.214088972640696</v>
       </c>
       <c r="Z26">
-        <v>0.0828164903319956</v>
+        <v>0.09157330735509012</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.03890745658521224</v>
+        <v>0.07179046812762324</v>
       </c>
       <c r="AC26">
-        <v>-0.03890745658521224</v>
+        <v>-0.07179046812762324</v>
       </c>
       <c r="AD26">
-        <v>24.8</v>
+        <v>122.2</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>24.8</v>
+        <v>122.2</v>
       </c>
       <c r="AG26">
-        <v>20.36</v>
+        <v>17</v>
       </c>
       <c r="AH26">
-        <v>0.5585585585585585</v>
+        <v>0.8050065876152832</v>
       </c>
       <c r="AI26">
-        <v>0.2931442080378251</v>
+        <v>0.5014361920393927</v>
       </c>
       <c r="AJ26">
-        <v>0.5095095095095095</v>
+        <v>0.3648068669527897</v>
       </c>
       <c r="AK26">
-        <v>0.2539920159680639</v>
+        <v>0.1227436823104693</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3605,7 +3620,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Emperor Capital Group Limited (SEHK:717)</t>
+          <t>Fu Shek Financial Holdings Limited (SEHK:2263)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3613,9 +3628,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D27">
-        <v>-0.188</v>
-      </c>
       <c r="G27">
         <v>0</v>
       </c>
@@ -3629,10 +3641,10 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>-74</v>
+        <v>1.63</v>
       </c>
       <c r="L27">
-        <v>-1.774580335731415</v>
+        <v>0.3646532438478747</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3641,7 +3653,7 @@
         <v>-0</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P27">
         <v>-0</v>
@@ -3650,61 +3662,61 @@
         <v>-0</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="U27">
-        <v>111</v>
+        <v>15.2</v>
       </c>
       <c r="V27">
-        <v>1.646884272997033</v>
+        <v>0.628099173553719</v>
       </c>
       <c r="W27">
-        <v>-0.1295971978984238</v>
+        <v>0.03781902552204176</v>
       </c>
       <c r="X27">
-        <v>0.06536250698392244</v>
+        <v>0.07497747072755753</v>
       </c>
       <c r="Y27">
-        <v>-0.1949597048823463</v>
+        <v>-0.03715844520551578</v>
       </c>
       <c r="Z27">
-        <v>0.0429631155985988</v>
+        <v>0.14030131826742</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.03926959830765168</v>
+        <v>0.07212732307824483</v>
       </c>
       <c r="AC27">
-        <v>-0.03926959830765168</v>
+        <v>-0.07212732307824483</v>
       </c>
       <c r="AD27">
-        <v>113.6</v>
+        <v>4.08</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>113.6</v>
+        <v>4.08</v>
       </c>
       <c r="AG27">
-        <v>2.599999999999994</v>
+        <v>-11.12</v>
       </c>
       <c r="AH27">
-        <v>0.6276243093922652</v>
+        <v>0.1442715700141443</v>
       </c>
       <c r="AI27">
-        <v>0.186811379707285</v>
+        <v>0.08415841584158416</v>
       </c>
       <c r="AJ27">
-        <v>0.03714285714285706</v>
+        <v>-0.8501529051987767</v>
       </c>
       <c r="AK27">
-        <v>0.005230335948501296</v>
+        <v>-0.3341346153846154</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3721,7 +3733,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CMBC Capital Holdings Limited (SEHK:1141)</t>
+          <t>Scully Royalty Ltd. (NYSE:SRL)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3729,6 +3741,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D28">
+        <v>-0.374</v>
+      </c>
       <c r="G28">
         <v>0</v>
       </c>
@@ -3742,85 +3757,85 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>55.2</v>
+        <v>1.33</v>
       </c>
       <c r="L28">
-        <v>0.6019629225736096</v>
+        <v>0.02923076923076923</v>
       </c>
       <c r="M28">
-        <v>21.94</v>
+        <v>6.68</v>
       </c>
       <c r="N28">
-        <v>0.04559434746467166</v>
+        <v>0.0584426946631671</v>
       </c>
       <c r="O28">
-        <v>0.397463768115942</v>
+        <v>5.022556390977443</v>
       </c>
       <c r="P28">
-        <v>20.3</v>
+        <v>6.68</v>
       </c>
       <c r="Q28">
-        <v>0.04218620116375728</v>
+        <v>0.0584426946631671</v>
       </c>
       <c r="R28">
-        <v>0.3677536231884058</v>
+        <v>5.022556390977443</v>
       </c>
       <c r="S28">
-        <v>1.640000000000001</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>0.07474931631722882</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>121.2</v>
+        <v>47.5</v>
       </c>
       <c r="V28">
-        <v>0.2518703241895262</v>
+        <v>0.4155730533683289</v>
       </c>
       <c r="W28">
-        <v>0.2027920646583395</v>
+        <v>0.004516129032258065</v>
       </c>
       <c r="X28">
-        <v>0.08705887457212032</v>
+        <v>0.07778758349893179</v>
       </c>
       <c r="Y28">
-        <v>0.1157331900862192</v>
+        <v>-0.07327145446667373</v>
       </c>
       <c r="Z28">
-        <v>0.06054044061821231</v>
+        <v>0.1581508515815085</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.03988790727937078</v>
+        <v>0.07224063493625468</v>
       </c>
       <c r="AC28">
-        <v>-0.03988790727937078</v>
+        <v>-0.07224063493625468</v>
       </c>
       <c r="AD28">
-        <v>1409.9</v>
+        <v>31.4</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>1409.9</v>
+        <v>31.4</v>
       </c>
       <c r="AG28">
-        <v>1288.7</v>
+        <v>-16.1</v>
       </c>
       <c r="AH28">
-        <v>0.7455449209454814</v>
+        <v>0.2155113246396706</v>
       </c>
       <c r="AI28">
-        <v>0.7999432624113476</v>
+        <v>0.1006087792374239</v>
       </c>
       <c r="AJ28">
-        <v>0.7281202327815131</v>
+        <v>-0.1639511201629328</v>
       </c>
       <c r="AK28">
-        <v>0.7851702918418326</v>
+        <v>-0.06084656084656086</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3837,7 +3852,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BOCOM International Holdings Company Limited (SEHK:3329)</t>
+          <t>LFG Investment Holdings Limited (SEHK:3938)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3852,97 +3867,103 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>0.001095995077339146</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>0.001095995077339146</v>
       </c>
       <c r="K29">
-        <v>144.4</v>
+        <v>-3.19</v>
       </c>
       <c r="L29">
-        <v>0.5199855959668708</v>
+        <v>-0.5379426644182125</v>
       </c>
       <c r="M29">
-        <v>31.7</v>
+        <v>0.139</v>
       </c>
       <c r="N29">
-        <v>0.04994485583740349</v>
+        <v>0.0102962962962963</v>
       </c>
       <c r="O29">
-        <v>0.2195290858725762</v>
+        <v>-0.04357366771159875</v>
       </c>
       <c r="P29">
-        <v>31.7</v>
+        <v>-0</v>
       </c>
       <c r="Q29">
-        <v>0.04994485583740349</v>
+        <v>-0</v>
       </c>
       <c r="R29">
-        <v>0.2195290858725762</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29">
-        <v>280</v>
+        <v>6.19</v>
       </c>
       <c r="V29">
-        <v>0.4411533007720183</v>
+        <v>0.4585185185185185</v>
       </c>
       <c r="W29">
-        <v>0.1695034628477521</v>
+        <v>-0.1369098712446352</v>
       </c>
       <c r="X29">
-        <v>0.106957805010534</v>
+        <v>0.07994297211804313</v>
       </c>
       <c r="Y29">
-        <v>0.06254565783721804</v>
+        <v>-0.2168528433626783</v>
       </c>
       <c r="Z29">
-        <v>0.1139889992611444</v>
+        <v>0.2292451586453085</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>0.0002512515653790896</v>
       </c>
       <c r="AB29">
-        <v>0.04018819767062894</v>
+        <v>0.07345131728615643</v>
       </c>
       <c r="AC29">
-        <v>-0.04018819767062894</v>
+        <v>-0.07320006572077735</v>
       </c>
       <c r="AD29">
-        <v>2584.1</v>
+        <v>4.8</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>0.007503745956894336</v>
       </c>
       <c r="AF29">
-        <v>2584.1</v>
+        <v>4.807503745956894</v>
       </c>
       <c r="AG29">
-        <v>2304.1</v>
+        <v>-1.382496254043106</v>
       </c>
       <c r="AH29">
-        <v>0.8028147135578476</v>
+        <v>0.2625974470724117</v>
       </c>
       <c r="AI29">
-        <v>0.7128748379265636</v>
+        <v>0.1930142737301513</v>
       </c>
       <c r="AJ29">
-        <v>0.7840274942153259</v>
+        <v>-0.1140908460213505</v>
       </c>
       <c r="AK29">
-        <v>0.6888397261502587</v>
+        <v>-0.07386114477694358</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
         <v>0</v>
+      </c>
+      <c r="AN29">
+        <v>600</v>
+      </c>
+      <c r="AP29">
+        <v>-172.8120317553883</v>
       </c>
     </row>
     <row r="30">
@@ -3953,7 +3974,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cinda International Holdings Limited (SEHK:111)</t>
+          <t>CL Group (Holdings) Limited (SEHK:8098)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3962,7 +3983,7 @@
         </is>
       </c>
       <c r="D30">
-        <v>0.0735</v>
+        <v>-0.222</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3977,28 +3998,28 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>14.2</v>
+        <v>-0.529</v>
       </c>
       <c r="L30">
-        <v>0.4536741214057508</v>
+        <v>-0.2449074074074074</v>
       </c>
       <c r="M30">
-        <v>2.5648</v>
+        <v>1.4</v>
       </c>
       <c r="N30">
-        <v>0.07085082872928178</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="O30">
-        <v>0.1806197183098592</v>
+        <v>-2.646502835538752</v>
       </c>
       <c r="P30">
-        <v>2.5648</v>
+        <v>1.4</v>
       </c>
       <c r="Q30">
-        <v>0.07085082872928178</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="R30">
-        <v>0.1806197183098592</v>
+        <v>-2.646502835538752</v>
       </c>
       <c r="S30">
         <v>0</v>
@@ -4007,55 +4028,55 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>94.40000000000001</v>
+        <v>0.491</v>
       </c>
       <c r="V30">
-        <v>2.607734806629834</v>
+        <v>0.03340136054421769</v>
       </c>
       <c r="W30">
-        <v>0.120954003407155</v>
+        <v>-0.01763333333333333</v>
       </c>
       <c r="X30">
-        <v>0.1176088961318489</v>
+        <v>0.08070885379623675</v>
       </c>
       <c r="Y30">
-        <v>0.003345107275306097</v>
+        <v>-0.09834218712957009</v>
       </c>
       <c r="Z30">
-        <v>0.1761395610579629</v>
+        <v>0.06147191075189255</v>
       </c>
       <c r="AA30">
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.04029936289705111</v>
+        <v>0.0736236184685794</v>
       </c>
       <c r="AC30">
-        <v>-0.04029936289705111</v>
+        <v>-0.0736236184685794</v>
       </c>
       <c r="AD30">
-        <v>169.5</v>
+        <v>5.66</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>169.5</v>
+        <v>5.66</v>
       </c>
       <c r="AG30">
-        <v>75.09999999999999</v>
+        <v>5.169</v>
       </c>
       <c r="AH30">
-        <v>0.8240155566358776</v>
+        <v>0.2779960707269155</v>
       </c>
       <c r="AI30">
-        <v>0.5655655655655656</v>
+        <v>0.169157202630006</v>
       </c>
       <c r="AJ30">
-        <v>0.6747529200359389</v>
+        <v>0.2601540087573607</v>
       </c>
       <c r="AK30">
-        <v>0.365806137359961</v>
+        <v>0.1567836452425005</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -4072,7 +4093,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LFG Investment Holdings Limited (SEHK:3938)</t>
+          <t>Emperor Capital Group Limited (SEHK:717)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4080,6 +4101,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D31">
+        <v>-0.319</v>
+      </c>
       <c r="G31">
         <v>0</v>
       </c>
@@ -4087,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0.0006607619606215817</v>
+        <v>0</v>
       </c>
       <c r="J31">
-        <v>0.0005459801148847399</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>1.6</v>
+        <v>-38.1</v>
       </c>
       <c r="L31">
-        <v>0.1290322580645161</v>
+        <v>-1.780373831775701</v>
       </c>
       <c r="M31">
-        <v>0.461</v>
+        <v>-0</v>
       </c>
       <c r="N31">
-        <v>0.03688</v>
+        <v>-0</v>
       </c>
       <c r="O31">
-        <v>0.288125</v>
+        <v>0</v>
       </c>
       <c r="P31">
         <v>-0</v>
@@ -4114,76 +4138,67 @@
         <v>-0</v>
       </c>
       <c r="R31">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>0.461</v>
-      </c>
-      <c r="T31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>5.82</v>
+        <v>109.7</v>
       </c>
       <c r="V31">
-        <v>0.4656</v>
+        <v>1.692901234567901</v>
       </c>
       <c r="W31">
-        <v>0.07373271889400922</v>
+        <v>-0.07704752275025278</v>
       </c>
       <c r="X31">
-        <v>0.04769279389187764</v>
+        <v>0.09331554928756736</v>
       </c>
       <c r="Y31">
-        <v>0.02603992500213158</v>
+        <v>-0.1703630720378201</v>
       </c>
       <c r="Z31">
-        <v>0.5953228910725393</v>
+        <v>0.04304968819151075</v>
       </c>
       <c r="AA31">
-        <v>0.0003250344604613005</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.04065798494910038</v>
+        <v>0.0742220877077111</v>
       </c>
       <c r="AC31">
-        <v>-0.04033295048863908</v>
+        <v>-0.0742220877077111</v>
       </c>
       <c r="AD31">
-        <v>8.380000000000001</v>
+        <v>55.8</v>
       </c>
       <c r="AE31">
-        <v>0.01903275844146193</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>8.399032758441463</v>
+        <v>55.8</v>
       </c>
       <c r="AG31">
-        <v>2.579032758441462</v>
+        <v>-53.90000000000001</v>
       </c>
       <c r="AH31">
-        <v>0.4018861951900121</v>
+        <v>0.4626865671641791</v>
       </c>
       <c r="AI31">
-        <v>0.2633005465101076</v>
+        <v>0.1098209013973627</v>
       </c>
       <c r="AJ31">
-        <v>0.171034362731103</v>
+        <v>-4.944954128440371</v>
       </c>
       <c r="AK31">
-        <v>0.09889296057602677</v>
+        <v>-0.1352911646586346</v>
       </c>
       <c r="AL31">
         <v>0</v>
       </c>
       <c r="AM31">
         <v>0</v>
-      </c>
-      <c r="AN31">
-        <v>698.3333333333334</v>
-      </c>
-      <c r="AP31">
-        <v>214.9193965367885</v>
       </c>
     </row>
     <row r="32">
@@ -4194,7 +4209,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kingston Financial Group Limited (SEHK:1031)</t>
+          <t>First Shanghai Investments Limited (SEHK:227)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4203,7 +4218,7 @@
         </is>
       </c>
       <c r="D32">
-        <v>-0.298</v>
+        <v>0.012</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4218,10 +4233,10 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>-14.2</v>
+        <v>-18</v>
       </c>
       <c r="L32">
-        <v>-0.25</v>
+        <v>-0.3296703296703297</v>
       </c>
       <c r="M32">
         <v>-0</v>
@@ -4245,61 +4260,61 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>122.2</v>
+        <v>42.8</v>
       </c>
       <c r="V32">
-        <v>0.1425571628558096</v>
+        <v>1.185595567867036</v>
       </c>
       <c r="W32">
-        <v>-0.005045480386583286</v>
+        <v>-0.05436424041075204</v>
       </c>
       <c r="X32">
-        <v>0.05251752827695298</v>
+        <v>0.09640655531115255</v>
       </c>
       <c r="Y32">
-        <v>-0.05756300866353627</v>
+        <v>-0.1507707957219046</v>
       </c>
       <c r="Z32">
-        <v>0.02351480024839578</v>
+        <v>0.07382368848025959</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.04040850725181148</v>
+        <v>0.07447629694207003</v>
       </c>
       <c r="AC32">
-        <v>-0.04040850725181148</v>
+        <v>-0.07447629694207003</v>
       </c>
       <c r="AD32">
-        <v>813.2</v>
+        <v>35.3</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>813.2</v>
+        <v>35.3</v>
       </c>
       <c r="AG32">
-        <v>691</v>
+        <v>-7.5</v>
       </c>
       <c r="AH32">
-        <v>0.4868295019157088</v>
+        <v>0.4943977591036414</v>
       </c>
       <c r="AI32">
-        <v>0.2294452908978049</v>
+        <v>0.1016119746689695</v>
       </c>
       <c r="AJ32">
-        <v>0.446324764242346</v>
+        <v>-0.2622377622377622</v>
       </c>
       <c r="AK32">
-        <v>0.2019286966686148</v>
+        <v>-0.02462245567957978</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-1.37</v>
+        <v>-2.7</v>
       </c>
       <c r="AQ32">
         <v>-0</v>
@@ -4313,7 +4328,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>First Shanghai Investments Limited (SEHK:227)</t>
+          <t>Kingston Financial Group Limited (SEHK:1031)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4322,7 +4337,10 @@
         </is>
       </c>
       <c r="D33">
-        <v>0.066</v>
+        <v>-0.257</v>
+      </c>
+      <c r="E33">
+        <v>-0.515</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -4337,10 +4355,10 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>-10.5</v>
+        <v>5.62</v>
       </c>
       <c r="L33">
-        <v>-0.1682692307692308</v>
+        <v>0.06946847960444993</v>
       </c>
       <c r="M33">
         <v>-0</v>
@@ -4349,7 +4367,7 @@
         <v>-0</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P33">
         <v>-0</v>
@@ -4358,67 +4376,67 @@
         <v>-0</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S33">
         <v>0</v>
       </c>
       <c r="U33">
-        <v>25</v>
+        <v>46.9</v>
       </c>
       <c r="V33">
-        <v>0.5617977528089888</v>
+        <v>0.07389317787931306</v>
       </c>
       <c r="W33">
-        <v>-0.03191489361702127</v>
+        <v>0.00205785426583669</v>
       </c>
       <c r="X33">
-        <v>0.2058104255613145</v>
+        <v>0.1016119006543888</v>
       </c>
       <c r="Y33">
-        <v>-0.2377253191783358</v>
+        <v>-0.09955404638855213</v>
       </c>
       <c r="Z33">
-        <v>0.1823495032144944</v>
+        <v>0.04025877083851705</v>
       </c>
       <c r="AA33">
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0.04073398177014773</v>
+        <v>0.07484271027074306</v>
       </c>
       <c r="AC33">
-        <v>-0.04073398177014773</v>
+        <v>-0.07484271027074306</v>
       </c>
       <c r="AD33">
-        <v>433.5</v>
+        <v>745.4</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>433.5</v>
+        <v>745.4</v>
       </c>
       <c r="AG33">
-        <v>408.5</v>
+        <v>698.5</v>
       </c>
       <c r="AH33">
-        <v>0.9069037656903766</v>
+        <v>0.5401057894355482</v>
       </c>
       <c r="AI33">
-        <v>0.5591383980394686</v>
+        <v>0.2205912817022284</v>
       </c>
       <c r="AJ33">
-        <v>0.9017660044150111</v>
+        <v>0.5239273927392739</v>
       </c>
       <c r="AK33">
-        <v>0.5444488871118219</v>
+        <v>0.209621271232219</v>
       </c>
       <c r="AL33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-2.28</v>
+        <v>-0.859</v>
       </c>
       <c r="AQ33">
         <v>-0</v>
@@ -4441,16 +4459,16 @@
         </is>
       </c>
       <c r="D34">
-        <v>0.0959</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="E34">
-        <v>-0.108</v>
+        <v>0.0464</v>
       </c>
       <c r="F34">
         <v>2.214</v>
       </c>
       <c r="G34">
-        <v>0.02821509680896108</v>
+        <v>0.04668169571672073</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -4462,28 +4480,28 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>354</v>
+        <v>510.7</v>
       </c>
       <c r="L34">
-        <v>0.136263905462104</v>
+        <v>0.2808049705833837</v>
       </c>
       <c r="M34">
-        <v>548.9</v>
+        <v>488.6</v>
       </c>
       <c r="N34">
-        <v>0.05643577590195453</v>
+        <v>0.05492479597113245</v>
       </c>
       <c r="O34">
-        <v>1.550564971751412</v>
+        <v>0.956726062267476</v>
       </c>
       <c r="P34">
-        <v>548.9</v>
+        <v>488.6</v>
       </c>
       <c r="Q34">
-        <v>0.05643577590195453</v>
+        <v>0.05492479597113245</v>
       </c>
       <c r="R34">
-        <v>1.550564971751412</v>
+        <v>0.956726062267476</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -4492,55 +4510,55 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>3690.6</v>
+        <v>1768.8</v>
       </c>
       <c r="V34">
-        <v>0.3794532237998787</v>
+        <v>0.1988354054722453</v>
       </c>
       <c r="W34">
-        <v>0.0457879011291762</v>
+        <v>0.05712400170018567</v>
       </c>
       <c r="X34">
-        <v>0.0648736083170718</v>
+        <v>0.1098778416623229</v>
       </c>
       <c r="Y34">
-        <v>-0.0190857071878956</v>
+        <v>-0.05275383996213726</v>
       </c>
       <c r="Z34">
-        <v>0.1244747471359644</v>
+        <v>0.0856943613326988</v>
       </c>
       <c r="AA34">
         <v>0</v>
       </c>
       <c r="AB34">
-        <v>0.04165388689716291</v>
+        <v>0.07530552259430688</v>
       </c>
       <c r="AC34">
-        <v>-0.04165388689716291</v>
+        <v>-0.07530552259430688</v>
       </c>
       <c r="AD34">
-        <v>16120.2</v>
+        <v>13224.2</v>
       </c>
       <c r="AE34">
         <v>0</v>
       </c>
       <c r="AF34">
-        <v>16120.2</v>
+        <v>13224.2</v>
       </c>
       <c r="AG34">
-        <v>12429.6</v>
+        <v>11455.4</v>
       </c>
       <c r="AH34">
-        <v>0.6236946874407555</v>
+        <v>0.5978390596745028</v>
       </c>
       <c r="AI34">
-        <v>0.6404401978506585</v>
+        <v>0.5910626810169128</v>
       </c>
       <c r="AJ34">
-        <v>0.5610113875887469</v>
+        <v>0.5628857266401982</v>
       </c>
       <c r="AK34">
-        <v>0.578661911833854</v>
+        <v>0.555957835067557</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -4557,7 +4575,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>China Fortune Financial Group Limited (SEHK:290)</t>
+          <t>CASH Financial Services Group Limited (SEHK:510)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4566,7 +4584,7 @@
         </is>
       </c>
       <c r="D35">
-        <v>0.106</v>
+        <v>-0.129</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4581,10 +4599,10 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>-5.63</v>
+        <v>-8.85</v>
       </c>
       <c r="L35">
-        <v>-0.7117572692793932</v>
+        <v>-0.9932659932659932</v>
       </c>
       <c r="M35">
         <v>-0</v>
@@ -4608,55 +4626,55 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>25.7</v>
+        <v>38.5</v>
       </c>
       <c r="V35">
-        <v>0.9961240310077519</v>
+        <v>2.305389221556887</v>
       </c>
       <c r="W35">
-        <v>-0.1318501170960187</v>
+        <v>-0.1574733096085409</v>
       </c>
       <c r="X35">
-        <v>0.05388540649850886</v>
+        <v>0.1049216309206561</v>
       </c>
       <c r="Y35">
-        <v>-0.1857355235945276</v>
+        <v>-0.262394940529197</v>
       </c>
       <c r="Z35">
-        <v>0.1156686407837976</v>
+        <v>0.0648</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.04187827534861041</v>
+        <v>0.07683618249531021</v>
       </c>
       <c r="AC35">
-        <v>-0.04187827534861041</v>
+        <v>-0.07683618249531021</v>
       </c>
       <c r="AD35">
-        <v>26.5</v>
+        <v>21.7</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>26.5</v>
+        <v>21.7</v>
       </c>
       <c r="AG35">
-        <v>0.8000000000000007</v>
+        <v>-16.8</v>
       </c>
       <c r="AH35">
-        <v>0.5066921606118547</v>
+        <v>0.5651041666666666</v>
       </c>
       <c r="AI35">
-        <v>0.4134165366614665</v>
+        <v>0.3104434907010014</v>
       </c>
       <c r="AJ35">
-        <v>0.03007518796992484</v>
+        <v>167.9999999999976</v>
       </c>
       <c r="AK35">
-        <v>0.02083333333333335</v>
+        <v>-0.535031847133758</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -4673,7 +4691,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bright Smart Securities &amp; Commodities Group Limited (SEHK:1428)</t>
+          <t>Altus Holdings Limited (SEHK:8149)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4682,10 +4700,10 @@
         </is>
       </c>
       <c r="D36">
-        <v>0.159</v>
+        <v>-0.0296</v>
       </c>
       <c r="E36">
-        <v>0.215</v>
+        <v>-0.234</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4700,85 +4718,85 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>83.8</v>
+        <v>0.734</v>
       </c>
       <c r="L36">
-        <v>0.5244055068836044</v>
+        <v>0.1124042879019908</v>
       </c>
       <c r="M36">
-        <v>28.3</v>
+        <v>0.061</v>
       </c>
       <c r="N36">
-        <v>0.09090909090909091</v>
+        <v>0.004236111111111111</v>
       </c>
       <c r="O36">
-        <v>0.337708830548926</v>
+        <v>0.08310626702997276</v>
       </c>
       <c r="P36">
-        <v>28.3</v>
+        <v>0.033</v>
       </c>
       <c r="Q36">
-        <v>0.09090909090909091</v>
+        <v>0.002291666666666667</v>
       </c>
       <c r="R36">
-        <v>0.337708830548926</v>
+        <v>0.0449591280653951</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>0.4590163934426229</v>
       </c>
       <c r="U36">
-        <v>81</v>
+        <v>4.34</v>
       </c>
       <c r="V36">
-        <v>0.2601991647928044</v>
+        <v>0.3013888888888889</v>
       </c>
       <c r="W36">
-        <v>0.3662587412587412</v>
+        <v>0.01267702936096718</v>
       </c>
       <c r="X36">
-        <v>0.09107435922044979</v>
+        <v>0.1069235148304242</v>
       </c>
       <c r="Y36">
-        <v>0.2751843820382914</v>
+        <v>-0.09424648546945702</v>
       </c>
       <c r="Z36">
-        <v>0.04686079587108882</v>
+        <v>0.08343981599795552</v>
       </c>
       <c r="AA36">
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>0.04289082772578766</v>
+        <v>0.07699107945781261</v>
       </c>
       <c r="AC36">
-        <v>-0.04289082772578766</v>
+        <v>-0.07699107945781261</v>
       </c>
       <c r="AD36">
-        <v>983.8</v>
+        <v>19.8</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>983.8</v>
+        <v>19.8</v>
       </c>
       <c r="AG36">
-        <v>902.8</v>
+        <v>15.46</v>
       </c>
       <c r="AH36">
-        <v>0.7596324608138368</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="AI36">
-        <v>0.7764798737174428</v>
+        <v>0.2861271676300578</v>
       </c>
       <c r="AJ36">
-        <v>0.7435960794003789</v>
+        <v>0.5177494976557268</v>
       </c>
       <c r="AK36">
-        <v>0.7612141652613827</v>
+        <v>0.2383595436324391</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -4795,7 +4813,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Southwest Securities International Securities Limited (SEHK:812)</t>
+          <t>Huarong International Financial Holdings Limited (SEHK:993)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4803,95 +4821,83 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G37">
-        <v>0</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
       <c r="K37">
-        <v>-0.775</v>
-      </c>
-      <c r="L37">
-        <v>-0.04329608938547486</v>
+        <v>-341</v>
       </c>
       <c r="M37">
-        <v>-0</v>
+        <v>14.2</v>
       </c>
       <c r="N37">
-        <v>-0</v>
+        <v>0.1059701492537313</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>-0.04164222873900293</v>
       </c>
       <c r="P37">
-        <v>-0</v>
+        <v>14.2</v>
       </c>
       <c r="Q37">
-        <v>-0</v>
+        <v>0.1059701492537313</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>-0.04164222873900293</v>
       </c>
       <c r="S37">
         <v>0</v>
       </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
       <c r="U37">
-        <v>51</v>
+        <v>302.9</v>
       </c>
       <c r="V37">
-        <v>2.09016393442623</v>
+        <v>2.26044776119403</v>
       </c>
       <c r="W37">
-        <v>-0.02039473684210526</v>
+        <v>5.599343185550082</v>
       </c>
       <c r="X37">
-        <v>0.1669458460009359</v>
+        <v>0.291900723894596</v>
       </c>
       <c r="Y37">
-        <v>-0.1873405828430411</v>
+        <v>5.307442461655486</v>
       </c>
       <c r="Z37">
-        <v>0.1023441966838193</v>
+        <v>0</v>
       </c>
       <c r="AA37">
         <v>0</v>
       </c>
       <c r="AB37">
-        <v>0.04400904645342558</v>
+        <v>0.07767299013717192</v>
       </c>
       <c r="AC37">
-        <v>-0.04400904645342558</v>
+        <v>-0.07767299013717192</v>
       </c>
       <c r="AD37">
-        <v>183.3</v>
+        <v>1120.3</v>
       </c>
       <c r="AE37">
         <v>0</v>
       </c>
       <c r="AF37">
-        <v>183.3</v>
+        <v>1120.3</v>
       </c>
       <c r="AG37">
-        <v>132.3</v>
+        <v>817.4</v>
       </c>
       <c r="AH37">
-        <v>0.882522869523351</v>
+        <v>0.8931675037869728</v>
       </c>
       <c r="AI37">
-        <v>0.8312925170068027</v>
+        <v>1.279173327243663</v>
       </c>
       <c r="AJ37">
-        <v>0.8442884492661136</v>
+        <v>0.8591549295774648</v>
       </c>
       <c r="AK37">
-        <v>0.7805309734513275</v>
+        <v>1.426776051666958</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -4908,7 +4914,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CASH Financial Services Group Limited (SEHK:510)</t>
+          <t>Southwest Securities International Securities Limited (SEHK:812)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4916,35 +4922,17 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D38">
-        <v>-0.143</v>
-      </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
       <c r="K38">
-        <v>-3.87</v>
-      </c>
-      <c r="L38">
-        <v>-0.3120967741935484</v>
+        <v>-33.9</v>
       </c>
       <c r="M38">
-        <v>0.319</v>
+        <v>-0</v>
       </c>
       <c r="N38">
-        <v>0.03977556109725686</v>
+        <v>-0</v>
       </c>
       <c r="O38">
-        <v>-0.08242894056847545</v>
+        <v>0</v>
       </c>
       <c r="P38">
         <v>-0</v>
@@ -4956,61 +4944,58 @@
         <v>0</v>
       </c>
       <c r="S38">
-        <v>0.319</v>
-      </c>
-      <c r="T38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>31.3</v>
+        <v>23.2</v>
       </c>
       <c r="V38">
-        <v>3.902743142144639</v>
+        <v>1.705882352941176</v>
       </c>
       <c r="W38">
-        <v>-0.06417910447761195</v>
+        <v>-0.911290322580645</v>
       </c>
       <c r="X38">
-        <v>0.2807462046190404</v>
+        <v>0.309615135134122</v>
       </c>
       <c r="Y38">
-        <v>-0.3449253090966523</v>
+        <v>-1.220905457714767</v>
       </c>
       <c r="Z38">
-        <v>0.2339622641509434</v>
+        <v>0</v>
       </c>
       <c r="AA38">
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>0.04447299628813037</v>
+        <v>0.07773011292830197</v>
       </c>
       <c r="AC38">
-        <v>-0.04447299628813037</v>
+        <v>-0.07773011292830197</v>
       </c>
       <c r="AD38">
-        <v>112.6</v>
+        <v>122.8</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>112.6</v>
+        <v>122.8</v>
       </c>
       <c r="AG38">
-        <v>81.3</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AH38">
-        <v>0.9335101973138783</v>
+        <v>0.9002932551319648</v>
       </c>
       <c r="AI38">
-        <v>0.6627427898763979</v>
+        <v>0.9815362481016705</v>
       </c>
       <c r="AJ38">
-        <v>0.9102104791759964</v>
+        <v>0.8798586572438163</v>
       </c>
       <c r="AK38">
-        <v>0.5865800865800865</v>
+        <v>0.9773329408301442</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -5027,7 +5012,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>China Industrial Securities International Financial Group Limited (SEHK:6058)</t>
+          <t>BOCOM International Holdings Company Limited (SEHK:3329)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5035,95 +5020,83 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
       <c r="K39">
-        <v>-19.7</v>
-      </c>
-      <c r="L39">
-        <v>-0.6655405405405405</v>
+        <v>-250.6</v>
       </c>
       <c r="M39">
-        <v>-0</v>
+        <v>55.8</v>
       </c>
       <c r="N39">
-        <v>-0</v>
+        <v>0.2841140529531568</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>-0.2226656025538707</v>
       </c>
       <c r="P39">
-        <v>-0</v>
+        <v>55.8</v>
       </c>
       <c r="Q39">
-        <v>-0</v>
+        <v>0.2841140529531568</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>-0.2226656025538707</v>
       </c>
       <c r="S39">
         <v>0</v>
       </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
       <c r="U39">
-        <v>534.9</v>
+        <v>236.1</v>
       </c>
       <c r="V39">
-        <v>5.486153846153845</v>
+        <v>1.20213849287169</v>
       </c>
       <c r="W39">
-        <v>-0.04296619411123228</v>
+        <v>-0.2584570957095709</v>
       </c>
       <c r="X39">
-        <v>0.2970372846230444</v>
+        <v>0.4706982083914353</v>
       </c>
       <c r="Y39">
-        <v>-0.3400034787342766</v>
+        <v>-0.7291553041010063</v>
       </c>
       <c r="Z39">
-        <v>0.01626909970319886</v>
+        <v>0</v>
       </c>
       <c r="AA39">
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0.04450838791289087</v>
+        <v>0.07803187566610663</v>
       </c>
       <c r="AC39">
-        <v>-0.04450838791289087</v>
+        <v>-0.07803187566610663</v>
       </c>
       <c r="AD39">
-        <v>1460</v>
+        <v>2968.1</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>1460</v>
+        <v>2968.1</v>
       </c>
       <c r="AG39">
-        <v>925.1</v>
+        <v>2732</v>
       </c>
       <c r="AH39">
-        <v>0.9373996789727127</v>
+        <v>0.9379364828566914</v>
       </c>
       <c r="AI39">
-        <v>0.7203828884393348</v>
+        <v>0.8347911686120095</v>
       </c>
       <c r="AJ39">
-        <v>0.9046548014864072</v>
+        <v>0.9329326594727496</v>
       </c>
       <c r="AK39">
-        <v>0.6201233409304195</v>
+        <v>0.8230403084894861</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -5149,10 +5122,13 @@
         </is>
       </c>
       <c r="D40">
-        <v>0.18</v>
+        <v>-0.0476</v>
       </c>
       <c r="E40">
-        <v>0.147</v>
+        <v>-0.234</v>
+      </c>
+      <c r="F40">
+        <v>-0.0287</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5167,85 +5143,85 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>244</v>
+        <v>40.6</v>
       </c>
       <c r="L40">
-        <v>0.4242740392975135</v>
+        <v>0.1589041095890411</v>
       </c>
       <c r="M40">
-        <v>105</v>
+        <v>79.91000000000001</v>
       </c>
       <c r="N40">
-        <v>0.07895924199127689</v>
+        <v>0.09055983680870355</v>
       </c>
       <c r="O40">
-        <v>0.430327868852459</v>
+        <v>1.968226600985222</v>
       </c>
       <c r="P40">
-        <v>105</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="Q40">
-        <v>0.07895924199127689</v>
+        <v>0.08318223028105169</v>
       </c>
       <c r="R40">
-        <v>0.430327868852459</v>
+        <v>1.807881773399015</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>6.510000000000005</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>0.08146664998122893</v>
       </c>
       <c r="U40">
-        <v>664.6</v>
+        <v>632.2</v>
       </c>
       <c r="V40">
-        <v>0.4997744021657393</v>
+        <v>0.7164551223934724</v>
       </c>
       <c r="W40">
-        <v>0.1305930207664312</v>
+        <v>0.02027263194687172</v>
       </c>
       <c r="X40">
-        <v>0.1786655502759027</v>
+        <v>0.3202309005126272</v>
       </c>
       <c r="Y40">
-        <v>-0.04807252950947152</v>
+        <v>-0.2999582685657555</v>
       </c>
       <c r="Z40">
-        <v>0.05135463361491616</v>
+        <v>0.02090509658891007</v>
       </c>
       <c r="AA40">
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>0.04493261681297431</v>
+        <v>0.07919522893927161</v>
       </c>
       <c r="AC40">
-        <v>-0.04493261681297431</v>
+        <v>-0.07919522893927161</v>
       </c>
       <c r="AD40">
-        <v>10883.8</v>
+        <v>8321.299999999999</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>10883.8</v>
+        <v>8321.299999999999</v>
       </c>
       <c r="AG40">
-        <v>10219.2</v>
+        <v>7689.099999999999</v>
       </c>
       <c r="AH40">
-        <v>0.8911213728957883</v>
+        <v>0.9041255147386378</v>
       </c>
       <c r="AI40">
-        <v>0.8435223362370958</v>
+        <v>0.809063596853701</v>
       </c>
       <c r="AJ40">
-        <v>0.884855831673738</v>
+        <v>0.8970541912150731</v>
       </c>
       <c r="AK40">
-        <v>0.835024758542923</v>
+        <v>0.7965585471723523</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -5262,7 +5238,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Haitong International Securities Group Limited (SEHK:665)</t>
+          <t>CMBC Capital Holdings Limited (SEHK:1141)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5270,12 +5246,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D41">
-        <v>0.107</v>
-      </c>
-      <c r="E41">
-        <v>0.0554</v>
-      </c>
       <c r="G41">
         <v>0</v>
       </c>
@@ -5289,82 +5259,85 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>241.8</v>
+        <v>-24</v>
       </c>
       <c r="L41">
-        <v>0.3269776876267749</v>
+        <v>-0.4624277456647399</v>
       </c>
       <c r="M41">
-        <v>-0</v>
+        <v>36.4</v>
       </c>
       <c r="N41">
-        <v>-0</v>
+        <v>0.1173814898419864</v>
       </c>
       <c r="O41">
-        <v>-0</v>
+        <v>-1.516666666666667</v>
       </c>
       <c r="P41">
-        <v>-0</v>
+        <v>20</v>
       </c>
       <c r="Q41">
-        <v>-0</v>
+        <v>0.06449532408900355</v>
       </c>
       <c r="R41">
-        <v>-0</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>16.4</v>
+      </c>
+      <c r="T41">
+        <v>0.4505494505494505</v>
       </c>
       <c r="U41">
-        <v>776.2</v>
+        <v>113.5</v>
       </c>
       <c r="V41">
-        <v>0.596709717097171</v>
+        <v>0.3660109642050951</v>
       </c>
       <c r="W41">
-        <v>0.06901275794160459</v>
+        <v>-0.06806579693703914</v>
       </c>
       <c r="X41">
-        <v>0.1231391872204111</v>
+        <v>0.2065098841033461</v>
       </c>
       <c r="Y41">
-        <v>-0.0541264292788065</v>
+        <v>-0.2745756810403852</v>
       </c>
       <c r="Z41">
-        <v>0.05644478028897896</v>
+        <v>0.03166197939226081</v>
       </c>
       <c r="AA41">
         <v>0</v>
       </c>
       <c r="AB41">
-        <v>0.04568131699059408</v>
+        <v>0.07987876642566256</v>
       </c>
       <c r="AC41">
-        <v>-0.04568131699059408</v>
+        <v>-0.07987876642566256</v>
       </c>
       <c r="AD41">
-        <v>6503.4</v>
+        <v>1592.6</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>6503.4</v>
+        <v>1592.6</v>
       </c>
       <c r="AG41">
-        <v>5727.2</v>
+        <v>1479.1</v>
       </c>
       <c r="AH41">
-        <v>0.8333205197201506</v>
+        <v>0.8370210753140275</v>
       </c>
       <c r="AI41">
-        <v>0.6410954042704204</v>
+        <v>0.87337537702221</v>
       </c>
       <c r="AJ41">
-        <v>0.8149117814456459</v>
+        <v>0.8266823161189358</v>
       </c>
       <c r="AK41">
-        <v>0.6113578138343296</v>
+        <v>0.8649707602339181</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -5381,7 +5354,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shenwan Hongyuan (H.K.) Limited (SEHK:218)</t>
+          <t>Future World Holdings Limited (SEHK:572)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5390,115 +5363,115 @@
         </is>
       </c>
       <c r="D42">
-        <v>0.109</v>
-      </c>
-      <c r="E42">
-        <v>0.06660000000000001</v>
+        <v>-0.138</v>
       </c>
       <c r="G42">
-        <v>0.01253761283851555</v>
+        <v>-0.1479166666666667</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>-0.1479166666666667</v>
       </c>
       <c r="I42">
-        <v>0.0009793820557762562</v>
+        <v>-0.07572916666666667</v>
       </c>
       <c r="J42">
-        <v>0.000824061553538612</v>
+        <v>-0.07572916666666667</v>
       </c>
       <c r="K42">
-        <v>19.1</v>
+        <v>-2.18</v>
       </c>
       <c r="L42">
-        <v>0.1915747241725176</v>
+        <v>-0.2270833333333334</v>
       </c>
       <c r="M42">
-        <v>8.039999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N42">
-        <v>0.04317937701396348</v>
+        <v>-0</v>
       </c>
       <c r="O42">
-        <v>0.4209424083769633</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>8.039999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q42">
-        <v>0.04317937701396348</v>
+        <v>-0</v>
       </c>
       <c r="R42">
-        <v>0.4209424083769633</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
       </c>
-      <c r="T42">
-        <v>0</v>
-      </c>
       <c r="U42">
-        <v>67.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>0.3603651987110634</v>
+        <v>0</v>
       </c>
       <c r="W42">
-        <v>0.03766515480181424</v>
+        <v>-0.0185374149659864</v>
       </c>
       <c r="X42">
-        <v>0.1568552155662489</v>
+        <v>0.09642777777540625</v>
       </c>
       <c r="Y42">
-        <v>-0.1191900607644347</v>
+        <v>-0.1149651927413926</v>
       </c>
       <c r="Z42">
-        <v>0.1037550829352994</v>
+        <v>0.05510907003444317</v>
       </c>
       <c r="AA42">
-        <v>8.55005748311904e-05</v>
+        <v>-0.004173363949483352</v>
       </c>
       <c r="AB42">
-        <v>0.04615440444513712</v>
+        <v>0.07604731253362652</v>
       </c>
       <c r="AC42">
-        <v>-0.04606890387030593</v>
+        <v>-0.08022067648310988</v>
       </c>
       <c r="AD42">
-        <v>1290.9</v>
+        <v>50.4</v>
       </c>
       <c r="AE42">
-        <v>0.1167780451955362</v>
+        <v>0</v>
       </c>
       <c r="AF42">
-        <v>1291.016778045196</v>
+        <v>50.4</v>
       </c>
       <c r="AG42">
-        <v>1223.916778045196</v>
+        <v>50.4</v>
       </c>
       <c r="AH42">
-        <v>0.8739521492259255</v>
+        <v>0.4946025515210991</v>
       </c>
       <c r="AI42">
-        <v>0.7136566082268484</v>
+        <v>0.3025210084033613</v>
       </c>
       <c r="AJ42">
-        <v>0.8679541986174196</v>
+        <v>0.4946025515210991</v>
       </c>
       <c r="AK42">
-        <v>0.7026264362748104</v>
+        <v>0.3025210084033613</v>
       </c>
       <c r="AL42">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM42">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN42">
-        <v>10668.59504132231</v>
+        <v>-76.24810892586989</v>
+      </c>
+      <c r="AO42">
+        <v>-0.3806282722513089</v>
       </c>
       <c r="AP42">
-        <v>10115.0146945884</v>
+        <v>-76.24810892586989</v>
+      </c>
+      <c r="AQ42">
+        <v>-0.3806282722513089</v>
       </c>
     </row>
     <row r="43">
@@ -5509,7 +5482,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Huarong International Financial Holdings Limited (SEHK:993)</t>
+          <t>Shenwan Hongyuan (H.K.) Limited (SEHK:218)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5517,104 +5490,110 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D43">
+        <v>0.0127</v>
+      </c>
       <c r="G43">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I43">
-        <v>-0</v>
+        <v>0.001377614573142752</v>
       </c>
       <c r="J43">
-        <v>-0</v>
+        <v>0.001377614573142752</v>
       </c>
       <c r="K43">
-        <v>-320.5</v>
+        <v>-34.8</v>
       </c>
       <c r="L43">
-        <v>1.793508673754897</v>
+        <v>-0.5515055467511886</v>
       </c>
       <c r="M43">
-        <v>20.4</v>
+        <v>-0</v>
       </c>
       <c r="N43">
-        <v>0.09319323892188212</v>
+        <v>-0</v>
       </c>
       <c r="O43">
-        <v>-0.06365054602184086</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>20.4</v>
+        <v>-0</v>
       </c>
       <c r="Q43">
-        <v>0.09319323892188212</v>
+        <v>-0</v>
       </c>
       <c r="R43">
-        <v>-0.06365054602184086</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
       </c>
-      <c r="T43">
-        <v>0</v>
-      </c>
       <c r="U43">
-        <v>237.1</v>
+        <v>72.8</v>
       </c>
       <c r="V43">
-        <v>1.083142987665601</v>
+        <v>0.6993275696445725</v>
       </c>
       <c r="W43">
-        <v>-1.06301824212272</v>
+        <v>-0.06722039791384971</v>
       </c>
       <c r="X43">
-        <v>0.1529892120104693</v>
+        <v>0.2668137575435922</v>
       </c>
       <c r="Y43">
-        <v>-1.216007454133189</v>
+        <v>-0.3340341554574419</v>
       </c>
       <c r="Z43">
-        <v>-0.1207677231871325</v>
+        <v>0.03623104436296771</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>4.991241471460587e-05</v>
       </c>
       <c r="AB43">
-        <v>0.04611220247514051</v>
+        <v>0.08037239994861858</v>
       </c>
       <c r="AC43">
-        <v>-0.04611220247514051</v>
+        <v>-0.08032248753390397</v>
       </c>
       <c r="AD43">
-        <v>1469.2</v>
+        <v>771.6</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>0.1003626021734617</v>
       </c>
       <c r="AF43">
-        <v>1469.2</v>
+        <v>771.7003626021735</v>
       </c>
       <c r="AG43">
-        <v>1232.1</v>
+        <v>698.9003626021736</v>
       </c>
       <c r="AH43">
-        <v>0.8703275872282448</v>
+        <v>0.8811372951585694</v>
       </c>
       <c r="AI43">
-        <v>0.9340708245915188</v>
+        <v>0.6210366468798774</v>
       </c>
       <c r="AJ43">
-        <v>0.8491385251550654</v>
+        <v>0.8703612042432243</v>
       </c>
       <c r="AK43">
-        <v>0.9223686180565953</v>
+        <v>0.5974526807698178</v>
       </c>
       <c r="AL43">
         <v>0</v>
       </c>
       <c r="AM43">
         <v>0</v>
+      </c>
+      <c r="AN43">
+        <v>7211.214953271028</v>
+      </c>
+      <c r="AP43">
+        <v>6531.77908973994</v>
       </c>
     </row>
     <row r="44">
@@ -5625,7 +5604,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>South China Financial Holdings Limited (SEHK:619)</t>
+          <t>Haitong International Securities Group Limited (SEHK:665)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5633,26 +5612,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D44">
-        <v>0.0209</v>
-      </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
       <c r="K44">
-        <v>-12</v>
-      </c>
-      <c r="L44">
-        <v>-0.8219178082191781</v>
+        <v>-426.4</v>
       </c>
       <c r="M44">
         <v>-0</v>
@@ -5676,55 +5637,55 @@
         <v>0</v>
       </c>
       <c r="U44">
-        <v>12.3</v>
+        <v>977.7</v>
       </c>
       <c r="V44">
-        <v>1.098214285714286</v>
+        <v>1.319433198380567</v>
       </c>
       <c r="W44">
-        <v>-0.1428571428571428</v>
+        <v>-0.1171171171171171</v>
       </c>
       <c r="X44">
-        <v>0.1782501966822085</v>
+        <v>0.3342195714788768</v>
       </c>
       <c r="Y44">
-        <v>-0.3211073395393513</v>
+        <v>-0.4513366885959939</v>
       </c>
       <c r="Z44">
-        <v>0.1114503816793893</v>
+        <v>0</v>
       </c>
       <c r="AA44">
         <v>0</v>
       </c>
       <c r="AB44">
-        <v>0.04635101437711951</v>
+        <v>0.08068133805442507</v>
       </c>
       <c r="AC44">
-        <v>-0.04635101437711951</v>
+        <v>-0.08068133805442507</v>
       </c>
       <c r="AD44">
-        <v>91.40000000000001</v>
+        <v>7379.3</v>
       </c>
       <c r="AE44">
         <v>0</v>
       </c>
       <c r="AF44">
-        <v>91.40000000000001</v>
+        <v>7379.3</v>
       </c>
       <c r="AG44">
-        <v>79.10000000000001</v>
+        <v>6401.6</v>
       </c>
       <c r="AH44">
-        <v>0.8908382066276803</v>
+        <v>0.9087472137728901</v>
       </c>
       <c r="AI44">
-        <v>0.5542753183747726</v>
+        <v>0.6998245530845465</v>
       </c>
       <c r="AJ44">
-        <v>0.875968992248062</v>
+        <v>0.8962562652255481</v>
       </c>
       <c r="AK44">
-        <v>0.518348623853211</v>
+        <v>0.6691474683279677</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -5741,7 +5702,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Arta TechFin Corporation Limited (SEHK:279)</t>
+          <t>China Industrial Securities International Financial Group Limited (SEHK:6058)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5750,25 +5711,25 @@
         </is>
       </c>
       <c r="D45">
-        <v>-0.19</v>
+        <v>-0.265</v>
       </c>
       <c r="G45">
-        <v>-0.9358974358974358</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>-0.9358974358974358</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>-0.5961538461538461</v>
+        <v>0</v>
       </c>
       <c r="J45">
-        <v>-0.5961538461538461</v>
+        <v>0</v>
       </c>
       <c r="K45">
-        <v>-91.90000000000001</v>
+        <v>-27</v>
       </c>
       <c r="L45">
-        <v>-14.7275641025641</v>
+        <v>-2.014925373134328</v>
       </c>
       <c r="M45">
         <v>-0</v>
@@ -5792,73 +5753,61 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>56.2</v>
+        <v>570.8</v>
       </c>
       <c r="V45">
-        <v>0.1002497324295398</v>
+        <v>11.23622047244094</v>
       </c>
       <c r="W45">
-        <v>0.2799268961315869</v>
+        <v>-0.04764425622022234</v>
       </c>
       <c r="X45">
-        <v>0.04772762955066239</v>
+        <v>0.6136211362537316</v>
       </c>
       <c r="Y45">
-        <v>0.2321992665809245</v>
+        <v>-0.661265392473954</v>
       </c>
       <c r="Z45">
-        <v>0.1313518292426221</v>
+        <v>0.008982437324038074</v>
       </c>
       <c r="AA45">
-        <v>-0.07830589820233239</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>0.04255407255477777</v>
+        <v>0.0811822023992976</v>
       </c>
       <c r="AC45">
-        <v>-0.1208599707571102</v>
+        <v>-0.0811822023992976</v>
       </c>
       <c r="AD45">
-        <v>377.8</v>
+        <v>1041.9</v>
       </c>
       <c r="AE45">
         <v>0</v>
       </c>
       <c r="AF45">
-        <v>377.8</v>
+        <v>1041.9</v>
       </c>
       <c r="AG45">
-        <v>321.6</v>
+        <v>471.1000000000001</v>
       </c>
       <c r="AH45">
-        <v>0.4026001705029838</v>
+        <v>0.9535096549830695</v>
       </c>
       <c r="AI45">
-        <v>-7.838174273858924</v>
+        <v>0.6616498380643933</v>
       </c>
       <c r="AJ45">
-        <v>0.3645431874858309</v>
+        <v>0.9026633454684807</v>
       </c>
       <c r="AK45">
-        <v>-3.080459770114943</v>
+        <v>0.469269847594382</v>
       </c>
       <c r="AL45">
-        <v>83.2</v>
+        <v>0</v>
       </c>
       <c r="AM45">
-        <v>83.18000000000001</v>
-      </c>
-      <c r="AN45">
-        <v>-95.16372795969774</v>
-      </c>
-      <c r="AO45">
-        <v>-0.04471153846153846</v>
-      </c>
-      <c r="AP45">
-        <v>-81.00755667506297</v>
-      </c>
-      <c r="AQ45">
-        <v>-0.04472228901178168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5869,7 +5818,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Amasse Capital Holdings Limited (SEHK:8168)</t>
+          <t>South China Financial Holdings Limited (SEHK:619)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5878,25 +5827,25 @@
         </is>
       </c>
       <c r="D46">
-        <v>-0.263</v>
+        <v>-0.194</v>
       </c>
       <c r="G46">
-        <v>-1.897356143079316</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>-1.897356143079316</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>-1.959564541213064</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>-1.959564541213064</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>-1.21</v>
+        <v>-19.8</v>
       </c>
       <c r="L46">
-        <v>-1.881804043545878</v>
+        <v>-3.267326732673268</v>
       </c>
       <c r="M46">
         <v>-0</v>
@@ -5920,73 +5869,61 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>2.43</v>
+        <v>4.15</v>
       </c>
       <c r="V46">
-        <v>0.18</v>
+        <v>0.2862068965517242</v>
       </c>
       <c r="W46">
-        <v>-0.2068376068376069</v>
+        <v>-0.2704918032786885</v>
       </c>
       <c r="X46">
-        <v>0.03765749297150167</v>
+        <v>0.1810000541927979</v>
       </c>
       <c r="Y46">
-        <v>-0.2444950998091085</v>
+        <v>-0.4514918574714864</v>
       </c>
       <c r="Z46">
-        <v>0.2165712361064332</v>
+        <v>0.04135954135954135</v>
       </c>
       <c r="AA46">
-        <v>-0.4243853149208488</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>0.0370014164139387</v>
+        <v>0.08715042248797764</v>
       </c>
       <c r="AC46">
-        <v>-0.4613867313347875</v>
+        <v>-0.08715042248797764</v>
       </c>
       <c r="AD46">
-        <v>1.3</v>
+        <v>60.5</v>
       </c>
       <c r="AE46">
         <v>0</v>
       </c>
       <c r="AF46">
-        <v>1.3</v>
+        <v>60.5</v>
       </c>
       <c r="AG46">
-        <v>-1.13</v>
+        <v>56.35</v>
       </c>
       <c r="AH46">
-        <v>0.08783783783783784</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="AI46">
-        <v>0.2407407407407408</v>
+        <v>0.5373001776198935</v>
       </c>
       <c r="AJ46">
-        <v>-0.09135004042037188</v>
+        <v>0.7953422724064927</v>
       </c>
       <c r="AK46">
-        <v>-0.3804713804713805</v>
+        <v>0.5195942830797603</v>
       </c>
       <c r="AL46">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="AM46">
-        <v>0.018</v>
-      </c>
-      <c r="AN46">
-        <v>-1.065573770491803</v>
-      </c>
-      <c r="AO46">
-        <v>-70</v>
-      </c>
-      <c r="AP46">
-        <v>0.9262295081967215</v>
-      </c>
-      <c r="AQ46">
-        <v>-70</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -5997,7 +5934,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Unitas Holdings Limited (SEHK:8020)</t>
+          <t>Glory Sun Financial Group Limited (SEHK:1282)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6006,25 +5943,25 @@
         </is>
       </c>
       <c r="D47">
-        <v>-0.514</v>
+        <v>0.146</v>
       </c>
       <c r="G47">
-        <v>-0.7116504854368931</v>
+        <v>-0.1518987341772152</v>
       </c>
       <c r="H47">
-        <v>-0.7116504854368931</v>
+        <v>-0.1518987341772152</v>
       </c>
       <c r="I47">
-        <v>-0.8388349514563106</v>
+        <v>-0.2634493670886076</v>
       </c>
       <c r="J47">
-        <v>-0.8388349514563106</v>
+        <v>-0.2634493670886076</v>
       </c>
       <c r="K47">
-        <v>-0.956</v>
+        <v>-75.5</v>
       </c>
       <c r="L47">
-        <v>-0.9281553398058252</v>
+        <v>-0.2986550632911392</v>
       </c>
       <c r="M47">
         <v>-0</v>
@@ -6048,73 +5985,201 @@
         <v>0</v>
       </c>
       <c r="U47">
-        <v>2.41</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="V47">
-        <v>0.1596026490066225</v>
+        <v>0.7831050228310502</v>
       </c>
       <c r="W47">
-        <v>-0.390204081632653</v>
+        <v>-0.07224189072815999</v>
       </c>
       <c r="X47">
-        <v>0.03656751209820538</v>
+        <v>0.1342956276754229</v>
       </c>
       <c r="Y47">
-        <v>-0.4267715937308584</v>
+        <v>-0.2065375184035829</v>
       </c>
       <c r="Z47">
-        <v>1.969407265774378</v>
+        <v>0.09334613396351819</v>
       </c>
       <c r="AA47">
-        <v>-1.652007648183556</v>
+        <v>-0.02459197991285724</v>
       </c>
       <c r="AB47">
-        <v>0.03651228957846654</v>
+        <v>0.07841978059448705</v>
       </c>
       <c r="AC47">
-        <v>-1.688519937762023</v>
+        <v>-0.1030117605073443</v>
       </c>
       <c r="AD47">
-        <v>0.51</v>
+        <v>211</v>
       </c>
       <c r="AE47">
         <v>0</v>
       </c>
       <c r="AF47">
-        <v>0.51</v>
+        <v>211</v>
       </c>
       <c r="AG47">
-        <v>-1.9</v>
+        <v>142.4</v>
       </c>
       <c r="AH47">
-        <v>0.03267136450992954</v>
+        <v>0.7066309444072337</v>
       </c>
       <c r="AI47">
-        <v>0.255</v>
+        <v>0.2285281057077873</v>
       </c>
       <c r="AJ47">
-        <v>-0.143939393939394</v>
+        <v>0.6191304347826088</v>
       </c>
       <c r="AK47">
-        <v>4.634146341463413</v>
+        <v>0.1666081666081666</v>
       </c>
       <c r="AL47">
-        <v>0.039</v>
+        <v>13</v>
       </c>
       <c r="AM47">
-        <v>0.039</v>
+        <v>0.5999999999999996</v>
       </c>
       <c r="AN47">
-        <v>-0.686406460296097</v>
+        <v>-3.386837881219904</v>
       </c>
       <c r="AO47">
-        <v>-22.15384615384615</v>
+        <v>-5.123076923076923</v>
       </c>
       <c r="AP47">
-        <v>2.557200538358008</v>
+        <v>-2.285714285714286</v>
       </c>
       <c r="AQ47">
-        <v>-22.15384615384615</v>
+        <v>-111.0000000000001</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Amasse Capital Holdings Limited (SEHK:8168)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>-0.276</v>
+      </c>
+      <c r="G48">
+        <v>-1.476650563607085</v>
+      </c>
+      <c r="H48">
+        <v>-1.476650563607085</v>
+      </c>
+      <c r="I48">
+        <v>-1.508856682769726</v>
+      </c>
+      <c r="J48">
+        <v>-1.508856682769726</v>
+      </c>
+      <c r="K48">
+        <v>-1.18</v>
+      </c>
+      <c r="L48">
+        <v>-1.900161030595813</v>
+      </c>
+      <c r="M48">
+        <v>-0</v>
+      </c>
+      <c r="N48">
+        <v>-0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>-0</v>
+      </c>
+      <c r="Q48">
+        <v>-0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>2.23</v>
+      </c>
+      <c r="V48">
+        <v>0.0832089552238806</v>
+      </c>
+      <c r="W48">
+        <v>-0.2878048780487805</v>
+      </c>
+      <c r="X48">
+        <v>0.07187655363440812</v>
+      </c>
+      <c r="Y48">
+        <v>-0.3596814316831887</v>
+      </c>
+      <c r="Z48">
+        <v>0.2090909090909091</v>
+      </c>
+      <c r="AA48">
+        <v>-0.3154882154882156</v>
+      </c>
+      <c r="AB48">
+        <v>0.07152303181198619</v>
+      </c>
+      <c r="AC48">
+        <v>-0.3870112473002018</v>
+      </c>
+      <c r="AD48">
+        <v>1.38</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>1.38</v>
+      </c>
+      <c r="AG48">
+        <v>-0.8500000000000001</v>
+      </c>
+      <c r="AH48">
+        <v>0.04897090134847409</v>
+      </c>
+      <c r="AI48">
+        <v>0.323943661971831</v>
+      </c>
+      <c r="AJ48">
+        <v>-0.03275529865125242</v>
+      </c>
+      <c r="AK48">
+        <v>-0.4187192118226602</v>
+      </c>
+      <c r="AL48">
+        <v>0.015</v>
+      </c>
+      <c r="AM48">
+        <v>0.015</v>
+      </c>
+      <c r="AN48">
+        <v>-1.504907306434024</v>
+      </c>
+      <c r="AO48">
+        <v>-62.46666666666668</v>
+      </c>
+      <c r="AP48">
+        <v>0.9269356597600873</v>
+      </c>
+      <c r="AQ48">
+        <v>-62.46666666666668</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ48"/>
+  <dimension ref="A1:AQ45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.08105000000000001</v>
+        <v>-0.103</v>
       </c>
       <c r="E2">
-        <v>-0.234</v>
-      </c>
-      <c r="F2">
-        <v>1.09265</v>
+        <v>-0.0963</v>
       </c>
       <c r="G2">
-        <v>0.04294082379021653</v>
+        <v>0.00559369916819</v>
       </c>
       <c r="H2">
-        <v>0.0164090280778953</v>
+        <v>0.004046488363583078</v>
       </c>
       <c r="I2">
-        <v>0.003093664527632569</v>
+        <v>0.002461030044438727</v>
       </c>
       <c r="J2">
-        <v>0.002848913458053613</v>
+        <v>0.002359779768600349</v>
       </c>
       <c r="K2">
-        <v>-844.64</v>
+        <v>-967.836</v>
       </c>
       <c r="L2">
-        <v>-0.2515695546750674</v>
+        <v>-0.2640998794157928</v>
       </c>
       <c r="M2">
-        <v>743.5690000000001</v>
+        <v>1721.04</v>
       </c>
       <c r="N2">
-        <v>0.05210554124469884</v>
+        <v>0.08870027990704468</v>
       </c>
       <c r="O2">
-        <v>-0.8803383690092822</v>
+        <v>-1.778235155542881</v>
       </c>
       <c r="P2">
-        <v>720.4920000000001</v>
+        <v>1500.507</v>
       </c>
       <c r="Q2">
-        <v>0.05048842222103875</v>
+        <v>0.0773342809594663</v>
       </c>
       <c r="R2">
-        <v>-0.8530166698238304</v>
+        <v>-1.550373203724598</v>
       </c>
       <c r="S2">
-        <v>23.07700000000001</v>
+        <v>220.533</v>
       </c>
       <c r="T2">
-        <v>0.03103545198898825</v>
+        <v>0.1281393808394924</v>
       </c>
       <c r="U2">
-        <v>6217.263</v>
+        <v>8710.284</v>
       </c>
       <c r="V2">
-        <v>0.4356742328898058</v>
+        <v>0.4489172993479831</v>
       </c>
       <c r="W2">
-        <v>-0.05100424831548719</v>
+        <v>-0.06703767123287671</v>
       </c>
       <c r="X2">
-        <v>0.08176606821095345</v>
+        <v>0.07227326435332249</v>
       </c>
       <c r="Y2">
-        <v>-0.1327703165264406</v>
+        <v>-0.1393109355861992</v>
       </c>
       <c r="Z2">
-        <v>0.05171635707578631</v>
+        <v>0.04127759531556581</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07261274276349294</v>
+        <v>0.06121638840460252</v>
       </c>
       <c r="AC2">
-        <v>-0.07171333957764961</v>
+        <v>-0.06056501990069586</v>
       </c>
       <c r="AD2">
-        <v>39434.269</v>
+        <v>66977.493</v>
       </c>
       <c r="AE2">
-        <v>1.755400640498401</v>
+        <v>1.065820491886099</v>
       </c>
       <c r="AF2">
-        <v>39436.0244006405</v>
+        <v>66978.55882049189</v>
       </c>
       <c r="AG2">
-        <v>33218.7614006405</v>
+        <v>58268.27482049189</v>
       </c>
       <c r="AH2">
-        <v>0.7342882247182554</v>
+        <v>0.775381464917409</v>
       </c>
       <c r="AI2">
-        <v>0.6086778015017571</v>
+        <v>0.6983162859467718</v>
       </c>
       <c r="AJ2">
-        <v>0.6995013691721603</v>
+        <v>0.7501920430702734</v>
       </c>
       <c r="AK2">
-        <v>0.5671402619268375</v>
+        <v>0.6681829368689037</v>
       </c>
       <c r="AL2">
-        <v>67.636</v>
+        <v>74.273</v>
       </c>
       <c r="AM2">
-        <v>50.212</v>
+        <v>49.886</v>
       </c>
       <c r="AN2">
-        <v>1723.977835096616</v>
+        <v>3303.941051696922</v>
       </c>
       <c r="AO2">
-        <v>0.1436513099532794</v>
+        <v>0.1136213698113716</v>
       </c>
       <c r="AP2">
-        <v>1452.249777067434</v>
+        <v>2874.322948919292</v>
       </c>
       <c r="AQ2">
-        <v>0.1934995618577234</v>
+        <v>0.1691656977909634</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Da Yu Financial Holdings Limited (SEHK:1073)</t>
+          <t>Hatcher Group Limited (SEHK:8365)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,23 +721,26 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0418</v>
+      </c>
       <c r="G3">
-        <v>0.3314285714285714</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.3314285714285714</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.4342857142857143</v>
+        <v>0.0003944807992182816</v>
       </c>
       <c r="J3">
-        <v>0.3443417366946779</v>
+        <v>0.0003944807992182816</v>
       </c>
       <c r="K3">
-        <v>3.24</v>
+        <v>-2.98</v>
       </c>
       <c r="L3">
-        <v>0.3085714285714286</v>
+        <v>-0.2893203883495146</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +758,67 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.4182509505703422</v>
-      </c>
-      <c r="W3">
-        <v>0.05436241610738255</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.07079090523976678</v>
-      </c>
-      <c r="Y3">
-        <v>-0.01642848913238423</v>
+        <v>0.07903043684738947</v>
       </c>
       <c r="Z3">
-        <v>1.552106430155211</v>
+        <v>2198.863113357302</v>
       </c>
       <c r="AA3">
-        <v>0.5344550236946219</v>
+        <v>0.8674092783287874</v>
       </c>
       <c r="AB3">
-        <v>0.07062921770085014</v>
+        <v>0.06724855456666079</v>
       </c>
       <c r="AC3">
-        <v>0.4638258059937718</v>
+        <v>0.8001607237621267</v>
       </c>
       <c r="AD3">
-        <v>0.276</v>
+        <v>4.66</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.004684238840258498</v>
       </c>
       <c r="AF3">
-        <v>0.276</v>
+        <v>4.664684238840259</v>
       </c>
       <c r="AG3">
-        <v>-10.724</v>
+        <v>4.664684238840259</v>
       </c>
       <c r="AH3">
-        <v>0.01038531005418423</v>
+        <v>0.5180286298901957</v>
       </c>
       <c r="AI3">
-        <v>0.004417696395415839</v>
+        <v>0.1782816943732022</v>
       </c>
       <c r="AJ3">
-        <v>-0.6884951206985105</v>
+        <v>0.5180286298901957</v>
       </c>
       <c r="AK3">
-        <v>-0.208330095578522</v>
+        <v>0.1782816943732022</v>
       </c>
       <c r="AL3">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.006999999999999999</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.04775086505190312</v>
-      </c>
-      <c r="AO3">
-        <v>268.235294117647</v>
+        <v>932</v>
       </c>
       <c r="AP3">
-        <v>-1.855363321799308</v>
-      </c>
-      <c r="AQ3">
-        <v>-651.4285714285714</v>
+        <v>932.9368477680517</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>eBullion, Inc. (OTCPK:EBML)</t>
+          <t>Garden Stage Limited (NasdaqCM:GSIW)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.3379273951899556</v>
+        <v>0.0174212052456537</v>
       </c>
       <c r="J4">
-        <v>0.3379273951899556</v>
+        <v>0.0174212052456537</v>
       </c>
       <c r="K4">
-        <v>-0.665</v>
+        <v>-0.207</v>
       </c>
       <c r="L4">
-        <v>-0.6333333333333333</v>
+        <v>-0.06349693251533742</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,70 +877,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>0.41015625</v>
-      </c>
-      <c r="W4">
-        <v>-0.2782426778242678</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>0.07802144944121166</v>
-      </c>
-      <c r="Y4">
-        <v>-0.3562641272654794</v>
+        <v>0.0600117585623989</v>
       </c>
       <c r="Z4">
-        <v>0.4691938122592319</v>
+        <v>49.36824210502638</v>
       </c>
       <c r="AA4">
-        <v>0.1585534428160073</v>
+        <v>0.8600542783287874</v>
       </c>
       <c r="AB4">
-        <v>0.07298485059073122</v>
+        <v>0.060006416716644</v>
       </c>
       <c r="AC4">
-        <v>0.08556859222527609</v>
+        <v>0.8000478616121435</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>0.7258811752527329</v>
+        <v>0.06603435449584473</v>
       </c>
       <c r="AF4">
-        <v>0.7258811752527329</v>
+        <v>0.06603435449584473</v>
       </c>
       <c r="AG4">
-        <v>-0.3241188247472672</v>
+        <v>0.06603435449584473</v>
       </c>
       <c r="AH4">
-        <v>0.2209091371652847</v>
+        <v>0.0005414159347340509</v>
       </c>
       <c r="AI4">
-        <v>0.3081145105609421</v>
+        <v>1</v>
       </c>
       <c r="AJ4">
-        <v>-0.1449624552210966</v>
+        <v>0.0005414159347340509</v>
       </c>
       <c r="AK4">
-        <v>-0.2481993238661543</v>
+        <v>1</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.048</v>
+        <v>0</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.6482376494945343</v>
-      </c>
-      <c r="AQ4">
-        <v>-0</v>
+        <v>0.9433479213692103</v>
       </c>
     </row>
     <row r="5">
@@ -978,16 +957,16 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.05835074596364428</v>
+        <v>0.1468469283297689</v>
       </c>
       <c r="J5">
-        <v>0.05479277364878792</v>
+        <v>0.1468469283297689</v>
       </c>
       <c r="K5">
-        <v>0.384</v>
+        <v>-0.586</v>
       </c>
       <c r="L5">
-        <v>0.1737556561085973</v>
+        <v>-0.5008547008547009</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -996,7 +975,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1005,73 +984,76 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.8120000000000001</v>
+        <v>12</v>
       </c>
       <c r="V5">
-        <v>0.03147286821705426</v>
+        <v>0.5</v>
       </c>
       <c r="W5">
-        <v>0.7514677103718199</v>
+        <v>-1.542105263157895</v>
       </c>
       <c r="X5">
-        <v>0.07248900629893952</v>
+        <v>0.06033481212523091</v>
       </c>
       <c r="Y5">
-        <v>0.6789787040728804</v>
+        <v>-1.602440075283126</v>
       </c>
       <c r="Z5">
-        <v>1.808178807742361</v>
+        <v>0.9148161732548584</v>
       </c>
       <c r="AA5">
-        <v>0.09907513212916239</v>
+        <v>0.1343379450288697</v>
       </c>
       <c r="AB5">
-        <v>0.07128999738837584</v>
+        <v>0.06014688874903659</v>
       </c>
       <c r="AC5">
-        <v>0.02778513474078655</v>
+        <v>0.07419105627983308</v>
       </c>
       <c r="AD5">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>0.6652242571017307</v>
+        <v>0.4509454692708518</v>
       </c>
       <c r="AF5">
-        <v>1.925224257101731</v>
+        <v>0.4509454692708518</v>
       </c>
       <c r="AG5">
-        <v>1.113224257101731</v>
+        <v>-11.54905453072915</v>
       </c>
       <c r="AH5">
-        <v>0.06943944760369576</v>
+        <v>0.01844286429895258</v>
       </c>
       <c r="AI5">
-        <v>0.8351570356639578</v>
+        <v>0.02512098708353821</v>
       </c>
       <c r="AJ5">
-        <v>0.04136346676515276</v>
+        <v>-0.9275644616091535</v>
       </c>
       <c r="AK5">
-        <v>0.7455171263172753</v>
+        <v>-1.940709184845582</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>-0.385</v>
       </c>
       <c r="AN5">
-        <v>4.809160305343512</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>4.248947546189811</v>
+        <v>-44.08036080430972</v>
+      </c>
+      <c r="AQ5">
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1064,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kingwisoft Technology Group Company Limited (SEHK:8295)</t>
+          <t>Da Yu Financial Holdings Limited (SEHK:1073)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,26 +1072,23 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.903</v>
-      </c>
       <c r="G6">
-        <v>0.1441358024691358</v>
+        <v>0.7422680412371134</v>
       </c>
       <c r="H6">
-        <v>0.1118827160493827</v>
+        <v>0.7422680412371134</v>
       </c>
       <c r="I6">
-        <v>0.04938271604938272</v>
+        <v>0.2209131075110456</v>
       </c>
       <c r="J6">
-        <v>0.04772625644016721</v>
+        <v>0.2209131075110456</v>
       </c>
       <c r="K6">
-        <v>13.4</v>
+        <v>-1.56</v>
       </c>
       <c r="L6">
-        <v>0.1033950617283951</v>
+        <v>-0.2297496318114875</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1118,7 +1097,7 @@
         <v>-0</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1127,79 +1106,79 @@
         <v>-0</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>30.8</v>
+        <v>11.7</v>
       </c>
       <c r="V6">
-        <v>0.3515981735159818</v>
+        <v>0.4223826714801444</v>
       </c>
       <c r="W6">
-        <v>0.08486383787207093</v>
+        <v>-0.02508038585209003</v>
       </c>
       <c r="X6">
-        <v>0.08039780635832447</v>
+        <v>0.06042846577538614</v>
       </c>
       <c r="Y6">
-        <v>0.004466031513746457</v>
+        <v>-0.08550885162747618</v>
       </c>
       <c r="Z6">
-        <v>1.820224719101123</v>
+        <v>0.5273376825100962</v>
       </c>
       <c r="AA6">
-        <v>0.08687251172255153</v>
+        <v>0.1164958061509785</v>
       </c>
       <c r="AB6">
-        <v>0.07355451703648565</v>
+        <v>0.06013427383286998</v>
       </c>
       <c r="AC6">
-        <v>0.01331799468606588</v>
+        <v>0.05636153231810853</v>
       </c>
       <c r="AD6">
-        <v>32.7</v>
+        <v>0.667</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>32.7</v>
+        <v>0.667</v>
       </c>
       <c r="AG6">
-        <v>1.900000000000002</v>
+        <v>-11.033</v>
       </c>
       <c r="AH6">
-        <v>0.2718204488778055</v>
+        <v>0.02351323721225368</v>
       </c>
       <c r="AI6">
-        <v>0.1507607192254495</v>
+        <v>0.01086903384555217</v>
       </c>
       <c r="AJ6">
-        <v>0.02122905027932963</v>
+        <v>-0.6619667606647867</v>
       </c>
       <c r="AK6">
-        <v>0.01020956475013435</v>
+        <v>-0.222139448728532</v>
       </c>
       <c r="AL6">
-        <v>2.99</v>
+        <v>0.017</v>
       </c>
       <c r="AM6">
-        <v>2.696</v>
+        <v>-0.096</v>
       </c>
       <c r="AN6">
-        <v>2.794871794871795</v>
+        <v>0.3403061224489796</v>
       </c>
       <c r="AO6">
-        <v>2.140468227424749</v>
+        <v>88.23529411764706</v>
       </c>
       <c r="AP6">
-        <v>0.1623931623931626</v>
+        <v>-5.629081632653061</v>
       </c>
       <c r="AQ6">
-        <v>2.373887240356083</v>
+        <v>-15.625</v>
       </c>
     </row>
     <row r="7">
@@ -1210,7 +1189,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOP Financial Group Limited (NasdaqCM:TOP)</t>
+          <t>Solowin Holdings (NasdaqCM:SWIN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,22 +1198,22 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.0696629213483146</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.00793093984139864</v>
+        <v>0.02606112503475483</v>
       </c>
       <c r="J7">
-        <v>0.00773377401852588</v>
+        <v>0.02606112503475483</v>
       </c>
       <c r="K7">
-        <v>3.49</v>
+        <v>1.35</v>
       </c>
       <c r="L7">
-        <v>0.4462915601023018</v>
+        <v>0.303370786516854</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1258,55 +1237,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>6.2</v>
+        <v>1.93</v>
       </c>
       <c r="V7">
-        <v>0.03625730994152047</v>
+        <v>0.04606205250596659</v>
       </c>
       <c r="W7">
-        <v>0.5170370370370371</v>
+        <v>0.675</v>
       </c>
       <c r="X7">
-        <v>0.0705850049965534</v>
+        <v>0.06010616861119286</v>
       </c>
       <c r="Y7">
-        <v>0.4464520320404837</v>
+        <v>0.6148938313888072</v>
       </c>
       <c r="Z7">
-        <v>3.706336350185842</v>
+        <v>3.522966664674541</v>
       </c>
       <c r="AA7">
-        <v>0.0286639677689853</v>
+        <v>0.09181247474135641</v>
       </c>
       <c r="AB7">
-        <v>0.07054335070836062</v>
+        <v>0.06004799573063511</v>
       </c>
       <c r="AC7">
-        <v>-0.04187938293937532</v>
+        <v>0.0317644790107213</v>
       </c>
       <c r="AD7">
-        <v>0.245</v>
+        <v>0.006</v>
       </c>
       <c r="AE7">
-        <v>0.2199002522013132</v>
+        <v>0.2401399679767051</v>
       </c>
       <c r="AF7">
-        <v>0.4649002522013131</v>
+        <v>0.2461399679767051</v>
       </c>
       <c r="AG7">
-        <v>-5.735099747798687</v>
+        <v>-1.683860032023295</v>
       </c>
       <c r="AH7">
-        <v>0.002711343554963778</v>
+        <v>0.00584015447591941</v>
       </c>
       <c r="AI7">
-        <v>0.04359161747484271</v>
+        <v>0.06863646432506004</v>
       </c>
       <c r="AJ7">
-        <v>-0.03470246700325768</v>
+        <v>-0.04187025491168766</v>
       </c>
       <c r="AK7">
-        <v>-1.284485525734003</v>
+        <v>-1.016737754406383</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1315,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>2.311320754716981</v>
+        <v>0.03658536585365853</v>
       </c>
       <c r="AP7">
-        <v>-54.10471460187441</v>
+        <v>-10.26743921965424</v>
       </c>
     </row>
     <row r="8">
@@ -1338,25 +1317,25 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.258</v>
+        <v>0.005180000000000001</v>
       </c>
       <c r="G8">
-        <v>0.3677570093457944</v>
+        <v>0.6914893617021276</v>
       </c>
       <c r="H8">
-        <v>0.3677570093457944</v>
+        <v>0.6914893617021276</v>
       </c>
       <c r="I8">
-        <v>0.2841121495327103</v>
+        <v>0.5063829787234042</v>
       </c>
       <c r="J8">
-        <v>0.2841121495327103</v>
+        <v>0.5063829787234042</v>
       </c>
       <c r="K8">
-        <v>-3.96</v>
+        <v>-6.48</v>
       </c>
       <c r="L8">
-        <v>-0.1850467289719626</v>
+        <v>-0.3446808510638298</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1380,73 +1359,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>35.6</v>
+        <v>16.2</v>
       </c>
       <c r="V8">
-        <v>0.586490939044481</v>
+        <v>0.3476394849785407</v>
       </c>
       <c r="W8">
-        <v>-0.01727748691099476</v>
+        <v>-0.02904527117884357</v>
       </c>
       <c r="X8">
-        <v>0.08521463209143235</v>
+        <v>0.07227326435332249</v>
       </c>
       <c r="Y8">
-        <v>-0.1024921190024271</v>
+        <v>-0.101318535532166</v>
       </c>
       <c r="Z8">
-        <v>0.08642518769208402</v>
+        <v>0.08529132886612437</v>
       </c>
       <c r="AA8">
-        <v>0.02455444584896593</v>
+        <v>0.04319007717050553</v>
       </c>
       <c r="AB8">
-        <v>0.07107951817797035</v>
+        <v>0.06230220238316085</v>
       </c>
       <c r="AC8">
-        <v>-0.04652507232900442</v>
+        <v>-0.01911212521265532</v>
       </c>
       <c r="AD8">
-        <v>33.7</v>
+        <v>32.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>33.7</v>
+        <v>32.3</v>
       </c>
       <c r="AG8">
-        <v>-1.899999999999999</v>
+        <v>16.1</v>
       </c>
       <c r="AH8">
-        <v>0.3569915254237288</v>
+        <v>0.4093789607097591</v>
       </c>
       <c r="AI8">
-        <v>0.110891740704179</v>
+        <v>0.1080628972900635</v>
       </c>
       <c r="AJ8">
-        <v>-0.032312925170068</v>
+        <v>0.2567783094098883</v>
       </c>
       <c r="AK8">
-        <v>-0.007081625046589633</v>
+        <v>0.0569508312698974</v>
       </c>
       <c r="AL8">
-        <v>0.73</v>
+        <v>1.63</v>
       </c>
       <c r="AM8">
-        <v>0.73</v>
+        <v>1.603</v>
       </c>
       <c r="AN8">
-        <v>4.87698986975398</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="AO8">
-        <v>8.328767123287671</v>
+        <v>5.840490797546012</v>
       </c>
       <c r="AP8">
-        <v>-0.2749638205499274</v>
+        <v>1.57843137254902</v>
       </c>
       <c r="AQ8">
-        <v>8.328767123287671</v>
+        <v>5.93886462882096</v>
       </c>
     </row>
     <row r="9">
@@ -1466,43 +1445,43 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.473</v>
+        <v>0.48</v>
       </c>
       <c r="G9">
-        <v>0.4952658412235979</v>
+        <v>0.3605491329479769</v>
       </c>
       <c r="H9">
-        <v>0.4952658412235979</v>
+        <v>0.3605491329479769</v>
       </c>
       <c r="I9">
-        <v>0.4304442825928623</v>
+        <v>0.2507225433526012</v>
       </c>
       <c r="J9">
-        <v>0.2152221412964312</v>
+        <v>0.2507225433526012</v>
       </c>
       <c r="K9">
-        <v>-22.4</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="L9">
-        <v>-0.1631463947560087</v>
+        <v>-0.4869942196531792</v>
       </c>
       <c r="M9">
         <v>0.029</v>
       </c>
       <c r="N9">
-        <v>0.001003460207612457</v>
+        <v>0.001318181818181818</v>
       </c>
       <c r="O9">
-        <v>-0.001294642857142857</v>
+        <v>-0.00043026706231454</v>
       </c>
       <c r="P9">
         <v>0.029</v>
       </c>
       <c r="Q9">
-        <v>0.001003460207612457</v>
+        <v>0.001318181818181818</v>
       </c>
       <c r="R9">
-        <v>-0.001294642857142857</v>
+        <v>-0.00043026706231454</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1511,73 +1490,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>101.3</v>
+        <v>55.4</v>
       </c>
       <c r="V9">
-        <v>3.505190311418685</v>
+        <v>2.518181818181818</v>
       </c>
       <c r="W9">
-        <v>-0.05509099852434825</v>
+        <v>-0.1760250718203187</v>
       </c>
       <c r="X9">
-        <v>0.8137041667669607</v>
+        <v>0.5924845045001124</v>
       </c>
       <c r="Y9">
-        <v>-0.868795165291309</v>
+        <v>-0.768509576320431</v>
       </c>
       <c r="Z9">
-        <v>0.08486309413437172</v>
+        <v>0.1002317497103129</v>
       </c>
       <c r="AA9">
-        <v>0.01826441683664009</v>
+        <v>0.02513035921205099</v>
       </c>
       <c r="AB9">
-        <v>0.07825359899350258</v>
+        <v>0.06543973144447122</v>
       </c>
       <c r="AC9">
-        <v>-0.05998918215686249</v>
+        <v>-0.04030937223242023</v>
       </c>
       <c r="AD9">
-        <v>811.1</v>
+        <v>661.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>811.1</v>
+        <v>661.7</v>
       </c>
       <c r="AG9">
-        <v>709.8000000000001</v>
+        <v>606.3000000000001</v>
       </c>
       <c r="AH9">
-        <v>0.9655952380952382</v>
+        <v>0.9678221442152991</v>
       </c>
       <c r="AI9">
-        <v>0.4712683748765325</v>
+        <v>0.4643834655063513</v>
       </c>
       <c r="AJ9">
-        <v>0.9608772167320969</v>
+        <v>0.964984879834474</v>
       </c>
       <c r="AK9">
-        <v>0.4382022471910113</v>
+        <v>0.4427163198247536</v>
       </c>
       <c r="AL9">
-        <v>48.8</v>
+        <v>50</v>
       </c>
       <c r="AM9">
-        <v>47.894</v>
+        <v>49.296</v>
       </c>
       <c r="AN9">
-        <v>13.63193277310924</v>
+        <v>18.74504249291785</v>
       </c>
       <c r="AO9">
-        <v>1.211065573770492</v>
+        <v>0.6940000000000001</v>
       </c>
       <c r="AP9">
-        <v>11.92941176470588</v>
+        <v>17.17563739376771</v>
       </c>
       <c r="AQ9">
-        <v>1.233975028187247</v>
+        <v>0.7039110678351186</v>
       </c>
     </row>
     <row r="10">
@@ -1588,7 +1567,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oriental Explorer Holdings Limited (SEHK:430)</t>
+          <t>TOP Financial Group Limited (NasdaqCM:TOP)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1596,122 +1575,107 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D10">
-        <v>-0.335</v>
-      </c>
-      <c r="E10">
-        <v>-0.374</v>
-      </c>
       <c r="G10">
-        <v>0.6305732484076433</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>0.6305732484076433</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0.5859872611464968</v>
+        <v>0.008698495435095575</v>
       </c>
       <c r="J10">
-        <v>0.501707818407897</v>
+        <v>0.008617343291094683</v>
       </c>
       <c r="K10">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="L10">
-        <v>0.6847133757961783</v>
+        <v>0.3505154639175258</v>
       </c>
       <c r="M10">
-        <v>1.48</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.07081339712918661</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.6883720930232559</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>1.48</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.07081339712918661</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.6883720930232559</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>22.2</v>
+        <v>16</v>
       </c>
       <c r="V10">
-        <v>1.062200956937799</v>
+        <v>0.1209372637944066</v>
       </c>
       <c r="W10">
-        <v>0.01104262968669748</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="X10">
-        <v>0.1208130366240062</v>
+        <v>0.06004005452937151</v>
       </c>
       <c r="Y10">
-        <v>-0.1097704069373087</v>
+        <v>0.2732932788039619</v>
       </c>
       <c r="Z10">
-        <v>0.0147764705882353</v>
+        <v>2.215561340640678</v>
       </c>
       <c r="AA10">
-        <v>0.007413470822591985</v>
+        <v>0.01909225265477869</v>
       </c>
       <c r="AB10">
-        <v>0.07576467288440494</v>
+        <v>0.0600189249474339</v>
       </c>
       <c r="AC10">
-        <v>-0.06835120206181296</v>
+        <v>-0.0409266722926552</v>
       </c>
       <c r="AD10">
-        <v>39.7</v>
+        <v>0.15</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>0.1331229713978647</v>
       </c>
       <c r="AF10">
-        <v>39.7</v>
+        <v>0.2831229713978647</v>
       </c>
       <c r="AG10">
-        <v>17.5</v>
+        <v>-15.71687702860214</v>
       </c>
       <c r="AH10">
-        <v>0.6551155115511551</v>
+        <v>0.002135437490478654</v>
       </c>
       <c r="AI10">
-        <v>0.1703862660944206</v>
+        <v>0.007803158830099925</v>
       </c>
       <c r="AJ10">
-        <v>0.4557291666666667</v>
+        <v>-0.1348126266308552</v>
       </c>
       <c r="AK10">
-        <v>0.08301707779886149</v>
+        <v>-0.774874611309373</v>
       </c>
       <c r="AL10">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>-0.01900000000000002</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>21.57608695652174</v>
-      </c>
-      <c r="AO10">
-        <v>10.57471264367816</v>
+        <v>1.351351351351351</v>
       </c>
       <c r="AP10">
-        <v>9.510869565217392</v>
-      </c>
-      <c r="AQ10">
-        <v>-96.84210526315782</v>
+        <v>-141.5934867441634</v>
       </c>
     </row>
     <row r="11">
@@ -1722,7 +1686,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CLSA Premium Limited (SEHK:6877)</t>
+          <t>Oriental Explorer Holdings Limited (SEHK:430)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1731,109 +1695,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.329</v>
+        <v>-0.193</v>
+      </c>
+      <c r="E11">
+        <v>-0.364</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>0.6188925081433225</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>0.6188925081433225</v>
       </c>
       <c r="I11">
-        <v>0.01071544487762077</v>
+        <v>0.5602605863192183</v>
       </c>
       <c r="J11">
-        <v>0.01071544487762077</v>
+        <v>0.4054107853782121</v>
       </c>
       <c r="K11">
-        <v>-5.61</v>
+        <v>1.04</v>
       </c>
       <c r="L11">
-        <v>-4.921052631578948</v>
+        <v>0.3387622149837134</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>0.927</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.05830188679245283</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>0.8913461538461539</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>0.927</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.05830188679245283</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>0.8913461538461539</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>28.2</v>
+        <v>23.3</v>
       </c>
       <c r="V11">
-        <v>0.746031746031746</v>
+        <v>1.465408805031447</v>
       </c>
       <c r="W11">
-        <v>-0.1464751958224543</v>
+        <v>0.005380237972064149</v>
       </c>
       <c r="X11">
-        <v>0.07064956282436816</v>
+        <v>0.1049854351364571</v>
       </c>
       <c r="Y11">
-        <v>-0.2171247586468225</v>
+        <v>-0.09960519716439298</v>
       </c>
       <c r="Z11">
-        <v>0.178043712913323</v>
+        <v>0.01456356736242884</v>
       </c>
       <c r="AA11">
-        <v>0.00190781759152965</v>
+        <v>0.005904227282310773</v>
       </c>
       <c r="AB11">
-        <v>0.07061882246051489</v>
+        <v>0.06563302742118982</v>
       </c>
       <c r="AC11">
-        <v>-0.06871100486898524</v>
+        <v>-0.05972880013887905</v>
       </c>
       <c r="AD11">
-        <v>0.181</v>
+        <v>40.4</v>
       </c>
       <c r="AE11">
-        <v>0.01392196419756161</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.1949219641975616</v>
+        <v>40.4</v>
       </c>
       <c r="AG11">
-        <v>-28.00507803580244</v>
+        <v>17.1</v>
       </c>
       <c r="AH11">
-        <v>0.005130210936641367</v>
+        <v>0.7175843694493783</v>
       </c>
       <c r="AI11">
-        <v>0.006188996575992243</v>
+        <v>0.1725758222981632</v>
       </c>
       <c r="AJ11">
-        <v>-2.859142537139828</v>
+        <v>0.5181818181818181</v>
       </c>
       <c r="AK11">
-        <v>-8.499466251432976</v>
+        <v>0.08111954459203036</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>0.487</v>
       </c>
       <c r="AN11">
-        <v>12.06666666666667</v>
+        <v>23.48837209302325</v>
+      </c>
+      <c r="AO11">
+        <v>2.333785617367707</v>
       </c>
       <c r="AP11">
-        <v>-1867.005202386829</v>
+        <v>9.941860465116278</v>
+      </c>
+      <c r="AQ11">
+        <v>3.531827515400411</v>
       </c>
     </row>
     <row r="12">
@@ -1844,7 +1820,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hatcher Group Limited (SEHK:8365)</t>
+          <t>Get Nice Holdings Limited (SEHK:64)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1853,7 +1829,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0142</v>
+        <v>-0.0132</v>
+      </c>
+      <c r="E12">
+        <v>-0.0246</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1862,88 +1841,91 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0.0004605478180712254</v>
+        <v>0.0001542492922843869</v>
       </c>
       <c r="J12">
-        <v>0.0004605478180712254</v>
+        <v>0.0001542492922843869</v>
       </c>
       <c r="K12">
-        <v>-1.05</v>
+        <v>30.4</v>
       </c>
       <c r="L12">
-        <v>-0.1190476190476191</v>
+        <v>0.579047619047619</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>12.3</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.06856187290969899</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>0.4046052631578948</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>12.3</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.06856187290969899</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>0.4046052631578948</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>2.14</v>
+        <v>350.2</v>
       </c>
       <c r="V12">
-        <v>0.02628992628992629</v>
+        <v>1.9520624303233</v>
       </c>
       <c r="W12">
-        <v>-0.2192066805845511</v>
+        <v>0.0420644804206448</v>
       </c>
       <c r="X12">
-        <v>0.07234604247868281</v>
+        <v>0.06000310668118806</v>
       </c>
       <c r="Y12">
-        <v>-0.291552723063234</v>
+        <v>-0.01793862626054326</v>
       </c>
       <c r="Z12">
-        <v>2.903522235979438</v>
+        <v>0.1137374201808795</v>
       </c>
       <c r="AA12">
-        <v>0.001337210830501616</v>
+        <v>1.754391656915261e-05</v>
       </c>
       <c r="AB12">
-        <v>0.07123742167408731</v>
+        <v>0.06000220881107234</v>
       </c>
       <c r="AC12">
-        <v>-0.06990021084358569</v>
+        <v>-0.05998466489450318</v>
       </c>
       <c r="AD12">
-        <v>5.63</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>0.004689841223058959</v>
+        <v>0.009509560775348435</v>
       </c>
       <c r="AF12">
-        <v>5.634689841223059</v>
+        <v>0.009509560775348435</v>
       </c>
       <c r="AG12">
-        <v>3.494689841223059</v>
+        <v>-350.1904904392246</v>
       </c>
       <c r="AH12">
-        <v>0.0647407355791397</v>
+        <v>5.300477549171969e-05</v>
       </c>
       <c r="AI12">
-        <v>0.3895479200089519</v>
+        <v>1.061560596740156e-05</v>
       </c>
       <c r="AJ12">
-        <v>0.04116499922149561</v>
+        <v>2.050409771285475</v>
       </c>
       <c r="AK12">
-        <v>0.2835519502920212</v>
+        <v>-0.6418335536730907</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1952,10 +1934,10 @@
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>1126</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>698.9379682446117</v>
+        <v>-35019.04904392246</v>
       </c>
     </row>
     <row r="13">
@@ -1975,10 +1957,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.0273</v>
+        <v>-0.00454</v>
       </c>
       <c r="E13">
-        <v>-0.186</v>
+        <v>-0.021</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1987,34 +1969,34 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.0001632066330289905</v>
+        <v>0.0001945636488551937</v>
       </c>
       <c r="J13">
-        <v>0.0001280033418349466</v>
+        <v>0.0001674208188297161</v>
       </c>
       <c r="K13">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="L13">
-        <v>0.3013392857142858</v>
+        <v>0.5035971223021583</v>
       </c>
       <c r="M13">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N13">
-        <v>0.08271979211779992</v>
+        <v>0.0923076923076923</v>
       </c>
       <c r="O13">
-        <v>1.414814814814815</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="P13">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="Q13">
-        <v>0.08271979211779992</v>
+        <v>0.0923076923076923</v>
       </c>
       <c r="R13">
-        <v>1.414814814814815</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2023,55 +2005,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>199.4</v>
+        <v>306.4</v>
       </c>
       <c r="V13">
-        <v>0.8635773061931572</v>
+        <v>1.473076923076923</v>
       </c>
       <c r="W13">
-        <v>0.02400426742532006</v>
+        <v>0.03802969938428105</v>
       </c>
       <c r="X13">
-        <v>0.07066994979270666</v>
+        <v>0.06004186848494464</v>
       </c>
       <c r="Y13">
-        <v>-0.04666568236738661</v>
+        <v>-0.02201216910066359</v>
       </c>
       <c r="Z13">
-        <v>0.109363934987945</v>
+        <v>0.1178250900650231</v>
       </c>
       <c r="AA13">
-        <v>1.39989491546768e-05</v>
+        <v>1.972637305737122e-05</v>
       </c>
       <c r="AB13">
-        <v>0.07057893626503804</v>
+        <v>0.06001972544568675</v>
       </c>
       <c r="AC13">
-        <v>-0.07056493731588337</v>
+        <v>-0.05999999907262937</v>
       </c>
       <c r="AD13">
-        <v>1.36</v>
+        <v>0.457</v>
       </c>
       <c r="AE13">
-        <v>0.008441714201506127</v>
+        <v>0.009433479213692104</v>
       </c>
       <c r="AF13">
-        <v>1.368441714201506</v>
+        <v>0.4664334792136921</v>
       </c>
       <c r="AG13">
-        <v>-198.0315582857985</v>
+        <v>-305.9335665207863</v>
       </c>
       <c r="AH13">
-        <v>0.005891638588962195</v>
+        <v>0.002237451235813465</v>
       </c>
       <c r="AI13">
-        <v>0.002472037079938908</v>
+        <v>0.0008391107127916443</v>
       </c>
       <c r="AJ13">
-        <v>-6.02497556798486</v>
+        <v>3.123888748153089</v>
       </c>
       <c r="AK13">
-        <v>-0.5591451268986899</v>
+        <v>-1.226351626766162</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2080,10 +2062,10 @@
         <v>0</v>
       </c>
       <c r="AN13">
-        <v>151.1111111111111</v>
+        <v>45.7</v>
       </c>
       <c r="AP13">
-        <v>-22003.50647619983</v>
+        <v>-30593.35665207863</v>
       </c>
     </row>
     <row r="14">
@@ -2094,7 +2076,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Get Nice Holdings Limited (SEHK:64)</t>
+          <t>Fu Shek Financial Holdings Limited (SEHK:2263)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2102,9 +2084,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D14">
-        <v>-0.0696</v>
-      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2112,103 +2091,94 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0.0001532194756048348</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>7.66097378024174e-05</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>-2.53</v>
+        <v>0.648</v>
       </c>
       <c r="L14">
-        <v>-0.05315126050420167</v>
+        <v>0.1588235294117647</v>
       </c>
       <c r="M14">
-        <v>12.3</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.06574024585783005</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>-4.861660079051384</v>
+        <v>-0</v>
       </c>
       <c r="P14">
-        <v>12.3</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.06574024585783005</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>-4.861660079051384</v>
+        <v>-0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>270.6</v>
+        <v>26.2</v>
       </c>
       <c r="V14">
-        <v>1.446285408872261</v>
+        <v>1.550295857988166</v>
       </c>
       <c r="W14">
-        <v>-0.00338099692636643</v>
+        <v>0.01459459459459459</v>
       </c>
       <c r="X14">
-        <v>0.07217012762258541</v>
+        <v>0.0600713073864836</v>
       </c>
       <c r="Y14">
-        <v>-0.07555112454895184</v>
+        <v>-0.045476712791889</v>
       </c>
       <c r="Z14">
-        <v>0.08380745969231986</v>
+        <v>0.1225961538461538</v>
       </c>
       <c r="AA14">
-        <v>6.420467512915289e-06</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.0706064698767874</v>
+        <v>0.06002402437346883</v>
       </c>
       <c r="AC14">
-        <v>-0.07060004940927449</v>
+        <v>-0.06002402437346883</v>
       </c>
       <c r="AD14">
-        <v>11.7</v>
+        <v>0.066</v>
       </c>
       <c r="AE14">
-        <v>0.008533764806049317</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>11.70853376480605</v>
+        <v>0.066</v>
       </c>
       <c r="AG14">
-        <v>-258.891466235194</v>
+        <v>-26.134</v>
       </c>
       <c r="AH14">
-        <v>0.05889351700897029</v>
+        <v>0.003890133207591655</v>
       </c>
       <c r="AI14">
-        <v>0.01321044909166255</v>
+        <v>0.001458047983033623</v>
       </c>
       <c r="AJ14">
-        <v>3.606159336362444</v>
+        <v>2.83019276586528</v>
       </c>
       <c r="AK14">
-        <v>-0.4204773070988289</v>
+        <v>-1.370712262666527</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
         <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>1300</v>
-      </c>
-      <c r="AP14">
-        <v>-28765.71847057711</v>
       </c>
     </row>
     <row r="15">
@@ -2219,7 +2189,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mason Group Holdings Limited (SEHK:273)</t>
+          <t>Innovax Holdings Limited (SEHK:2680)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2228,7 +2198,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.224</v>
+        <v>-0.155</v>
+      </c>
+      <c r="E15">
+        <v>-0.104</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2243,10 +2216,10 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>-105.2</v>
+        <v>1.54</v>
       </c>
       <c r="L15">
-        <v>-2.348214285714286</v>
+        <v>0.3073852295409182</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2255,7 +2228,7 @@
         <v>-0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2264,61 +2237,61 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>113.3</v>
+        <v>14.5</v>
       </c>
       <c r="V15">
-        <v>0.6637375512595196</v>
+        <v>0.8579881656804734</v>
       </c>
       <c r="W15">
-        <v>-0.1583383503913305</v>
+        <v>0.05877862595419848</v>
       </c>
       <c r="X15">
-        <v>0.07105906331738263</v>
+        <v>0.0601467319045242</v>
       </c>
       <c r="Y15">
-        <v>-0.2293974137087132</v>
+        <v>-0.001368105950325722</v>
       </c>
       <c r="Z15">
-        <v>0.0774483533581122</v>
+        <v>0.286810167162812</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.07067497826549667</v>
+        <v>0.0600476743049821</v>
       </c>
       <c r="AC15">
-        <v>-0.07067497826549667</v>
+        <v>-0.0600476743049821</v>
       </c>
       <c r="AD15">
-        <v>3.52</v>
+        <v>0.138</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>3.52</v>
+        <v>0.138</v>
       </c>
       <c r="AG15">
-        <v>-109.78</v>
+        <v>-14.362</v>
       </c>
       <c r="AH15">
-        <v>0.02020433934106302</v>
+        <v>0.008099542199788708</v>
       </c>
       <c r="AI15">
-        <v>0.006538861643632041</v>
+        <v>0.004939508912592168</v>
       </c>
       <c r="AJ15">
-        <v>-1.802035456336179</v>
+        <v>-5.658786446020492</v>
       </c>
       <c r="AK15">
-        <v>-0.2582937273540069</v>
+        <v>-1.068760232177407</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2335,7 +2308,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DLC Asia Limited (SEHK:8210)</t>
+          <t>Pinestone Capital Limited (SEHK:804)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2343,23 +2316,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
       <c r="K16">
-        <v>-0.674</v>
-      </c>
-      <c r="L16">
-        <v>-0.1278937381404175</v>
+        <v>-5.44</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2383,55 +2341,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>6.59</v>
+        <v>5.15</v>
       </c>
       <c r="V16">
-        <v>1.734210526315789</v>
+        <v>0.5525751072961373</v>
       </c>
       <c r="W16">
-        <v>-0.06017857142857144</v>
+        <v>-0.2211382113821138</v>
       </c>
       <c r="X16">
-        <v>0.07112624194604861</v>
+        <v>0.06027190441327291</v>
       </c>
       <c r="Y16">
-        <v>-0.13130481337462</v>
+        <v>-0.2814101157953867</v>
       </c>
       <c r="Z16">
-        <v>1.129205056781659</v>
+        <v>0</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.07069445332392621</v>
+        <v>0.0600864850542325</v>
       </c>
       <c r="AC16">
-        <v>-0.07069445332392621</v>
+        <v>-0.0600864850542325</v>
       </c>
       <c r="AD16">
-        <v>0.08799999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0.08799999999999999</v>
+        <v>0.142</v>
       </c>
       <c r="AG16">
-        <v>-6.502</v>
+        <v>-5.008</v>
       </c>
       <c r="AH16">
-        <v>0.02263374485596708</v>
+        <v>0.01500739801310505</v>
       </c>
       <c r="AI16">
-        <v>0.008390541571319604</v>
+        <v>0.006716488506290795</v>
       </c>
       <c r="AJ16">
-        <v>2.406365655070318</v>
+        <v>-1.161410018552876</v>
       </c>
       <c r="AK16">
-        <v>-1.668034889687019</v>
+        <v>-0.3131565782891446</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2448,7 +2406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Innovax Holdings Limited (SEHK:2680)</t>
+          <t>GoFintech Innovation Limited (SEHK:290)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2456,6 +2414,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D17">
+        <v>-0.138</v>
+      </c>
       <c r="G17">
         <v>0</v>
       </c>
@@ -2469,10 +2430,10 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>-3.81</v>
+        <v>-6.6</v>
       </c>
       <c r="L17">
-        <v>-0.8619909502262444</v>
+        <v>-2.986425339366516</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2496,55 +2457,55 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>9.050000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="V17">
-        <v>0.8786407766990292</v>
+        <v>0.06020841373986877</v>
       </c>
       <c r="W17">
-        <v>-0.1291525423728813</v>
+        <v>-0.1935483870967742</v>
       </c>
       <c r="X17">
-        <v>0.07133056157673257</v>
+        <v>0.06025976517866571</v>
       </c>
       <c r="Y17">
-        <v>-0.2004831039496139</v>
+        <v>-0.2538081522754399</v>
       </c>
       <c r="Z17">
-        <v>0.1923244278130711</v>
+        <v>0.1041961338991042</v>
       </c>
       <c r="AA17">
         <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.07084812502781986</v>
+        <v>0.06011470697781181</v>
       </c>
       <c r="AC17">
-        <v>-0.07084812502781986</v>
+        <v>-0.06011470697781181</v>
       </c>
       <c r="AD17">
-        <v>0.318</v>
+        <v>3.77</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0.318</v>
+        <v>3.77</v>
       </c>
       <c r="AG17">
-        <v>-8.732000000000001</v>
+        <v>-11.83</v>
       </c>
       <c r="AH17">
-        <v>0.02994914296477679</v>
+        <v>0.01434168980865066</v>
       </c>
       <c r="AI17">
-        <v>0.01199185458933555</v>
+        <v>0.08327810912303954</v>
       </c>
       <c r="AJ17">
-        <v>-5.56887755102041</v>
+        <v>-0.04784243943867028</v>
       </c>
       <c r="AK17">
-        <v>-0.4998855049232885</v>
+        <v>-0.3987192450286485</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2561,7 +2522,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Imagi International Holdings Limited (SEHK:585)</t>
+          <t>Sunwah Kingsway Capital Holdings Limited (SEHK:188)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2569,6 +2530,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D18">
+        <v>-0.478</v>
+      </c>
       <c r="G18">
         <v>0</v>
       </c>
@@ -2582,82 +2546,85 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>-2.99</v>
+        <v>-10</v>
       </c>
       <c r="L18">
-        <v>-2.669642857142857</v>
+        <v>-10.88139281828074</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>1.52</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.06940639269406393</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>-0.152</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>1.52</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.06940639269406393</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>-0.152</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V18">
-        <v>0.5924855491329479</v>
+        <v>0.9315068493150684</v>
       </c>
       <c r="W18">
-        <v>-0.02836812144212524</v>
+        <v>-0.08620689655172414</v>
       </c>
       <c r="X18">
-        <v>0.07102807849847825</v>
+        <v>0.06785974988465568</v>
       </c>
       <c r="Y18">
-        <v>-0.09939619994060349</v>
+        <v>-0.1540666464363798</v>
       </c>
       <c r="Z18">
-        <v>0.01054613935969868</v>
+        <v>0.008426785992646048</v>
       </c>
       <c r="AA18">
         <v>0</v>
       </c>
       <c r="AB18">
-        <v>0.07090653013559396</v>
+        <v>0.06023743086799698</v>
       </c>
       <c r="AC18">
-        <v>-0.07090653013559396</v>
+        <v>-0.06023743086799698</v>
       </c>
       <c r="AD18">
-        <v>0.673</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0.673</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="AG18">
-        <v>-19.827</v>
+        <v>-10.68</v>
       </c>
       <c r="AH18">
-        <v>0.01907974938338106</v>
+        <v>0.3074003795066414</v>
       </c>
       <c r="AI18">
-        <v>0.005338177087877658</v>
+        <v>0.0864614837217577</v>
       </c>
       <c r="AJ18">
-        <v>-1.34211060718879</v>
+        <v>-0.9518716577540105</v>
       </c>
       <c r="AK18">
-        <v>-0.1878036998096104</v>
+        <v>-0.1160617257118017</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2674,7 +2641,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sunwah Kingsway Capital Holdings Limited (SEHK:188)</t>
+          <t>DLC Asia Limited (SEHK:8210)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2683,7 +2650,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>-0.194</v>
+        <v>-0.0384</v>
+      </c>
+      <c r="E19">
+        <v>-0.0886</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2698,85 +2668,82 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>-9.949999999999999</v>
+        <v>0.505</v>
       </c>
       <c r="L19">
-        <v>-1.742556917688266</v>
+        <v>0.06026252983293556</v>
       </c>
       <c r="M19">
-        <v>1.78</v>
+        <v>-0</v>
       </c>
       <c r="N19">
-        <v>0.05953177257525084</v>
+        <v>-0</v>
       </c>
       <c r="O19">
-        <v>-0.1788944723618091</v>
+        <v>-0</v>
       </c>
       <c r="P19">
-        <v>1.78</v>
+        <v>-0</v>
       </c>
       <c r="Q19">
-        <v>0.05953177257525084</v>
+        <v>-0</v>
       </c>
       <c r="R19">
-        <v>-0.1788944723618091</v>
+        <v>-0</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
       <c r="U19">
-        <v>20.7</v>
+        <v>7.69</v>
       </c>
       <c r="V19">
-        <v>0.6923076923076923</v>
+        <v>1.598752598752599</v>
       </c>
       <c r="W19">
-        <v>-0.07761310452418096</v>
+        <v>0.04855769230769231</v>
       </c>
       <c r="X19">
-        <v>0.08282328262567012</v>
+        <v>0.06100697911028458</v>
       </c>
       <c r="Y19">
-        <v>-0.1604363871498511</v>
+        <v>-0.01244928680259227</v>
       </c>
       <c r="Z19">
-        <v>0.04614066843364148</v>
+        <v>2.149820420728579</v>
       </c>
       <c r="AA19">
         <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.07101661403330851</v>
+        <v>0.06030392103913192</v>
       </c>
       <c r="AC19">
-        <v>-0.07101661403330851</v>
+        <v>-0.06030392103913192</v>
       </c>
       <c r="AD19">
-        <v>13.9</v>
+        <v>0.273</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>13.9</v>
+        <v>0.273</v>
       </c>
       <c r="AG19">
-        <v>-6.799999999999999</v>
+        <v>-7.417000000000001</v>
       </c>
       <c r="AH19">
-        <v>0.317351598173516</v>
+        <v>0.05370843989769822</v>
       </c>
       <c r="AI19">
-        <v>0.1069230769230769</v>
+        <v>0.02443390315940213</v>
       </c>
       <c r="AJ19">
-        <v>-0.2943722943722943</v>
+        <v>2.845032604526275</v>
       </c>
       <c r="AK19">
-        <v>-0.06221408966148215</v>
+        <v>-2.12948607522251</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2793,7 +2760,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Power Financial Group Limited (SEHK:397)</t>
+          <t>Imagi International Holdings Limited (SEHK:585)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2801,9 +2768,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D20">
-        <v>0.275</v>
-      </c>
       <c r="G20">
         <v>0</v>
       </c>
@@ -2817,10 +2781,10 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>-4.33</v>
+        <v>-3</v>
       </c>
       <c r="L20">
-        <v>-0.4369323915237134</v>
+        <v>-0.6072874493927125</v>
       </c>
       <c r="M20">
         <v>-0</v>
@@ -2844,55 +2808,55 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>31.5</v>
+        <v>14.8</v>
       </c>
       <c r="V20">
-        <v>0.4715568862275449</v>
+        <v>0.09475032010243278</v>
       </c>
       <c r="W20">
-        <v>-0.02117359413202934</v>
+        <v>-0.02932551319648094</v>
       </c>
       <c r="X20">
-        <v>0.07188856434620605</v>
+        <v>0.06010043459379457</v>
       </c>
       <c r="Y20">
-        <v>-0.09306215847823539</v>
+        <v>-0.08942594779027552</v>
       </c>
       <c r="Z20">
-        <v>0.05199588650100739</v>
+        <v>0.05989839098856596</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.07106555516844536</v>
+        <v>0.06036985637591248</v>
       </c>
       <c r="AC20">
-        <v>-0.07106555516844536</v>
+        <v>-0.06036985637591248</v>
       </c>
       <c r="AD20">
-        <v>3.47</v>
+        <v>0.867</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>3.47</v>
+        <v>0.867</v>
       </c>
       <c r="AG20">
-        <v>-28.03</v>
+        <v>-13.933</v>
       </c>
       <c r="AH20">
-        <v>0.04938095915753523</v>
+        <v>0.00551993735157608</v>
       </c>
       <c r="AI20">
-        <v>0.01707929320273662</v>
+        <v>0.007456974033904718</v>
       </c>
       <c r="AJ20">
-        <v>-0.7229816868712924</v>
+        <v>-0.0979355718473012</v>
       </c>
       <c r="AK20">
-        <v>-0.1632783829440205</v>
+        <v>-0.1373155804350183</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2909,7 +2873,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pinestone Capital Limited (SEHK:804)</t>
+          <t>Minerva Group Holding Limited (SEHK:397)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2918,7 +2882,7 @@
         </is>
       </c>
       <c r="D21">
-        <v>-0.172</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2933,10 +2897,10 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>-1.03</v>
+        <v>-24.2</v>
       </c>
       <c r="L21">
-        <v>-0.4639639639639639</v>
+        <v>-1.951612903225806</v>
       </c>
       <c r="M21">
         <v>-0</v>
@@ -2960,55 +2924,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>8.68</v>
+        <v>26.2</v>
       </c>
       <c r="V21">
-        <v>0.7233333333333333</v>
+        <v>0.6022988505747127</v>
       </c>
       <c r="W21">
-        <v>-0.03976833976833977</v>
+        <v>-0.1213032581453634</v>
       </c>
       <c r="X21">
-        <v>0.07109116707611454</v>
+        <v>0.06128009847302511</v>
       </c>
       <c r="Y21">
-        <v>-0.1108595068444543</v>
+        <v>-0.1825833566183885</v>
       </c>
       <c r="Z21">
-        <v>0.1070911722141824</v>
+        <v>0.0723230273019428</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.0713337204556838</v>
+        <v>0.06038041905717925</v>
       </c>
       <c r="AC21">
-        <v>-0.0713337204556838</v>
+        <v>-0.06038041905717925</v>
       </c>
       <c r="AD21">
-        <v>0.262</v>
+        <v>3.14</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>0.262</v>
+        <v>3.14</v>
       </c>
       <c r="AG21">
-        <v>-8.417999999999999</v>
+        <v>-23.06</v>
       </c>
       <c r="AH21">
-        <v>0.02136682433534497</v>
+        <v>0.06732418524871356</v>
       </c>
       <c r="AI21">
-        <v>0.01053817070227657</v>
+        <v>0.01746967842439079</v>
       </c>
       <c r="AJ21">
-        <v>-2.350083752093802</v>
+        <v>-1.128180039138943</v>
       </c>
       <c r="AK21">
-        <v>-0.5202076381164256</v>
+        <v>-0.1501888758629673</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3025,7 +2989,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bright Smart Securities &amp; Commodities Group Limited (SEHK:1428)</t>
+          <t>Arta TechFin Corporation Limited (SEHK:279)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3033,104 +2997,80 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D22">
-        <v>0.0699</v>
-      </c>
-      <c r="E22">
-        <v>0.0727</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
       <c r="K22">
-        <v>63.4</v>
-      </c>
-      <c r="L22">
-        <v>0.4847094801223241</v>
+        <v>-12.6</v>
       </c>
       <c r="M22">
-        <v>21.6</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.05114847264977505</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>0.3406940063091483</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>21.6</v>
+        <v>-0</v>
       </c>
       <c r="Q22">
-        <v>0.05114847264977505</v>
+        <v>-0</v>
       </c>
       <c r="R22">
-        <v>0.3406940063091483</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
-        <v>72.7</v>
+        <v>7.13</v>
       </c>
       <c r="V22">
-        <v>0.1721524982240114</v>
+        <v>0.07094527363184079</v>
       </c>
       <c r="W22">
-        <v>0.2238700564971751</v>
+        <v>-3.727810650887574</v>
       </c>
       <c r="X22">
-        <v>0.1051952054039374</v>
+        <v>0.06153826006012154</v>
       </c>
       <c r="Y22">
-        <v>0.1186748510932378</v>
+        <v>-3.789348910947695</v>
       </c>
       <c r="Z22">
-        <v>0.1102866779089376</v>
+        <v>0</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.07141285662809255</v>
+        <v>0.06045073086073779</v>
       </c>
       <c r="AC22">
-        <v>-0.07141285662809255</v>
+        <v>-0.06045073086073779</v>
       </c>
       <c r="AD22">
-        <v>553.1</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>553.1</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AG22">
-        <v>480.4</v>
+        <v>1.590000000000001</v>
       </c>
       <c r="AH22">
-        <v>0.5670494156243592</v>
+        <v>0.07983885735213332</v>
       </c>
       <c r="AI22">
-        <v>0.6315368805663394</v>
+        <v>0.7254575707154743</v>
       </c>
       <c r="AJ22">
-        <v>0.5321812340755512</v>
+        <v>0.01557449309432854</v>
       </c>
       <c r="AK22">
-        <v>0.5981820445772631</v>
+        <v>0.325153374233129</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3147,7 +3087,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GoFintech Innovation Limited (SEHK:290)</t>
+          <t>Orient Securities International Holdings Limited (SEHK:8001)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3155,26 +3095,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D23">
-        <v>-0.0737</v>
-      </c>
-      <c r="G23">
-        <v>0</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>0.0001694645768646301</v>
-      </c>
-      <c r="J23">
-        <v>0.0001694645768646301</v>
-      </c>
       <c r="K23">
-        <v>-9.039999999999999</v>
-      </c>
-      <c r="L23">
-        <v>-1.887265135699373</v>
+        <v>-13.5</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3198,67 +3120,61 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>18</v>
+        <v>0.466</v>
       </c>
       <c r="V23">
-        <v>0.4736842105263158</v>
+        <v>0.4123893805309735</v>
       </c>
       <c r="W23">
-        <v>-0.2404255319148936</v>
+        <v>-0.2896995708154506</v>
       </c>
       <c r="X23">
-        <v>0.07407458068677203</v>
+        <v>0.06120853409212233</v>
       </c>
       <c r="Y23">
-        <v>-0.3145001126016656</v>
+        <v>-0.350908104907573</v>
       </c>
       <c r="Z23">
-        <v>0.125573662819179</v>
+        <v>0</v>
       </c>
       <c r="AA23">
-        <v>2.12802876349939e-05</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.07146338117797854</v>
+        <v>0.0605027616812325</v>
       </c>
       <c r="AC23">
-        <v>-0.07144210089034354</v>
+        <v>-0.0605027616812325</v>
       </c>
       <c r="AD23">
-        <v>5.11</v>
+        <v>0.077</v>
       </c>
       <c r="AE23">
-        <v>0.0009413233840921099</v>
+        <v>0</v>
       </c>
       <c r="AF23">
-        <v>5.110941323384092</v>
+        <v>0.077</v>
       </c>
       <c r="AG23">
-        <v>-12.88905867661591</v>
+        <v>-0.389</v>
       </c>
       <c r="AH23">
-        <v>0.1185532295629052</v>
+        <v>0.06379453189726596</v>
       </c>
       <c r="AI23">
-        <v>0.1303447749757565</v>
+        <v>0.002534812522632254</v>
       </c>
       <c r="AJ23">
-        <v>-0.5132845682934718</v>
+        <v>-0.5249662618083671</v>
       </c>
       <c r="AK23">
-        <v>-0.6076608520153846</v>
+        <v>-0.01300524890508509</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
         <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>5110</v>
-      </c>
-      <c r="AP23">
-        <v>-12889.05867661591</v>
       </c>
     </row>
     <row r="24">
@@ -3269,7 +3185,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Value Convergence Holdings Limited (SEHK:821)</t>
+          <t>Cinda International Holdings Limited (SEHK:111)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3278,7 +3194,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>-0.08310000000000001</v>
+        <v>-0.133</v>
+      </c>
+      <c r="E24">
+        <v>-0.228</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3293,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>-18.8</v>
+        <v>2.21</v>
       </c>
       <c r="L24">
-        <v>-1.693693693693694</v>
+        <v>0.1407643312101911</v>
       </c>
       <c r="M24">
         <v>-0</v>
@@ -3305,7 +3224,7 @@
         <v>-0</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P24">
         <v>-0</v>
@@ -3314,61 +3233,61 @@
         <v>-0</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
       <c r="U24">
-        <v>6.54</v>
+        <v>62.2</v>
       </c>
       <c r="V24">
-        <v>0.1635</v>
+        <v>2.853211009174312</v>
       </c>
       <c r="W24">
-        <v>-0.1557580778790389</v>
+        <v>0.01818930041152263</v>
       </c>
       <c r="X24">
-        <v>0.07310146814793225</v>
+        <v>0.1092155129863469</v>
       </c>
       <c r="Y24">
-        <v>-0.2288595460269712</v>
+        <v>-0.09102621257482427</v>
       </c>
       <c r="Z24">
-        <v>0.09940001790991314</v>
+        <v>0.1133574007220217</v>
       </c>
       <c r="AA24">
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.07150938020768809</v>
+        <v>0.06056501990069586</v>
       </c>
       <c r="AC24">
-        <v>-0.07150938020768809</v>
+        <v>-0.06056501990069586</v>
       </c>
       <c r="AD24">
-        <v>3.91</v>
+        <v>60.6</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>3.91</v>
+        <v>60.6</v>
       </c>
       <c r="AG24">
-        <v>-2.63</v>
+        <v>-1.600000000000001</v>
       </c>
       <c r="AH24">
-        <v>0.08904577544978366</v>
+        <v>0.7354368932038835</v>
       </c>
       <c r="AI24">
-        <v>0.03426518271842958</v>
+        <v>0.3355481727574751</v>
       </c>
       <c r="AJ24">
-        <v>-0.07037730800107038</v>
+        <v>-0.07920792079207928</v>
       </c>
       <c r="AK24">
-        <v>-0.02444919587245514</v>
+        <v>-0.01351351351351352</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3385,7 +3304,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PF Group Holdings Limited (SEHK:8221)</t>
+          <t>Shenwan Hongyuan Group Co., Ltd. (SZSE:000166)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3394,7 +3313,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.346</v>
+        <v>0.0793</v>
+      </c>
+      <c r="E25">
+        <v>-0.07969999999999999</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3409,82 +3331,85 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>-3.29</v>
+        <v>391.6</v>
       </c>
       <c r="L25">
-        <v>-3.046296296296296</v>
+        <v>0.1545504775436104</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>1108.1</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0.07607337534840933</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>2.829673135852911</v>
       </c>
       <c r="P25">
-        <v>-0</v>
+        <v>1108.1</v>
       </c>
       <c r="Q25">
-        <v>-0</v>
+        <v>0.07607337534840933</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.829673135852911</v>
       </c>
       <c r="S25">
         <v>0</v>
       </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
       <c r="U25">
-        <v>10.6</v>
+        <v>3543.9</v>
       </c>
       <c r="V25">
-        <v>1.118143459915612</v>
+        <v>0.2432961239032829</v>
       </c>
       <c r="W25">
-        <v>-0.1495454545454545</v>
+        <v>0.02874719208351074</v>
       </c>
       <c r="X25">
-        <v>0.07203814740009798</v>
+        <v>0.1150065906522282</v>
       </c>
       <c r="Y25">
-        <v>-0.2215836019455525</v>
+        <v>-0.08625939856871745</v>
       </c>
       <c r="Z25">
-        <v>0.11281729865246</v>
+        <v>0.04513986624433035</v>
       </c>
       <c r="AA25">
         <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.07163621102767598</v>
+        <v>0.06058114690185731</v>
       </c>
       <c r="AC25">
-        <v>-0.07163621102767598</v>
+        <v>-0.06058114690185731</v>
       </c>
       <c r="AD25">
-        <v>0.546</v>
+        <v>45256.1</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0.546</v>
+        <v>45256.1</v>
       </c>
       <c r="AG25">
-        <v>-10.054</v>
+        <v>41712.2</v>
       </c>
       <c r="AH25">
-        <v>0.05445840813883902</v>
+        <v>0.7565088604082424</v>
       </c>
       <c r="AI25">
-        <v>0.02866743673212223</v>
+        <v>0.7253928614934828</v>
       </c>
       <c r="AJ25">
-        <v>17.51567944250872</v>
+        <v>0.7411760106897141</v>
       </c>
       <c r="AK25">
-        <v>-1.190385981529718</v>
+        <v>0.7088546933018378</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3501,7 +3426,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cinda International Holdings Limited (SEHK:111)</t>
+          <t>Value Convergence Holdings Limited (SEHK:821)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3510,7 +3435,7 @@
         </is>
       </c>
       <c r="D26">
-        <v>-0.079</v>
+        <v>0.239</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3525,85 +3450,82 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>-4.46</v>
+        <v>-32</v>
       </c>
       <c r="L26">
-        <v>-0.2372340425531915</v>
+        <v>-3.336809176225235</v>
       </c>
       <c r="M26">
-        <v>4.09</v>
+        <v>-0</v>
       </c>
       <c r="N26">
-        <v>0.1381756756756757</v>
+        <v>-0</v>
       </c>
       <c r="O26">
-        <v>-0.9170403587443946</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>4.09</v>
+        <v>-0</v>
       </c>
       <c r="Q26">
-        <v>0.1381756756756757</v>
+        <v>-0</v>
       </c>
       <c r="R26">
-        <v>-0.9170403587443946</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <v>0</v>
       </c>
-      <c r="T26">
-        <v>0</v>
-      </c>
       <c r="U26">
-        <v>105.2</v>
+        <v>3.22</v>
       </c>
       <c r="V26">
-        <v>3.554054054054054</v>
+        <v>0.06924731182795699</v>
       </c>
       <c r="W26">
-        <v>-0.03425499231950845</v>
+        <v>-0.2903811252268603</v>
       </c>
       <c r="X26">
-        <v>0.1798339803211876</v>
+        <v>0.06176112748018357</v>
       </c>
       <c r="Y26">
-        <v>-0.214088972640696</v>
+        <v>-0.3521422527070439</v>
       </c>
       <c r="Z26">
-        <v>0.09157330735509012</v>
+        <v>0.08936475543503584</v>
       </c>
       <c r="AA26">
         <v>0</v>
       </c>
       <c r="AB26">
-        <v>0.07179046812762324</v>
+        <v>0.06071134227968504</v>
       </c>
       <c r="AC26">
-        <v>-0.07179046812762324</v>
+        <v>-0.06071134227968504</v>
       </c>
       <c r="AD26">
-        <v>122.2</v>
+        <v>4.62</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>122.2</v>
+        <v>4.62</v>
       </c>
       <c r="AG26">
-        <v>17</v>
+        <v>1.4</v>
       </c>
       <c r="AH26">
-        <v>0.8050065876152832</v>
+        <v>0.09037558685446009</v>
       </c>
       <c r="AI26">
-        <v>0.5014361920393927</v>
+        <v>0.05092592592592593</v>
       </c>
       <c r="AJ26">
-        <v>0.3648068669527897</v>
+        <v>0.02922755741127349</v>
       </c>
       <c r="AK26">
-        <v>0.1227436823104693</v>
+        <v>0.016</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3620,7 +3542,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fu Shek Financial Holdings Limited (SEHK:2263)</t>
+          <t>CL Group (Holdings) Limited (SEHK:8098)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3628,23 +3550,8 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
       <c r="K27">
-        <v>1.63</v>
-      </c>
-      <c r="L27">
-        <v>0.3646532438478747</v>
+        <v>-4.31</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3653,7 +3560,7 @@
         <v>-0</v>
       </c>
       <c r="O27">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P27">
         <v>-0</v>
@@ -3662,61 +3569,61 @@
         <v>-0</v>
       </c>
       <c r="R27">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="U27">
-        <v>15.2</v>
+        <v>2.14</v>
       </c>
       <c r="V27">
-        <v>0.628099173553719</v>
+        <v>0.1725806451612903</v>
       </c>
       <c r="W27">
-        <v>0.03781902552204176</v>
+        <v>-0.1550359712230216</v>
       </c>
       <c r="X27">
-        <v>0.07497747072755753</v>
+        <v>0.06324310774493699</v>
       </c>
       <c r="Y27">
-        <v>-0.03715844520551578</v>
+        <v>-0.2182790789679586</v>
       </c>
       <c r="Z27">
-        <v>0.14030131826742</v>
+        <v>0</v>
       </c>
       <c r="AA27">
         <v>0</v>
       </c>
       <c r="AB27">
-        <v>0.07212732307824483</v>
+        <v>0.06121638840460252</v>
       </c>
       <c r="AC27">
-        <v>-0.07212732307824483</v>
+        <v>-0.06121638840460252</v>
       </c>
       <c r="AD27">
-        <v>4.08</v>
+        <v>2.27</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>4.08</v>
+        <v>2.27</v>
       </c>
       <c r="AG27">
-        <v>-11.12</v>
+        <v>0.1299999999999999</v>
       </c>
       <c r="AH27">
-        <v>0.1442715700141443</v>
+        <v>0.1547375596455351</v>
       </c>
       <c r="AI27">
-        <v>0.08415841584158416</v>
+        <v>0.08808692277842453</v>
       </c>
       <c r="AJ27">
-        <v>-0.8501529051987767</v>
+        <v>0.01037509976057461</v>
       </c>
       <c r="AK27">
-        <v>-0.3341346153846154</v>
+        <v>0.005501481168006766</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -3733,7 +3640,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Scully Royalty Ltd. (NYSE:SRL)</t>
+          <t>Emperor Capital Group Limited (SEHK:717)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3742,7 +3649,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>-0.374</v>
+        <v>-0.277</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3757,85 +3664,82 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>1.33</v>
+        <v>-20.5</v>
       </c>
       <c r="L28">
-        <v>0.02923076923076923</v>
+        <v>-0.702054794520548</v>
       </c>
       <c r="M28">
-        <v>6.68</v>
+        <v>-0</v>
       </c>
       <c r="N28">
-        <v>0.0584426946631671</v>
+        <v>-0</v>
       </c>
       <c r="O28">
-        <v>5.022556390977443</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>6.68</v>
+        <v>-0</v>
       </c>
       <c r="Q28">
-        <v>0.0584426946631671</v>
+        <v>-0</v>
       </c>
       <c r="R28">
-        <v>5.022556390977443</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
       <c r="U28">
-        <v>47.5</v>
+        <v>128</v>
       </c>
       <c r="V28">
-        <v>0.4155730533683289</v>
+        <v>3.615819209039548</v>
       </c>
       <c r="W28">
-        <v>0.004516129032258065</v>
+        <v>-0.04532390006632766</v>
       </c>
       <c r="X28">
-        <v>0.07778758349893179</v>
+        <v>0.07480535441280216</v>
       </c>
       <c r="Y28">
-        <v>-0.07327145446667373</v>
+        <v>-0.1201292544791298</v>
       </c>
       <c r="Z28">
-        <v>0.1581508515815085</v>
+        <v>0.07329317269076305</v>
       </c>
       <c r="AA28">
         <v>0</v>
       </c>
       <c r="AB28">
-        <v>0.07224063493625468</v>
+        <v>0.06256067823673089</v>
       </c>
       <c r="AC28">
-        <v>-0.07224063493625468</v>
+        <v>-0.06256067823673089</v>
       </c>
       <c r="AD28">
-        <v>31.4</v>
+        <v>29.6</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>31.4</v>
+        <v>29.6</v>
       </c>
       <c r="AG28">
-        <v>-16.1</v>
+        <v>-98.40000000000001</v>
       </c>
       <c r="AH28">
-        <v>0.2155113246396706</v>
+        <v>0.4553846153846154</v>
       </c>
       <c r="AI28">
-        <v>0.1006087792374239</v>
+        <v>0.06401384083044982</v>
       </c>
       <c r="AJ28">
-        <v>-0.1639511201629328</v>
+        <v>1.561904761904762</v>
       </c>
       <c r="AK28">
-        <v>-0.06084656084656086</v>
+        <v>-0.2942583732057417</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3867,103 +3771,97 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>0.001095995077339146</v>
+        <v>0</v>
       </c>
       <c r="J29">
-        <v>0.001095995077339146</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>-3.19</v>
+        <v>0.172</v>
       </c>
       <c r="L29">
-        <v>-0.5379426644182125</v>
+        <v>0.01563636363636364</v>
       </c>
       <c r="M29">
-        <v>0.139</v>
+        <v>1.218</v>
       </c>
       <c r="N29">
-        <v>0.0102962962962963</v>
+        <v>0.1379388448471121</v>
       </c>
       <c r="O29">
-        <v>-0.04357366771159875</v>
+        <v>7.081395348837209</v>
       </c>
       <c r="P29">
-        <v>-0</v>
+        <v>1.218</v>
       </c>
       <c r="Q29">
-        <v>-0</v>
+        <v>0.1379388448471121</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>7.081395348837209</v>
       </c>
       <c r="S29">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>6.19</v>
+        <v>5.48</v>
       </c>
       <c r="V29">
-        <v>0.4585185185185185</v>
+        <v>0.6206115515288788</v>
       </c>
       <c r="W29">
-        <v>-0.1369098712446352</v>
+        <v>0.0086</v>
       </c>
       <c r="X29">
-        <v>0.07994297211804313</v>
+        <v>0.06918489214292468</v>
       </c>
       <c r="Y29">
-        <v>-0.2168528433626783</v>
+        <v>-0.06058489214292469</v>
       </c>
       <c r="Z29">
-        <v>0.2292451586453085</v>
+        <v>0.5910800644814616</v>
       </c>
       <c r="AA29">
-        <v>0.0002512515653790896</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>0.07345131728615643</v>
+        <v>0.06268219047239426</v>
       </c>
       <c r="AC29">
-        <v>-0.07320006572077735</v>
+        <v>-0.06268219047239426</v>
       </c>
       <c r="AD29">
-        <v>4.8</v>
+        <v>4.58</v>
       </c>
       <c r="AE29">
-        <v>0.007503745956894336</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>4.807503745956894</v>
+        <v>4.58</v>
       </c>
       <c r="AG29">
-        <v>-1.382496254043106</v>
+        <v>-0.9000000000000004</v>
       </c>
       <c r="AH29">
-        <v>0.2625974470724117</v>
+        <v>0.3415361670395227</v>
       </c>
       <c r="AI29">
-        <v>0.1930142737301513</v>
+        <v>0.1840836012861736</v>
       </c>
       <c r="AJ29">
-        <v>-0.1140908460213505</v>
+        <v>-0.1134930643127365</v>
       </c>
       <c r="AK29">
-        <v>-0.07386114477694358</v>
+        <v>-0.04639175257731961</v>
       </c>
       <c r="AL29">
         <v>0</v>
       </c>
       <c r="AM29">
         <v>0</v>
-      </c>
-      <c r="AN29">
-        <v>600</v>
-      </c>
-      <c r="AP29">
-        <v>-172.8120317553883</v>
       </c>
     </row>
     <row r="30">
@@ -3974,7 +3872,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CL Group (Holdings) Limited (SEHK:8098)</t>
+          <t>First Shanghai Investments Limited (SEHK:227)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3983,7 +3881,7 @@
         </is>
       </c>
       <c r="D30">
-        <v>-0.222</v>
+        <v>-0.09029999999999999</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3998,91 +3896,91 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>-0.529</v>
+        <v>-3.09</v>
       </c>
       <c r="L30">
-        <v>-0.2449074074074074</v>
+        <v>-0.0819628647214854</v>
       </c>
       <c r="M30">
-        <v>1.4</v>
+        <v>-0</v>
       </c>
       <c r="N30">
-        <v>0.09523809523809523</v>
+        <v>-0</v>
       </c>
       <c r="O30">
-        <v>-2.646502835538752</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>1.4</v>
+        <v>-0</v>
       </c>
       <c r="Q30">
-        <v>0.09523809523809523</v>
+        <v>-0</v>
       </c>
       <c r="R30">
-        <v>-2.646502835538752</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <v>0</v>
       </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
       <c r="U30">
-        <v>0.491</v>
+        <v>32.7</v>
       </c>
       <c r="V30">
-        <v>0.03340136054421769</v>
+        <v>1.015527950310559</v>
       </c>
       <c r="W30">
-        <v>-0.01763333333333333</v>
+        <v>-0.01019465522929726</v>
       </c>
       <c r="X30">
-        <v>0.08070885379623675</v>
+        <v>0.07693624783884484</v>
       </c>
       <c r="Y30">
-        <v>-0.09834218712957009</v>
+        <v>-0.0871309030681421</v>
       </c>
       <c r="Z30">
-        <v>0.06147191075189255</v>
+        <v>0.1275372124492558</v>
       </c>
       <c r="AA30">
         <v>0</v>
       </c>
       <c r="AB30">
-        <v>0.0736236184685794</v>
+        <v>0.06274891695985016</v>
       </c>
       <c r="AC30">
-        <v>-0.0736236184685794</v>
+        <v>-0.06274891695985016</v>
       </c>
       <c r="AD30">
-        <v>5.66</v>
+        <v>30.8</v>
       </c>
       <c r="AE30">
         <v>0</v>
       </c>
       <c r="AF30">
-        <v>5.66</v>
+        <v>30.8</v>
       </c>
       <c r="AG30">
-        <v>5.169</v>
+        <v>-1.900000000000002</v>
       </c>
       <c r="AH30">
-        <v>0.2779960707269155</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="AI30">
-        <v>0.169157202630006</v>
+        <v>0.09302325581395349</v>
       </c>
       <c r="AJ30">
-        <v>0.2601540087573607</v>
+        <v>-0.06270627062706277</v>
       </c>
       <c r="AK30">
-        <v>0.1567836452425005</v>
+        <v>-0.006367292225201079</v>
       </c>
       <c r="AL30">
         <v>0</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>-10.8</v>
+      </c>
+      <c r="AQ30">
+        <v>-0</v>
       </c>
     </row>
     <row r="31">
@@ -4093,7 +3991,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Emperor Capital Group Limited (SEHK:717)</t>
+          <t>Bright Smart Securities &amp; Commodities Group Limited (SEHK:1428)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4102,7 +4000,10 @@
         </is>
       </c>
       <c r="D31">
-        <v>-0.319</v>
+        <v>0.0167</v>
+      </c>
+      <c r="E31">
+        <v>0.0501</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -4117,82 +4018,85 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>-38.1</v>
+        <v>88.5</v>
       </c>
       <c r="L31">
-        <v>-1.780373831775701</v>
+        <v>0.620617110799439</v>
       </c>
       <c r="M31">
-        <v>-0</v>
+        <v>260.1</v>
       </c>
       <c r="N31">
-        <v>-0</v>
+        <v>0.8312559923298179</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>2.938983050847458</v>
       </c>
       <c r="P31">
-        <v>-0</v>
+        <v>260.1</v>
       </c>
       <c r="Q31">
-        <v>-0</v>
+        <v>0.8312559923298179</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.938983050847458</v>
       </c>
       <c r="S31">
         <v>0</v>
       </c>
+      <c r="T31">
+        <v>0</v>
+      </c>
       <c r="U31">
-        <v>109.7</v>
+        <v>51.2</v>
       </c>
       <c r="V31">
-        <v>1.692901234567901</v>
+        <v>0.1636305528922979</v>
       </c>
       <c r="W31">
-        <v>-0.07704752275025278</v>
+        <v>0.2742485280446235</v>
       </c>
       <c r="X31">
-        <v>0.09331554928756736</v>
+        <v>0.09770692793459464</v>
       </c>
       <c r="Y31">
-        <v>-0.1703630720378201</v>
+        <v>0.1765416001100289</v>
       </c>
       <c r="Z31">
-        <v>0.04304968819151075</v>
+        <v>0.1775619474536173</v>
       </c>
       <c r="AA31">
         <v>0</v>
       </c>
       <c r="AB31">
-        <v>0.0742220877077111</v>
+        <v>0.06382537686624987</v>
       </c>
       <c r="AC31">
-        <v>-0.0742220877077111</v>
+        <v>-0.06382537686624987</v>
       </c>
       <c r="AD31">
-        <v>55.8</v>
+        <v>666.4</v>
       </c>
       <c r="AE31">
         <v>0</v>
       </c>
       <c r="AF31">
-        <v>55.8</v>
+        <v>666.4</v>
       </c>
       <c r="AG31">
-        <v>-53.90000000000001</v>
+        <v>615.1999999999999</v>
       </c>
       <c r="AH31">
-        <v>0.4626865671641791</v>
+        <v>0.6804860614724804</v>
       </c>
       <c r="AI31">
-        <v>0.1098209013973627</v>
+        <v>0.8144707895380102</v>
       </c>
       <c r="AJ31">
-        <v>-4.944954128440371</v>
+        <v>0.6628596056459433</v>
       </c>
       <c r="AK31">
-        <v>-0.1352911646586346</v>
+        <v>0.8020860495436766</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -4209,7 +4113,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>First Shanghai Investments Limited (SEHK:227)</t>
+          <t>CASH Financial Services Group Limited (SEHK:510)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4218,7 +4122,7 @@
         </is>
       </c>
       <c r="D32">
-        <v>0.012</v>
+        <v>-0.157</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -4233,10 +4137,10 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>-18</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L32">
-        <v>-0.3296703296703297</v>
+        <v>-1.170731707317073</v>
       </c>
       <c r="M32">
         <v>-0</v>
@@ -4260,64 +4164,61 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>42.8</v>
+        <v>21.6</v>
       </c>
       <c r="V32">
-        <v>1.185595567867036</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="W32">
-        <v>-0.05436424041075204</v>
+        <v>-0.1834394904458599</v>
       </c>
       <c r="X32">
-        <v>0.09640655531115255</v>
+        <v>0.08297496994511061</v>
       </c>
       <c r="Y32">
-        <v>-0.1507707957219046</v>
+        <v>-0.2664144603909705</v>
       </c>
       <c r="Z32">
-        <v>0.07382368848025959</v>
+        <v>0.2435643564356436</v>
       </c>
       <c r="AA32">
         <v>0</v>
       </c>
       <c r="AB32">
-        <v>0.07447629694207003</v>
+        <v>0.06443387366571962</v>
       </c>
       <c r="AC32">
-        <v>-0.07447629694207003</v>
+        <v>-0.06443387366571962</v>
       </c>
       <c r="AD32">
-        <v>35.3</v>
+        <v>21.8</v>
       </c>
       <c r="AE32">
         <v>0</v>
       </c>
       <c r="AF32">
-        <v>35.3</v>
+        <v>21.8</v>
       </c>
       <c r="AG32">
-        <v>-7.5</v>
+        <v>0.1999999999999993</v>
       </c>
       <c r="AH32">
-        <v>0.4943977591036414</v>
+        <v>0.5647668393782384</v>
       </c>
       <c r="AI32">
-        <v>0.1016119746689695</v>
+        <v>0.3556280587275694</v>
       </c>
       <c r="AJ32">
-        <v>-0.2622377622377622</v>
+        <v>0.0117647058823529</v>
       </c>
       <c r="AK32">
-        <v>-0.02462245567957978</v>
+        <v>0.005037783375314843</v>
       </c>
       <c r="AL32">
         <v>0</v>
       </c>
       <c r="AM32">
-        <v>-2.7</v>
-      </c>
-      <c r="AQ32">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -4328,7 +4229,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kingston Financial Group Limited (SEHK:1031)</t>
+          <t>Huarong International Financial Holdings Limited (SEHK:993)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4336,110 +4237,89 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D33">
-        <v>-0.257</v>
-      </c>
-      <c r="E33">
-        <v>-0.515</v>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
       <c r="K33">
-        <v>5.62</v>
-      </c>
-      <c r="L33">
-        <v>0.06946847960444993</v>
+        <v>-173.6</v>
       </c>
       <c r="M33">
-        <v>-0</v>
+        <v>259.1</v>
       </c>
       <c r="N33">
-        <v>-0</v>
+        <v>3.872944693572496</v>
       </c>
       <c r="O33">
-        <v>-0</v>
+        <v>-1.492511520737327</v>
       </c>
       <c r="P33">
-        <v>-0</v>
+        <v>43.8</v>
       </c>
       <c r="Q33">
-        <v>-0</v>
+        <v>0.6547085201793721</v>
       </c>
       <c r="R33">
-        <v>-0</v>
+        <v>-0.2523041474654378</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>215.3</v>
+      </c>
+      <c r="T33">
+        <v>0.8309532998842145</v>
       </c>
       <c r="U33">
-        <v>46.9</v>
+        <v>317.9</v>
       </c>
       <c r="V33">
-        <v>0.07389317787931306</v>
+        <v>4.751868460388639</v>
       </c>
       <c r="W33">
-        <v>0.00205785426583669</v>
+        <v>0.4262214583844832</v>
       </c>
       <c r="X33">
-        <v>0.1016119006543888</v>
+        <v>0.2675522215037962</v>
       </c>
       <c r="Y33">
-        <v>-0.09955404638855213</v>
+        <v>0.158669236880687</v>
       </c>
       <c r="Z33">
-        <v>0.04025877083851705</v>
+        <v>0</v>
       </c>
       <c r="AA33">
         <v>0</v>
       </c>
       <c r="AB33">
-        <v>0.07484271027074306</v>
+        <v>0.06517894412122036</v>
       </c>
       <c r="AC33">
-        <v>-0.07484271027074306</v>
+        <v>-0.06517894412122036</v>
       </c>
       <c r="AD33">
-        <v>745.4</v>
+        <v>784.3</v>
       </c>
       <c r="AE33">
         <v>0</v>
       </c>
       <c r="AF33">
-        <v>745.4</v>
+        <v>784.3</v>
       </c>
       <c r="AG33">
-        <v>698.5</v>
+        <v>466.4</v>
       </c>
       <c r="AH33">
-        <v>0.5401057894355482</v>
+        <v>0.92140507518797</v>
       </c>
       <c r="AI33">
-        <v>0.2205912817022284</v>
+        <v>1.272181670721817</v>
       </c>
       <c r="AJ33">
-        <v>0.5239273927392739</v>
+        <v>0.8745546596662291</v>
       </c>
       <c r="AK33">
-        <v>0.209621271232219</v>
+        <v>1.561955793703952</v>
       </c>
       <c r="AL33">
         <v>0</v>
       </c>
       <c r="AM33">
-        <v>-0.859</v>
-      </c>
-      <c r="AQ33">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4450,7 +4330,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Everbright Securities Company Limited (SHSE:601788)</t>
+          <t>BOCOM International Holdings Company Limited (SEHK:3329)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4458,50 +4338,26 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D34">
-        <v>0.07870000000000001</v>
-      </c>
-      <c r="E34">
-        <v>0.0464</v>
-      </c>
-      <c r="F34">
-        <v>2.214</v>
-      </c>
-      <c r="G34">
-        <v>0.04668169571672073</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
       <c r="K34">
-        <v>510.7</v>
-      </c>
-      <c r="L34">
-        <v>0.2808049705833837</v>
+        <v>-214.3</v>
       </c>
       <c r="M34">
-        <v>488.6</v>
+        <v>17.4</v>
       </c>
       <c r="N34">
-        <v>0.05492479597113245</v>
+        <v>0.1308270676691729</v>
       </c>
       <c r="O34">
-        <v>0.956726062267476</v>
+        <v>-0.08119458702753149</v>
       </c>
       <c r="P34">
-        <v>488.6</v>
+        <v>17.4</v>
       </c>
       <c r="Q34">
-        <v>0.05492479597113245</v>
+        <v>0.1308270676691729</v>
       </c>
       <c r="R34">
-        <v>0.956726062267476</v>
+        <v>-0.08119458702753149</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -4510,61 +4366,67 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>1768.8</v>
+        <v>196.7</v>
       </c>
       <c r="V34">
-        <v>0.1988354054722453</v>
+        <v>1.478947368421053</v>
       </c>
       <c r="W34">
-        <v>0.05712400170018567</v>
+        <v>-0.4226824457593689</v>
       </c>
       <c r="X34">
-        <v>0.1098778416623229</v>
+        <v>0.363326794119742</v>
       </c>
       <c r="Y34">
-        <v>-0.05275383996213726</v>
+        <v>-0.7860092398791109</v>
       </c>
       <c r="Z34">
-        <v>0.0856943613326988</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>7.510161308869935e-06</v>
       </c>
       <c r="AB34">
-        <v>0.07530552259430688</v>
+        <v>0.06531068179335187</v>
       </c>
       <c r="AC34">
-        <v>-0.07530552259430688</v>
+        <v>-0.06530317163204299</v>
       </c>
       <c r="AD34">
-        <v>13224.2</v>
+        <v>2278.7</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>0.02837187221616649</v>
       </c>
       <c r="AF34">
-        <v>13224.2</v>
+        <v>2278.728371872216</v>
       </c>
       <c r="AG34">
-        <v>11455.4</v>
+        <v>2082.028371872216</v>
       </c>
       <c r="AH34">
-        <v>0.5978390596745028</v>
+        <v>0.9448528277267176</v>
       </c>
       <c r="AI34">
-        <v>0.5910626810169128</v>
+        <v>0.8864479972313516</v>
       </c>
       <c r="AJ34">
-        <v>0.5628857266401982</v>
+        <v>0.9399556223798687</v>
       </c>
       <c r="AK34">
-        <v>0.555957835067557</v>
+        <v>0.8770392554979277</v>
       </c>
       <c r="AL34">
         <v>0</v>
       </c>
       <c r="AM34">
         <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>75956.66666666666</v>
+      </c>
+      <c r="AP34">
+        <v>69400.94572907388</v>
       </c>
     </row>
     <row r="35">
@@ -4575,7 +4437,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASH Financial Services Group Limited (SEHK:510)</t>
+          <t>Guotai Junan International Holdings Limited (SEHK:1788)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4584,7 +4446,10 @@
         </is>
       </c>
       <c r="D35">
-        <v>-0.129</v>
+        <v>-0.103</v>
+      </c>
+      <c r="E35">
+        <v>-0.494</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4599,82 +4464,85 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>-8.85</v>
+        <v>4.92</v>
       </c>
       <c r="L35">
-        <v>-0.9932659932659932</v>
+        <v>0.02450199203187251</v>
       </c>
       <c r="M35">
-        <v>-0</v>
+        <v>25.153</v>
       </c>
       <c r="N35">
-        <v>-0</v>
+        <v>0.03427773235213954</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>5.11239837398374</v>
       </c>
       <c r="P35">
-        <v>-0</v>
+        <v>24.4</v>
       </c>
       <c r="Q35">
-        <v>-0</v>
+        <v>0.03325156718451894</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>4.959349593495935</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>0.7530000000000001</v>
+      </c>
+      <c r="T35">
+        <v>0.02993678686438994</v>
       </c>
       <c r="U35">
-        <v>38.5</v>
+        <v>1527.6</v>
       </c>
       <c r="V35">
-        <v>2.305389221556887</v>
+        <v>2.081766148814391</v>
       </c>
       <c r="W35">
-        <v>-0.1574733096085409</v>
+        <v>0.002526964560862866</v>
       </c>
       <c r="X35">
-        <v>0.1049216309206561</v>
+        <v>0.2592725725744331</v>
       </c>
       <c r="Y35">
-        <v>-0.262394940529197</v>
+        <v>-0.2567456080135703</v>
       </c>
       <c r="Z35">
-        <v>0.0648</v>
+        <v>0.02083830595365345</v>
       </c>
       <c r="AA35">
         <v>0</v>
       </c>
       <c r="AB35">
-        <v>0.07683618249531021</v>
+        <v>0.06618509701865799</v>
       </c>
       <c r="AC35">
-        <v>-0.07683618249531021</v>
+        <v>-0.06618509701865799</v>
       </c>
       <c r="AD35">
-        <v>21.7</v>
+        <v>8259.5</v>
       </c>
       <c r="AE35">
         <v>0</v>
       </c>
       <c r="AF35">
-        <v>21.7</v>
+        <v>8259.5</v>
       </c>
       <c r="AG35">
-        <v>-16.8</v>
+        <v>6731.9</v>
       </c>
       <c r="AH35">
-        <v>0.5651041666666666</v>
+        <v>0.9184059244103945</v>
       </c>
       <c r="AI35">
-        <v>0.3104434907010014</v>
+        <v>0.8120956482410083</v>
       </c>
       <c r="AJ35">
-        <v>167.9999999999976</v>
+        <v>0.9017104893044189</v>
       </c>
       <c r="AK35">
-        <v>-0.535031847133758</v>
+        <v>0.778884646534768</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -4691,7 +4559,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Altus Holdings Limited (SEHK:8149)</t>
+          <t>Haitong International Securities Group Limited (SEHK:665)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4699,104 +4567,80 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D36">
-        <v>-0.0296</v>
-      </c>
-      <c r="E36">
-        <v>-0.234</v>
-      </c>
-      <c r="G36">
-        <v>0</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-      <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>0</v>
-      </c>
       <c r="K36">
-        <v>0.734</v>
-      </c>
-      <c r="L36">
-        <v>0.1124042879019908</v>
+        <v>-719.7</v>
       </c>
       <c r="M36">
-        <v>0.061</v>
+        <v>-0</v>
       </c>
       <c r="N36">
-        <v>0.004236111111111111</v>
+        <v>-0</v>
       </c>
       <c r="O36">
-        <v>0.08310626702997276</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>0.033</v>
+        <v>-0</v>
       </c>
       <c r="Q36">
-        <v>0.002291666666666667</v>
+        <v>-0</v>
       </c>
       <c r="R36">
-        <v>0.0449591280653951</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>0.028</v>
-      </c>
-      <c r="T36">
-        <v>0.4590163934426229</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>4.34</v>
+        <v>1237.2</v>
       </c>
       <c r="V36">
-        <v>0.3013888888888889</v>
+        <v>0.758506529336031</v>
       </c>
       <c r="W36">
-        <v>0.01267702936096718</v>
+        <v>-0.2201456013703659</v>
       </c>
       <c r="X36">
-        <v>0.1069235148304242</v>
+        <v>0.1294248536965458</v>
       </c>
       <c r="Y36">
-        <v>-0.09424648546945702</v>
+        <v>-0.3495704550669116</v>
       </c>
       <c r="Z36">
-        <v>0.08343981599795552</v>
+        <v>0</v>
       </c>
       <c r="AA36">
         <v>0</v>
       </c>
       <c r="AB36">
-        <v>0.07699107945781261</v>
+        <v>0.06625465610625107</v>
       </c>
       <c r="AC36">
-        <v>-0.07699107945781261</v>
+        <v>-0.06625465610625107</v>
       </c>
       <c r="AD36">
-        <v>19.8</v>
+        <v>6396.1</v>
       </c>
       <c r="AE36">
         <v>0</v>
       </c>
       <c r="AF36">
-        <v>19.8</v>
+        <v>6396.1</v>
       </c>
       <c r="AG36">
-        <v>15.46</v>
+        <v>5158.900000000001</v>
       </c>
       <c r="AH36">
-        <v>0.5789473684210527</v>
+        <v>0.7968033685469403</v>
       </c>
       <c r="AI36">
-        <v>0.2861271676300578</v>
+        <v>0.687922819622057</v>
       </c>
       <c r="AJ36">
-        <v>0.5177494976557268</v>
+        <v>0.7597790868924891</v>
       </c>
       <c r="AK36">
-        <v>0.2383595436324391</v>
+        <v>0.6400223311208982</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -4813,7 +4657,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Huarong International Financial Holdings Limited (SEHK:993)</t>
+          <t>Shenwan Hongyuan (H.K.) Limited (SEHK:218)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4821,89 +4665,110 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D37">
+        <v>-0.111</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0.00271133378724813</v>
+      </c>
+      <c r="J37">
+        <v>0.00271133378724813</v>
+      </c>
       <c r="K37">
-        <v>-341</v>
+        <v>-105.6</v>
+      </c>
+      <c r="L37">
+        <v>-2.693877551020408</v>
       </c>
       <c r="M37">
-        <v>14.2</v>
+        <v>-0</v>
       </c>
       <c r="N37">
-        <v>0.1059701492537313</v>
+        <v>-0</v>
       </c>
       <c r="O37">
-        <v>-0.04164222873900293</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>14.2</v>
+        <v>-0</v>
       </c>
       <c r="Q37">
-        <v>0.1059701492537313</v>
+        <v>-0</v>
       </c>
       <c r="R37">
-        <v>-0.04164222873900293</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
       </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
       <c r="U37">
-        <v>302.9</v>
+        <v>166.3</v>
       </c>
       <c r="V37">
-        <v>2.26044776119403</v>
+        <v>2.34555712270804</v>
       </c>
       <c r="W37">
-        <v>5.599343185550082</v>
+        <v>-0.2242514334253557</v>
       </c>
       <c r="X37">
-        <v>0.291900723894596</v>
+        <v>0.145156142940234</v>
       </c>
       <c r="Y37">
-        <v>5.307442461655486</v>
+        <v>-0.3694075763655896</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>0.03350932629316665</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>9.085496856658485e-05</v>
       </c>
       <c r="AB37">
-        <v>0.07767299013717192</v>
+        <v>0.06649851878926513</v>
       </c>
       <c r="AC37">
-        <v>-0.07767299013717192</v>
+        <v>-0.06640766382069854</v>
       </c>
       <c r="AD37">
-        <v>1120.3</v>
+        <v>340.9</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>0.1235785776993666</v>
       </c>
       <c r="AF37">
-        <v>1120.3</v>
+        <v>341.0235785776994</v>
       </c>
       <c r="AG37">
-        <v>817.4</v>
+        <v>174.7235785776994</v>
       </c>
       <c r="AH37">
-        <v>0.8931675037869728</v>
+        <v>0.8278806951405759</v>
       </c>
       <c r="AI37">
-        <v>1.279173327243663</v>
+        <v>0.4786137453281644</v>
       </c>
       <c r="AJ37">
-        <v>0.8591549295774648</v>
+        <v>0.7113469300848418</v>
       </c>
       <c r="AK37">
-        <v>1.426776051666958</v>
+        <v>0.3198755700598986</v>
       </c>
       <c r="AL37">
         <v>0</v>
       </c>
       <c r="AM37">
         <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>2602.290076335878</v>
+      </c>
+      <c r="AP37">
+        <v>1333.767775402285</v>
       </c>
     </row>
     <row r="38">
@@ -4914,7 +4779,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Southwest Securities International Securities Limited (SEHK:812)</t>
+          <t>South China Financial Holdings Limited (SEHK:619)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4922,8 +4787,26 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D38">
+        <v>-0.217</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
       <c r="K38">
-        <v>-33.9</v>
+        <v>-15.7</v>
+      </c>
+      <c r="L38">
+        <v>-1.912302070645554</v>
       </c>
       <c r="M38">
         <v>-0</v>
@@ -4947,55 +4830,55 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>23.2</v>
+        <v>5.17</v>
       </c>
       <c r="V38">
-        <v>1.705882352941176</v>
+        <v>0.6089517078916372</v>
       </c>
       <c r="W38">
-        <v>-0.911290322580645</v>
+        <v>-0.3030888030888031</v>
       </c>
       <c r="X38">
-        <v>0.309615135134122</v>
+        <v>0.1924158273459675</v>
       </c>
       <c r="Y38">
-        <v>-1.220905457714767</v>
+        <v>-0.4955046304347706</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>0.08015229913111395</v>
       </c>
       <c r="AA38">
         <v>0</v>
       </c>
       <c r="AB38">
-        <v>0.07773011292830197</v>
+        <v>0.06692371644472009</v>
       </c>
       <c r="AC38">
-        <v>-0.07773011292830197</v>
+        <v>-0.06692371644472009</v>
       </c>
       <c r="AD38">
-        <v>122.8</v>
+        <v>63.5</v>
       </c>
       <c r="AE38">
         <v>0</v>
       </c>
       <c r="AF38">
-        <v>122.8</v>
+        <v>63.5</v>
       </c>
       <c r="AG38">
-        <v>99.59999999999999</v>
+        <v>58.33</v>
       </c>
       <c r="AH38">
-        <v>0.9002932551319648</v>
+        <v>0.8820669537435756</v>
       </c>
       <c r="AI38">
-        <v>0.9815362481016705</v>
+        <v>0.6331006979062812</v>
       </c>
       <c r="AJ38">
-        <v>0.8798586572438163</v>
+        <v>0.872942232864412</v>
       </c>
       <c r="AK38">
-        <v>0.9773329408301442</v>
+        <v>0.613160937664249</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -5012,7 +4895,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BOCOM International Holdings Company Limited (SEHK:3329)</t>
+          <t>China Industrial Securities International Financial Group Limited (SEHK:6058)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5020,83 +4903,98 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D39">
+        <v>-0.128</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
       <c r="K39">
-        <v>-250.6</v>
+        <v>-4.7</v>
+      </c>
+      <c r="L39">
+        <v>-0.1039823008849557</v>
       </c>
       <c r="M39">
-        <v>55.8</v>
+        <v>-0</v>
       </c>
       <c r="N39">
-        <v>0.2841140529531568</v>
+        <v>-0</v>
       </c>
       <c r="O39">
-        <v>-0.2226656025538707</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>55.8</v>
+        <v>-0</v>
       </c>
       <c r="Q39">
-        <v>0.2841140529531568</v>
+        <v>-0</v>
       </c>
       <c r="R39">
-        <v>-0.2226656025538707</v>
+        <v>0</v>
       </c>
       <c r="S39">
         <v>0</v>
       </c>
-      <c r="T39">
-        <v>0</v>
-      </c>
       <c r="U39">
-        <v>236.1</v>
+        <v>264</v>
       </c>
       <c r="V39">
-        <v>1.20213849287169</v>
+        <v>2.540904716073147</v>
       </c>
       <c r="W39">
-        <v>-0.2584570957095709</v>
+        <v>-0.008821321321321322</v>
       </c>
       <c r="X39">
-        <v>0.4706982083914353</v>
+        <v>0.2180244381521006</v>
       </c>
       <c r="Y39">
-        <v>-0.7291553041010063</v>
+        <v>-0.2268457594734219</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>0.04502440482119733</v>
       </c>
       <c r="AA39">
         <v>0</v>
       </c>
       <c r="AB39">
-        <v>0.07803187566610663</v>
+        <v>0.06705857764178358</v>
       </c>
       <c r="AC39">
-        <v>-0.07803187566610663</v>
+        <v>-0.06705857764178358</v>
       </c>
       <c r="AD39">
-        <v>2968.1</v>
+        <v>927.4</v>
       </c>
       <c r="AE39">
         <v>0</v>
       </c>
       <c r="AF39">
-        <v>2968.1</v>
+        <v>927.4</v>
       </c>
       <c r="AG39">
-        <v>2732</v>
+        <v>663.4</v>
       </c>
       <c r="AH39">
-        <v>0.9379364828566914</v>
+        <v>0.8992533695335984</v>
       </c>
       <c r="AI39">
-        <v>0.8347911686120095</v>
+        <v>0.6404696132596684</v>
       </c>
       <c r="AJ39">
-        <v>0.9329326594727496</v>
+        <v>0.8645901212042226</v>
       </c>
       <c r="AK39">
-        <v>0.8230403084894861</v>
+        <v>0.560304054054054</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -5113,7 +5011,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Guotai Junan International Holdings Limited (SEHK:1788)</t>
+          <t>Southwest Securities International Securities Limited (SEHK:812)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5122,13 +5020,7 @@
         </is>
       </c>
       <c r="D40">
-        <v>-0.0476</v>
-      </c>
-      <c r="E40">
-        <v>-0.234</v>
-      </c>
-      <c r="F40">
-        <v>-0.0287</v>
+        <v>-0.518</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -5143,85 +5035,85 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>40.6</v>
+        <v>-5.75</v>
       </c>
       <c r="L40">
-        <v>0.1589041095890411</v>
+        <v>-4.791666666666667</v>
       </c>
       <c r="M40">
-        <v>79.91000000000001</v>
+        <v>0.613</v>
       </c>
       <c r="N40">
-        <v>0.09055983680870355</v>
+        <v>0.06223350253807107</v>
       </c>
       <c r="O40">
-        <v>1.968226600985222</v>
+        <v>-0.1066086956521739</v>
       </c>
       <c r="P40">
-        <v>73.40000000000001</v>
+        <v>0.613</v>
       </c>
       <c r="Q40">
-        <v>0.08318223028105169</v>
+        <v>0.06223350253807107</v>
       </c>
       <c r="R40">
-        <v>1.807881773399015</v>
+        <v>-0.1066086956521739</v>
       </c>
       <c r="S40">
-        <v>6.510000000000005</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>0.08146664998122893</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>632.2</v>
+        <v>49.4</v>
       </c>
       <c r="V40">
-        <v>0.7164551223934724</v>
+        <v>5.015228426395939</v>
       </c>
       <c r="W40">
-        <v>0.02027263194687172</v>
+        <v>-2.489177489177489</v>
       </c>
       <c r="X40">
-        <v>0.3202309005126272</v>
+        <v>0.2260764919780014</v>
       </c>
       <c r="Y40">
-        <v>-0.2999582685657555</v>
+        <v>-2.71525398115549</v>
       </c>
       <c r="Z40">
-        <v>0.02090509658891007</v>
+        <v>0.01177509567265234</v>
       </c>
       <c r="AA40">
         <v>0</v>
       </c>
       <c r="AB40">
-        <v>0.07919522893927161</v>
+        <v>0.06709321502359497</v>
       </c>
       <c r="AC40">
-        <v>-0.07919522893927161</v>
+        <v>-0.06709321502359497</v>
       </c>
       <c r="AD40">
-        <v>8321.299999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AE40">
         <v>0</v>
       </c>
       <c r="AF40">
-        <v>8321.299999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AG40">
-        <v>7689.099999999999</v>
+        <v>43.00000000000001</v>
       </c>
       <c r="AH40">
-        <v>0.9041255147386378</v>
+        <v>0.9036674816625917</v>
       </c>
       <c r="AI40">
-        <v>0.809063596853701</v>
+        <v>1.03831891223733</v>
       </c>
       <c r="AJ40">
-        <v>0.8970541912150731</v>
+        <v>0.8136234626300851</v>
       </c>
       <c r="AK40">
-        <v>0.7965585471723523</v>
+        <v>1.086132861833796</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -5259,85 +5151,85 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>-24</v>
+        <v>-52.1</v>
       </c>
       <c r="L41">
-        <v>-0.4624277456647399</v>
+        <v>-7.002688172043011</v>
       </c>
       <c r="M41">
-        <v>36.4</v>
+        <v>15.32</v>
       </c>
       <c r="N41">
-        <v>0.1173814898419864</v>
+        <v>0.3419642857142857</v>
       </c>
       <c r="O41">
-        <v>-1.516666666666667</v>
+        <v>-0.2940499040307102</v>
       </c>
       <c r="P41">
-        <v>20</v>
+        <v>10.9</v>
       </c>
       <c r="Q41">
-        <v>0.06449532408900355</v>
+        <v>0.2433035714285715</v>
       </c>
       <c r="R41">
-        <v>-0.8333333333333334</v>
+        <v>-0.2092130518234165</v>
       </c>
       <c r="S41">
-        <v>16.4</v>
+        <v>4.42</v>
       </c>
       <c r="T41">
-        <v>0.4505494505494505</v>
+        <v>0.2885117493472585</v>
       </c>
       <c r="U41">
-        <v>113.5</v>
+        <v>79</v>
       </c>
       <c r="V41">
-        <v>0.3660109642050951</v>
+        <v>1.763392857142857</v>
       </c>
       <c r="W41">
-        <v>-0.06806579693703914</v>
+        <v>-0.2256388046773495</v>
       </c>
       <c r="X41">
-        <v>0.2065098841033461</v>
+        <v>0.3478866757891488</v>
       </c>
       <c r="Y41">
-        <v>-0.2745756810403852</v>
+        <v>-0.5735254804664983</v>
       </c>
       <c r="Z41">
-        <v>0.03166197939226081</v>
+        <v>0.004356201439185905</v>
       </c>
       <c r="AA41">
         <v>0</v>
       </c>
       <c r="AB41">
-        <v>0.07987876642566256</v>
+        <v>0.06739453051475426</v>
       </c>
       <c r="AC41">
-        <v>-0.07987876642566256</v>
+        <v>-0.06739453051475426</v>
       </c>
       <c r="AD41">
-        <v>1592.6</v>
+        <v>728.5</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>1592.6</v>
+        <v>728.5</v>
       </c>
       <c r="AG41">
-        <v>1479.1</v>
+        <v>649.5</v>
       </c>
       <c r="AH41">
-        <v>0.8370210753140275</v>
+        <v>0.9420664683822579</v>
       </c>
       <c r="AI41">
-        <v>0.87337537702221</v>
+        <v>0.7940919991279703</v>
       </c>
       <c r="AJ41">
-        <v>0.8266823161189358</v>
+        <v>0.9354745787123723</v>
       </c>
       <c r="AK41">
-        <v>0.8649707602339181</v>
+        <v>0.7746898854961832</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -5363,25 +5255,25 @@
         </is>
       </c>
       <c r="D42">
-        <v>-0.138</v>
+        <v>-0.03240000000000001</v>
       </c>
       <c r="G42">
-        <v>-0.1479166666666667</v>
+        <v>-0.5664206642066421</v>
       </c>
       <c r="H42">
-        <v>-0.1479166666666667</v>
+        <v>-0.5664206642066421</v>
       </c>
       <c r="I42">
-        <v>-0.07572916666666667</v>
+        <v>-0.4317343173431734</v>
       </c>
       <c r="J42">
-        <v>-0.07572916666666667</v>
+        <v>-0.4317343173431734</v>
       </c>
       <c r="K42">
-        <v>-2.18</v>
+        <v>-7.83</v>
       </c>
       <c r="L42">
-        <v>-0.2270833333333334</v>
+        <v>-1.444649446494465</v>
       </c>
       <c r="M42">
         <v>-0</v>
@@ -5405,73 +5297,73 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>0.848</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>0.03351778656126482</v>
       </c>
       <c r="W42">
-        <v>-0.0185374149659864</v>
+        <v>-0.06703767123287671</v>
       </c>
       <c r="X42">
-        <v>0.09642777777540625</v>
+        <v>0.09701922653078229</v>
       </c>
       <c r="Y42">
-        <v>-0.1149651927413926</v>
+        <v>-0.164056897763659</v>
       </c>
       <c r="Z42">
-        <v>0.05510907003444317</v>
+        <v>0.03241626794258373</v>
       </c>
       <c r="AA42">
-        <v>-0.004173363949483352</v>
+        <v>-0.01399521531100478</v>
       </c>
       <c r="AB42">
-        <v>0.07604731253362652</v>
+        <v>0.06946490241596967</v>
       </c>
       <c r="AC42">
-        <v>-0.08022067648310988</v>
+        <v>-0.08346011772697445</v>
       </c>
       <c r="AD42">
-        <v>50.4</v>
+        <v>52.9</v>
       </c>
       <c r="AE42">
         <v>0</v>
       </c>
       <c r="AF42">
-        <v>50.4</v>
+        <v>52.9</v>
       </c>
       <c r="AG42">
-        <v>50.4</v>
+        <v>52.052</v>
       </c>
       <c r="AH42">
-        <v>0.4946025515210991</v>
+        <v>0.676470588235294</v>
       </c>
       <c r="AI42">
-        <v>0.3025210084033613</v>
+        <v>0.3302122347066168</v>
       </c>
       <c r="AJ42">
-        <v>0.4946025515210991</v>
+        <v>0.6729237770193401</v>
       </c>
       <c r="AK42">
-        <v>0.3025210084033613</v>
+        <v>0.3266479240925749</v>
       </c>
       <c r="AL42">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="AM42">
-        <v>1.91</v>
+        <v>2.181</v>
       </c>
       <c r="AN42">
-        <v>-76.24810892586989</v>
+        <v>-23.10043668122271</v>
       </c>
       <c r="AO42">
-        <v>-0.3806282722513089</v>
+        <v>-1.054054054054054</v>
       </c>
       <c r="AP42">
-        <v>-76.24810892586989</v>
+        <v>-22.73013100436681</v>
       </c>
       <c r="AQ42">
-        <v>-0.3806282722513089</v>
+        <v>-1.072902338376891</v>
       </c>
     </row>
     <row r="43">
@@ -5482,7 +5374,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Shenwan Hongyuan (H.K.) Limited (SEHK:218)</t>
+          <t>Renze Harvest International Limited (SEHK:1282)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5491,25 +5383,28 @@
         </is>
       </c>
       <c r="D43">
-        <v>0.0127</v>
+        <v>-0.262</v>
+      </c>
+      <c r="E43">
+        <v>-0.202</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>-0.6010526315789474</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>-0.6010526315789474</v>
       </c>
       <c r="I43">
-        <v>0.001377614573142752</v>
+        <v>-0.3378947368421053</v>
       </c>
       <c r="J43">
-        <v>0.001377614573142752</v>
+        <v>-0.2555796646642159</v>
       </c>
       <c r="K43">
-        <v>-34.8</v>
+        <v>42.2</v>
       </c>
       <c r="L43">
-        <v>-0.5515055467511886</v>
+        <v>0.4442105263157895</v>
       </c>
       <c r="M43">
         <v>-0</v>
@@ -5518,7 +5413,7 @@
         <v>-0</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P43">
         <v>-0</v>
@@ -5527,73 +5422,79 @@
         <v>-0</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S43">
         <v>0</v>
       </c>
       <c r="U43">
-        <v>72.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="V43">
-        <v>0.6993275696445725</v>
+        <v>1.879120879120879</v>
       </c>
       <c r="W43">
-        <v>-0.06722039791384971</v>
+        <v>0.0625648628613788</v>
       </c>
       <c r="X43">
-        <v>0.2668137575435922</v>
+        <v>0.1415175154209701</v>
       </c>
       <c r="Y43">
-        <v>-0.3340341554574419</v>
+        <v>-0.07895265255959133</v>
       </c>
       <c r="Z43">
-        <v>0.03623104436296771</v>
+        <v>0.1162933039539723</v>
       </c>
       <c r="AA43">
-        <v>4.991241471460587e-05</v>
+        <v>-0.02972220362724999</v>
       </c>
       <c r="AB43">
-        <v>0.08037239994861858</v>
+        <v>0.06644898821727357</v>
       </c>
       <c r="AC43">
-        <v>-0.08032248753390397</v>
+        <v>-0.09617119184452357</v>
       </c>
       <c r="AD43">
-        <v>771.6</v>
+        <v>167.6</v>
       </c>
       <c r="AE43">
-        <v>0.1003626021734617</v>
+        <v>0</v>
       </c>
       <c r="AF43">
-        <v>771.7003626021735</v>
+        <v>167.6</v>
       </c>
       <c r="AG43">
-        <v>698.9003626021736</v>
+        <v>99.19999999999999</v>
       </c>
       <c r="AH43">
-        <v>0.8811372951585694</v>
+        <v>0.8215686274509804</v>
       </c>
       <c r="AI43">
-        <v>0.6210366468798774</v>
+        <v>0.1518115942028986</v>
       </c>
       <c r="AJ43">
-        <v>0.8703612042432243</v>
+        <v>0.7315634218289085</v>
       </c>
       <c r="AK43">
-        <v>0.5974526807698178</v>
+        <v>0.09578988026264967</v>
       </c>
       <c r="AL43">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="AM43">
-        <v>0</v>
+        <v>4.600000000000001</v>
       </c>
       <c r="AN43">
-        <v>7211.214953271028</v>
+        <v>-5.513157894736842</v>
+      </c>
+      <c r="AO43">
+        <v>-1.969325153374233</v>
       </c>
       <c r="AP43">
-        <v>6531.77908973994</v>
+        <v>-3.263157894736842</v>
+      </c>
+      <c r="AQ43">
+        <v>-6.978260869565216</v>
       </c>
     </row>
     <row r="44">
@@ -5604,7 +5505,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Haitong International Securities Group Limited (SEHK:665)</t>
+          <t>Kingwisoft Technology Group Company Limited (SEHK:8295)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5612,17 +5513,35 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D44">
+        <v>0.364</v>
+      </c>
+      <c r="G44">
+        <v>0.07352537722908094</v>
+      </c>
+      <c r="H44">
+        <v>0.03676268861454047</v>
+      </c>
+      <c r="I44">
+        <v>-0.02976680384087791</v>
+      </c>
+      <c r="J44">
+        <v>-0.02976680384087791</v>
+      </c>
       <c r="K44">
-        <v>-426.4</v>
+        <v>-34.7</v>
+      </c>
+      <c r="L44">
+        <v>-0.237997256515775</v>
       </c>
       <c r="M44">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="N44">
-        <v>-0</v>
+        <v>0.003389830508474576</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>-0.001729106628242075</v>
       </c>
       <c r="P44">
         <v>-0</v>
@@ -5634,64 +5553,79 @@
         <v>0</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>0.06</v>
+      </c>
+      <c r="T44">
+        <v>1</v>
       </c>
       <c r="U44">
-        <v>977.7</v>
+        <v>13</v>
       </c>
       <c r="V44">
-        <v>1.319433198380567</v>
+        <v>0.7344632768361582</v>
       </c>
       <c r="W44">
-        <v>-0.1171171171171171</v>
+        <v>-0.1905546403075234</v>
       </c>
       <c r="X44">
-        <v>0.3342195714788768</v>
+        <v>0.1006109086783886</v>
       </c>
       <c r="Y44">
-        <v>-0.4513366885959939</v>
+        <v>-0.291165548985912</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>1.436453201970443</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>-0.04275862068965517</v>
       </c>
       <c r="AB44">
-        <v>0.08068133805442507</v>
+        <v>0.07787117161632423</v>
       </c>
       <c r="AC44">
-        <v>-0.08068133805442507</v>
+        <v>-0.1206297923059794</v>
       </c>
       <c r="AD44">
-        <v>7379.3</v>
+        <v>40.6</v>
       </c>
       <c r="AE44">
         <v>0</v>
       </c>
       <c r="AF44">
-        <v>7379.3</v>
+        <v>40.6</v>
       </c>
       <c r="AG44">
-        <v>6401.6</v>
+        <v>27.6</v>
       </c>
       <c r="AH44">
-        <v>0.9087472137728901</v>
+        <v>0.6963979416809606</v>
       </c>
       <c r="AI44">
-        <v>0.6998245530845465</v>
+        <v>0.2223439211391019</v>
       </c>
       <c r="AJ44">
-        <v>0.8962562652255481</v>
+        <v>0.6092715231788081</v>
       </c>
       <c r="AK44">
-        <v>0.6691474683279677</v>
+        <v>0.1627358490566038</v>
       </c>
       <c r="AL44">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AM44">
-        <v>0</v>
+        <v>2.981</v>
+      </c>
+      <c r="AN44">
+        <v>12.72727272727273</v>
+      </c>
+      <c r="AO44">
+        <v>-1.295522388059701</v>
+      </c>
+      <c r="AP44">
+        <v>8.652037617554859</v>
+      </c>
+      <c r="AQ44">
+        <v>-1.455887286145589</v>
       </c>
     </row>
     <row r="45">
@@ -5702,7 +5636,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>China Industrial Securities International Financial Group Limited (SEHK:6058)</t>
+          <t>Amasse Capital Holdings Limited (SEHK:8168)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5711,25 +5645,25 @@
         </is>
       </c>
       <c r="D45">
-        <v>-0.265</v>
+        <v>-0.141</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>-0.1649253731343283</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>-0.1649253731343283</v>
       </c>
       <c r="K45">
-        <v>-27</v>
+        <v>-0.248</v>
       </c>
       <c r="L45">
-        <v>-2.014925373134328</v>
+        <v>-0.1850746268656716</v>
       </c>
       <c r="M45">
         <v>-0</v>
@@ -5753,433 +5687,73 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>570.8</v>
+        <v>3.06</v>
       </c>
       <c r="V45">
-        <v>11.23622047244094</v>
+        <v>0.2283582089552239</v>
       </c>
       <c r="W45">
-        <v>-0.04764425622022234</v>
+        <v>-0.08611111111111111</v>
       </c>
       <c r="X45">
-        <v>0.6136211362537316</v>
+        <v>0.06141583072393499</v>
       </c>
       <c r="Y45">
-        <v>-0.661265392473954</v>
+        <v>-0.1475269418350461</v>
       </c>
       <c r="Z45">
-        <v>0.008982437324038074</v>
+        <v>0.6600985221674878</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>-0.1088669950738916</v>
       </c>
       <c r="AB45">
-        <v>0.0811822023992976</v>
+        <v>0.06103655503963953</v>
       </c>
       <c r="AC45">
-        <v>-0.0811822023992976</v>
+        <v>-0.1699035501135312</v>
       </c>
       <c r="AD45">
-        <v>1041.9</v>
+        <v>1.07</v>
       </c>
       <c r="AE45">
         <v>0</v>
       </c>
       <c r="AF45">
-        <v>1041.9</v>
+        <v>1.07</v>
       </c>
       <c r="AG45">
-        <v>471.1000000000001</v>
+        <v>-1.99</v>
       </c>
       <c r="AH45">
-        <v>0.9535096549830695</v>
+        <v>0.07394609536973047</v>
       </c>
       <c r="AI45">
-        <v>0.6616498380643933</v>
+        <v>0.2165991902834008</v>
       </c>
       <c r="AJ45">
-        <v>0.9026633454684807</v>
+        <v>-0.1744084136722173</v>
       </c>
       <c r="AK45">
-        <v>0.469269847594382</v>
+        <v>-1.058510638297872</v>
       </c>
       <c r="AL45">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AM45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>South China Financial Holdings Limited (SEHK:619)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>-0.194</v>
-      </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>-19.8</v>
-      </c>
-      <c r="L46">
-        <v>-3.267326732673268</v>
-      </c>
-      <c r="M46">
-        <v>-0</v>
-      </c>
-      <c r="N46">
-        <v>-0</v>
-      </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46">
-        <v>-0</v>
-      </c>
-      <c r="Q46">
-        <v>-0</v>
-      </c>
-      <c r="R46">
-        <v>0</v>
-      </c>
-      <c r="S46">
-        <v>0</v>
-      </c>
-      <c r="U46">
-        <v>4.15</v>
-      </c>
-      <c r="V46">
-        <v>0.2862068965517242</v>
-      </c>
-      <c r="W46">
-        <v>-0.2704918032786885</v>
-      </c>
-      <c r="X46">
-        <v>0.1810000541927979</v>
-      </c>
-      <c r="Y46">
-        <v>-0.4514918574714864</v>
-      </c>
-      <c r="Z46">
-        <v>0.04135954135954135</v>
-      </c>
-      <c r="AA46">
-        <v>0</v>
-      </c>
-      <c r="AB46">
-        <v>0.08715042248797764</v>
-      </c>
-      <c r="AC46">
-        <v>-0.08715042248797764</v>
-      </c>
-      <c r="AD46">
-        <v>60.5</v>
-      </c>
-      <c r="AE46">
-        <v>0</v>
-      </c>
-      <c r="AF46">
-        <v>60.5</v>
-      </c>
-      <c r="AG46">
-        <v>56.35</v>
-      </c>
-      <c r="AH46">
-        <v>0.8066666666666666</v>
-      </c>
-      <c r="AI46">
-        <v>0.5373001776198935</v>
-      </c>
-      <c r="AJ46">
-        <v>0.7953422724064927</v>
-      </c>
-      <c r="AK46">
-        <v>0.5195942830797603</v>
-      </c>
-      <c r="AL46">
-        <v>0</v>
-      </c>
-      <c r="AM46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Glory Sun Financial Group Limited (SEHK:1282)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>0.146</v>
-      </c>
-      <c r="G47">
-        <v>-0.1518987341772152</v>
-      </c>
-      <c r="H47">
-        <v>-0.1518987341772152</v>
-      </c>
-      <c r="I47">
-        <v>-0.2634493670886076</v>
-      </c>
-      <c r="J47">
-        <v>-0.2634493670886076</v>
-      </c>
-      <c r="K47">
-        <v>-75.5</v>
-      </c>
-      <c r="L47">
-        <v>-0.2986550632911392</v>
-      </c>
-      <c r="M47">
-        <v>-0</v>
-      </c>
-      <c r="N47">
-        <v>-0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>-0</v>
-      </c>
-      <c r="Q47">
-        <v>-0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
-      <c r="S47">
-        <v>0</v>
-      </c>
-      <c r="U47">
-        <v>68.59999999999999</v>
-      </c>
-      <c r="V47">
-        <v>0.7831050228310502</v>
-      </c>
-      <c r="W47">
-        <v>-0.07224189072815999</v>
-      </c>
-      <c r="X47">
-        <v>0.1342956276754229</v>
-      </c>
-      <c r="Y47">
-        <v>-0.2065375184035829</v>
-      </c>
-      <c r="Z47">
-        <v>0.09334613396351819</v>
-      </c>
-      <c r="AA47">
-        <v>-0.02459197991285724</v>
-      </c>
-      <c r="AB47">
-        <v>0.07841978059448705</v>
-      </c>
-      <c r="AC47">
-        <v>-0.1030117605073443</v>
-      </c>
-      <c r="AD47">
-        <v>211</v>
-      </c>
-      <c r="AE47">
-        <v>0</v>
-      </c>
-      <c r="AF47">
-        <v>211</v>
-      </c>
-      <c r="AG47">
-        <v>142.4</v>
-      </c>
-      <c r="AH47">
-        <v>0.7066309444072337</v>
-      </c>
-      <c r="AI47">
-        <v>0.2285281057077873</v>
-      </c>
-      <c r="AJ47">
-        <v>0.6191304347826088</v>
-      </c>
-      <c r="AK47">
-        <v>0.1666081666081666</v>
-      </c>
-      <c r="AL47">
-        <v>13</v>
-      </c>
-      <c r="AM47">
-        <v>0.5999999999999996</v>
-      </c>
-      <c r="AN47">
-        <v>-3.386837881219904</v>
-      </c>
-      <c r="AO47">
-        <v>-5.123076923076923</v>
-      </c>
-      <c r="AP47">
-        <v>-2.285714285714286</v>
-      </c>
-      <c r="AQ47">
-        <v>-111.0000000000001</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Amasse Capital Holdings Limited (SEHK:8168)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>-0.276</v>
-      </c>
-      <c r="G48">
-        <v>-1.476650563607085</v>
-      </c>
-      <c r="H48">
-        <v>-1.476650563607085</v>
-      </c>
-      <c r="I48">
-        <v>-1.508856682769726</v>
-      </c>
-      <c r="J48">
-        <v>-1.508856682769726</v>
-      </c>
-      <c r="K48">
-        <v>-1.18</v>
-      </c>
-      <c r="L48">
-        <v>-1.900161030595813</v>
-      </c>
-      <c r="M48">
-        <v>-0</v>
-      </c>
-      <c r="N48">
-        <v>-0</v>
-      </c>
-      <c r="O48">
-        <v>0</v>
-      </c>
-      <c r="P48">
-        <v>-0</v>
-      </c>
-      <c r="Q48">
-        <v>-0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>2.23</v>
-      </c>
-      <c r="V48">
-        <v>0.0832089552238806</v>
-      </c>
-      <c r="W48">
-        <v>-0.2878048780487805</v>
-      </c>
-      <c r="X48">
-        <v>0.07187655363440812</v>
-      </c>
-      <c r="Y48">
-        <v>-0.3596814316831887</v>
-      </c>
-      <c r="Z48">
-        <v>0.2090909090909091</v>
-      </c>
-      <c r="AA48">
-        <v>-0.3154882154882156</v>
-      </c>
-      <c r="AB48">
-        <v>0.07152303181198619</v>
-      </c>
-      <c r="AC48">
-        <v>-0.3870112473002018</v>
-      </c>
-      <c r="AD48">
-        <v>1.38</v>
-      </c>
-      <c r="AE48">
-        <v>0</v>
-      </c>
-      <c r="AF48">
-        <v>1.38</v>
-      </c>
-      <c r="AG48">
-        <v>-0.8500000000000001</v>
-      </c>
-      <c r="AH48">
-        <v>0.04897090134847409</v>
-      </c>
-      <c r="AI48">
-        <v>0.323943661971831</v>
-      </c>
-      <c r="AJ48">
-        <v>-0.03275529865125242</v>
-      </c>
-      <c r="AK48">
-        <v>-0.4187192118226602</v>
-      </c>
-      <c r="AL48">
-        <v>0.015</v>
-      </c>
-      <c r="AM48">
-        <v>0.015</v>
-      </c>
-      <c r="AN48">
-        <v>-1.504907306434024</v>
-      </c>
-      <c r="AO48">
-        <v>-62.46666666666668</v>
-      </c>
-      <c r="AP48">
-        <v>0.9269356597600873</v>
-      </c>
-      <c r="AQ48">
-        <v>-62.46666666666668</v>
+        <v>0.019</v>
+      </c>
+      <c r="AN45">
+        <v>-5.323383084577115</v>
+      </c>
+      <c r="AO45">
+        <v>-11.63157894736842</v>
+      </c>
+      <c r="AP45">
+        <v>9.900497512437811</v>
+      </c>
+      <c r="AQ45">
+        <v>-11.63157894736842</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/hong_kong/hong_kong_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,118 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0352</v>
+        <v>-0.0548</v>
       </c>
       <c r="E2">
-        <v>-0.021</v>
+        <v>-0.04975</v>
       </c>
       <c r="F2">
         <v>0.108</v>
       </c>
       <c r="G2">
-        <v>0.05202173565606521</v>
+        <v>0.02861331094506906</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>-0.003244545251131684</v>
       </c>
       <c r="I2">
-        <v>1.284743004826455E-05</v>
+        <v>-0.004538367068364502</v>
       </c>
       <c r="J2">
-        <v>1.284743004826455E-05</v>
+        <v>-0.004338385741148129</v>
       </c>
       <c r="K2">
-        <v>2251.4</v>
+        <v>2399.259</v>
       </c>
       <c r="L2">
-        <v>0.359821000479463</v>
+        <v>0.2294216025075876</v>
       </c>
       <c r="M2">
-        <v>2167.19</v>
+        <v>2916.39</v>
       </c>
       <c r="N2">
-        <v>0.09850908413220059</v>
+        <v>0.06895261134913185</v>
       </c>
       <c r="O2">
-        <v>0.9625966065559207</v>
+        <v>1.215537797294915</v>
       </c>
       <c r="P2">
-        <v>2166.1</v>
+        <v>2908.03</v>
       </c>
       <c r="Q2">
-        <v>0.0984595384524475</v>
+        <v>0.06875495471511556</v>
       </c>
       <c r="R2">
-        <v>0.9621124633561339</v>
+        <v>1.212053388150258</v>
       </c>
       <c r="S2">
-        <v>1.090000000000146</v>
+        <v>8.360000000000145</v>
       </c>
       <c r="T2">
-        <v>0.0005029554399937918</v>
+        <v>0.002866557627752168</v>
       </c>
       <c r="U2">
-        <v>9572.1</v>
+        <v>16256.672</v>
       </c>
       <c r="V2">
-        <v>0.4350974322610557</v>
+        <v>0.3843587401706609</v>
       </c>
       <c r="W2">
-        <v>0.01868961512063777</v>
+        <v>-0.06567446517717765</v>
       </c>
       <c r="X2">
-        <v>0.103422499190215</v>
+        <v>0.07024819920705805</v>
       </c>
       <c r="Y2">
-        <v>-0.08473288406957727</v>
+        <v>-0.1359226643842357</v>
       </c>
       <c r="Z2">
-        <v>0.08235366097807167</v>
+        <v>0.07376952191969308</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06773564865115106</v>
+        <v>0.06674411579663209</v>
       </c>
       <c r="AC2">
-        <v>-0.06773564865115106</v>
+        <v>-0.06646714637718709</v>
       </c>
       <c r="AD2">
-        <v>57041.6</v>
+        <v>106070.809</v>
       </c>
       <c r="AE2">
-        <v>0.09306815094004357</v>
+        <v>2.053037147831998</v>
       </c>
       <c r="AF2">
-        <v>57041.69306815093</v>
+        <v>106072.8620371478</v>
       </c>
       <c r="AG2">
-        <v>47469.59306815093</v>
+        <v>89816.19003714783</v>
       </c>
       <c r="AH2">
-        <v>0.7216667940759831</v>
+        <v>0.7149287795303368</v>
       </c>
       <c r="AI2">
-        <v>0.6647116406822147</v>
+        <v>0.662927010158931</v>
       </c>
       <c r="AJ2">
-        <v>0.6833156680959558</v>
+        <v>0.6798500755110134</v>
       </c>
       <c r="AK2">
-        <v>0.6226166040027132</v>
+        <v>0.6248075090296242</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>69.133</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>40.65899999999999</v>
       </c>
       <c r="AN2">
-        <v>576177.7777777778</v>
+        <v>-2883.220772513523</v>
+      </c>
+      <c r="AO2">
+        <v>-0.7005482186510061</v>
       </c>
       <c r="AP2">
-        <v>479490.8390722316</v>
+        <v>-2441.387100414467</v>
+      </c>
+      <c r="AQ2">
+        <v>-1.191150790722842</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Shenwan Hongyuan (H.K.) Limited (SEHK:218)</t>
+          <t>Da Yu Financial Holdings Limited (SEHK:1073)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,26 +724,23 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0687</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1890547263681592</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1890547263681592</v>
       </c>
       <c r="I3">
-        <v>0.001522469125227108</v>
+        <v>0.2006633499170812</v>
       </c>
       <c r="J3">
-        <v>0.001522469125227108</v>
+        <v>0.2006633499170812</v>
       </c>
       <c r="K3">
-        <v>-20.3</v>
+        <v>-18</v>
       </c>
       <c r="L3">
-        <v>-0.384469696969697</v>
+        <v>-2.985074626865671</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,67 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>76.90000000000001</v>
+        <v>24.9</v>
       </c>
       <c r="V3">
-        <v>0.2347374847374847</v>
+        <v>1.163551401869159</v>
       </c>
       <c r="W3">
-        <v>-0.05464333781965007</v>
+        <v>-0.2965403624382207</v>
       </c>
       <c r="X3">
-        <v>0.06730127134815267</v>
+        <v>0.06585678773641161</v>
       </c>
       <c r="Y3">
-        <v>-0.1219446091678027</v>
+        <v>-0.3623971501746324</v>
       </c>
       <c r="Z3">
-        <v>0.09666911405292453</v>
+        <v>0.4380039224231858</v>
       </c>
       <c r="AA3">
-        <v>0.0001471757415086355</v>
+        <v>0.08789133435025784</v>
       </c>
       <c r="AB3">
-        <v>0.06604133346550699</v>
+        <v>0.0657097134877766</v>
       </c>
       <c r="AC3">
-        <v>-0.06589415772399836</v>
+        <v>0.02218162086248124</v>
       </c>
       <c r="AD3">
-        <v>32.1</v>
+        <v>0.252</v>
       </c>
       <c r="AE3">
-        <v>0.09306815094004357</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>32.19306815094004</v>
+        <v>0.252</v>
       </c>
       <c r="AG3">
-        <v>-44.70693184905996</v>
+        <v>-24.648</v>
       </c>
       <c r="AH3">
-        <v>0.08947662142683203</v>
+        <v>0.01163864769998153</v>
       </c>
       <c r="AI3">
-        <v>0.08368507471600349</v>
+        <v>0.00387382401770891</v>
       </c>
       <c r="AJ3">
-        <v>-0.1580347377943039</v>
+        <v>7.588669950738914</v>
       </c>
       <c r="AK3">
-        <v>-0.1452499632874641</v>
+        <v>-0.6138673042438733</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.461</v>
       </c>
       <c r="AN3">
-        <v>324.2424242424242</v>
+        <v>0.1508982035928144</v>
+      </c>
+      <c r="AO3">
+        <v>55</v>
       </c>
       <c r="AP3">
-        <v>-451.5851701925249</v>
+        <v>-14.75928143712575</v>
+      </c>
+      <c r="AQ3">
+        <v>-2.62472885032538</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Huatai Securities Co., Ltd. (SHSE:601688)</t>
+          <t>Solowin Holdings (NasdaqCM:SWIN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,113 +849,110 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.147</v>
-      </c>
-      <c r="E4">
-        <v>0.175</v>
-      </c>
-      <c r="F4">
-        <v>0.108</v>
-      </c>
       <c r="G4">
-        <v>0.05474912956452996</v>
+        <v>0.1652892561983471</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.193280566215163</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.193280566215163</v>
       </c>
       <c r="K4">
-        <v>2236.3</v>
+        <v>-12.1</v>
       </c>
       <c r="L4">
-        <v>0.3761458631187661</v>
+        <v>-5</v>
       </c>
       <c r="M4">
-        <v>2141.59</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.1055131571816386</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.9576487948844072</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>2140.5</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.1054594543994403</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.9571613826409694</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>1.090000000000146</v>
-      </c>
-      <c r="T4">
-        <v>0.0005089676361956049</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>7949</v>
+        <v>2.46</v>
       </c>
       <c r="V4">
-        <v>0.3916361611871763</v>
+        <v>0.09213483146067415</v>
       </c>
       <c r="W4">
-        <v>0.09482276119402985</v>
+        <v>-1.110091743119266</v>
       </c>
       <c r="X4">
-        <v>0.103422499190215</v>
+        <v>0.06630207683581901</v>
       </c>
       <c r="Y4">
-        <v>-0.008599737996185186</v>
+        <v>-1.176393819955085</v>
       </c>
       <c r="Z4">
-        <v>0.08899483571588954</v>
+        <v>0.4356980639647337</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.08421196850195402</v>
       </c>
       <c r="AB4">
-        <v>0.06773564865115106</v>
+        <v>0.06581556760493515</v>
       </c>
       <c r="AC4">
-        <v>-0.06773564865115106</v>
+        <v>0.01839640089701887</v>
       </c>
       <c r="AD4">
-        <v>46181.2</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.031305148796529</v>
       </c>
       <c r="AF4">
-        <v>46181.2</v>
+        <v>1.031305148796529</v>
       </c>
       <c r="AG4">
-        <v>38232.2</v>
+        <v>-1.428694851203471</v>
       </c>
       <c r="AH4">
-        <v>0.6946829106126678</v>
+        <v>0.0371892034386014</v>
       </c>
       <c r="AI4">
-        <v>0.6354595954244795</v>
+        <v>0.1464650554127448</v>
       </c>
       <c r="AJ4">
-        <v>0.6532169467837367</v>
+        <v>-0.0565342724798489</v>
       </c>
       <c r="AK4">
-        <v>0.5906894894839219</v>
+        <v>-0.3118532393719239</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-0.063</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>-2.119725298521471</v>
+      </c>
+      <c r="AQ4">
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
@@ -957,118 +963,5277 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Gemini Investments (Holdings) Limited (SEHK:174)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.429</v>
+      </c>
+      <c r="G5">
+        <v>0.2247956403269755</v>
+      </c>
+      <c r="H5">
+        <v>0.2247956403269755</v>
+      </c>
+      <c r="I5">
+        <v>0.3753405994550408</v>
+      </c>
+      <c r="J5">
+        <v>0.3753405994550408</v>
+      </c>
+      <c r="K5">
+        <v>-39.3</v>
+      </c>
+      <c r="L5">
+        <v>-0.2677111716621253</v>
+      </c>
+      <c r="M5">
+        <v>0.029</v>
+      </c>
+      <c r="N5">
+        <v>0.001746987951807229</v>
+      </c>
+      <c r="O5">
+        <v>-0.0007379134860050891</v>
+      </c>
+      <c r="P5">
+        <v>0.029</v>
+      </c>
+      <c r="Q5">
+        <v>0.001746987951807229</v>
+      </c>
+      <c r="R5">
+        <v>-0.0007379134860050891</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>49.1</v>
+      </c>
+      <c r="V5">
+        <v>2.957831325301205</v>
+      </c>
+      <c r="W5">
+        <v>-0.1238965952080706</v>
+      </c>
+      <c r="X5">
+        <v>0.6240345356760253</v>
+      </c>
+      <c r="Y5">
+        <v>-0.7479311308840959</v>
+      </c>
+      <c r="Z5">
+        <v>0.1211221122112211</v>
+      </c>
+      <c r="AA5">
+        <v>0.04546204620462047</v>
+      </c>
+      <c r="AB5">
+        <v>0.06968492295607027</v>
+      </c>
+      <c r="AC5">
+        <v>-0.02422287675144981</v>
+      </c>
+      <c r="AD5">
+        <v>558.9</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>558.9</v>
+      </c>
+      <c r="AG5">
+        <v>509.8</v>
+      </c>
+      <c r="AH5">
+        <v>0.9711555169417897</v>
+      </c>
+      <c r="AI5">
+        <v>0.4470842332613391</v>
+      </c>
+      <c r="AJ5">
+        <v>0.9684650455927051</v>
+      </c>
+      <c r="AK5">
+        <v>0.4244796003330558</v>
+      </c>
+      <c r="AL5">
+        <v>46.6</v>
+      </c>
+      <c r="AM5">
+        <v>45.48</v>
+      </c>
+      <c r="AN5">
+        <v>10.125</v>
+      </c>
+      <c r="AO5">
+        <v>1.182403433476395</v>
+      </c>
+      <c r="AP5">
+        <v>9.235507246376811</v>
+      </c>
+      <c r="AQ5">
+        <v>1.211521547933157</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Garden Stage Limited (NasdaqCM:GSIW)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0.03365730166492672</v>
+      </c>
+      <c r="J6">
+        <v>0.03365730166492672</v>
+      </c>
+      <c r="K6">
+        <v>-4.59</v>
+      </c>
+      <c r="L6">
+        <v>-3.25531914893617</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>2.67</v>
+      </c>
+      <c r="V6">
+        <v>0.2567307692307692</v>
+      </c>
+      <c r="W6">
+        <v>-2.353846153846154</v>
+      </c>
+      <c r="X6">
+        <v>0.06609638171558858</v>
+      </c>
+      <c r="Y6">
+        <v>-2.419942535561742</v>
+      </c>
+      <c r="Z6">
+        <v>1.011683855581726</v>
+      </c>
+      <c r="AA6">
+        <v>0.03405054871685029</v>
+      </c>
+      <c r="AB6">
+        <v>0.0657673581401656</v>
+      </c>
+      <c r="AC6">
+        <v>-0.03171680942331531</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0.2727160232622666</v>
+      </c>
+      <c r="AF6">
+        <v>0.2727160232622666</v>
+      </c>
+      <c r="AG6">
+        <v>-2.397283976737733</v>
+      </c>
+      <c r="AH6">
+        <v>0.02555263558665427</v>
+      </c>
+      <c r="AI6">
+        <v>0.0285186784380983</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.2995587960099192</v>
+      </c>
+      <c r="AK6">
+        <v>-0.3477996146435057</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>-23.50278408566405</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Magic Empire Global Limited (NasdaqCM:MEGL)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0.09391122684902564</v>
+      </c>
+      <c r="J7">
+        <v>0.09391122684902564</v>
+      </c>
+      <c r="K7">
+        <v>-0.075</v>
+      </c>
+      <c r="L7">
+        <v>-0.03787878787878788</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>11.9</v>
+      </c>
+      <c r="V7">
+        <v>1.091743119266055</v>
+      </c>
+      <c r="W7">
+        <v>-0.004285714285714286</v>
+      </c>
+      <c r="X7">
+        <v>0.06598904215662263</v>
+      </c>
+      <c r="Y7">
+        <v>-0.07027475644233691</v>
+      </c>
+      <c r="Z7">
+        <v>0.3464397889434227</v>
+      </c>
+      <c r="AA7">
+        <v>0.03253458560899433</v>
+      </c>
+      <c r="AB7">
+        <v>0.06574173494341923</v>
+      </c>
+      <c r="AC7">
+        <v>-0.0332071493344249</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0.2152788541946463</v>
+      </c>
+      <c r="AF7">
+        <v>0.2152788541946463</v>
+      </c>
+      <c r="AG7">
+        <v>-11.68472114580535</v>
+      </c>
+      <c r="AH7">
+        <v>0.01936783206418659</v>
+      </c>
+      <c r="AI7">
+        <v>0.01229091788870322</v>
+      </c>
+      <c r="AJ7">
+        <v>14.89028454026611</v>
+      </c>
+      <c r="AK7">
+        <v>-2.080879943669546</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>-0.572</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>-51.02498316945569</v>
+      </c>
+      <c r="AQ7">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Planetree International Development Limited (SEHK:613)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>0.0573</v>
+      </c>
+      <c r="G8">
+        <v>0.4869230769230769</v>
+      </c>
+      <c r="H8">
+        <v>0.4869230769230769</v>
+      </c>
+      <c r="I8">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="J8">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="K8">
+        <v>-25.7</v>
+      </c>
+      <c r="L8">
+        <v>-1.976923076923077</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>5.45</v>
+      </c>
+      <c r="V8">
+        <v>0.1860068259385665</v>
+      </c>
+      <c r="W8">
+        <v>-0.1177278973889143</v>
+      </c>
+      <c r="X8">
+        <v>0.08332127964955856</v>
+      </c>
+      <c r="Y8">
+        <v>-0.2010491770384729</v>
+      </c>
+      <c r="Z8">
+        <v>0.05564592072596523</v>
+      </c>
+      <c r="AA8">
+        <v>0.01284136632137659</v>
+      </c>
+      <c r="AB8">
+        <v>0.06779801373594056</v>
+      </c>
+      <c r="AC8">
+        <v>-0.05495664741456397</v>
+      </c>
+      <c r="AD8">
+        <v>31.2</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>31.2</v>
+      </c>
+      <c r="AG8">
+        <v>25.75</v>
+      </c>
+      <c r="AH8">
+        <v>0.5157024793388429</v>
+      </c>
+      <c r="AI8">
+        <v>0.1224489795918367</v>
+      </c>
+      <c r="AJ8">
+        <v>0.4677565849227975</v>
+      </c>
+      <c r="AK8">
+        <v>0.1032684980950471</v>
+      </c>
+      <c r="AL8">
+        <v>2.16</v>
+      </c>
+      <c r="AM8">
+        <v>2.129</v>
+      </c>
+      <c r="AN8">
+        <v>8.478260869565217</v>
+      </c>
+      <c r="AO8">
+        <v>1.388888888888889</v>
+      </c>
+      <c r="AP8">
+        <v>6.997282608695651</v>
+      </c>
+      <c r="AQ8">
+        <v>1.409112259276656</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Oriental Explorer Holdings Limited (SEHK:430)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G9">
+        <v>0.526984126984127</v>
+      </c>
+      <c r="H9">
+        <v>0.526984126984127</v>
+      </c>
+      <c r="I9">
+        <v>0.5619047619047619</v>
+      </c>
+      <c r="J9">
+        <v>0.5619047619047619</v>
+      </c>
+      <c r="K9">
+        <v>-5.16</v>
+      </c>
+      <c r="L9">
+        <v>-1.638095238095238</v>
+      </c>
+      <c r="M9">
+        <v>0.948</v>
+      </c>
+      <c r="N9">
+        <v>0.04989473684210526</v>
+      </c>
+      <c r="O9">
+        <v>-0.1837209302325581</v>
+      </c>
+      <c r="P9">
+        <v>0.948</v>
+      </c>
+      <c r="Q9">
+        <v>0.04989473684210526</v>
+      </c>
+      <c r="R9">
+        <v>-0.1837209302325581</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>1.02</v>
+      </c>
+      <c r="V9">
+        <v>0.05368421052631579</v>
+      </c>
+      <c r="W9">
+        <v>-0.02663913267940114</v>
+      </c>
+      <c r="X9">
+        <v>0.08259498825305127</v>
+      </c>
+      <c r="Y9">
+        <v>-0.1092341209324524</v>
+      </c>
+      <c r="Z9">
+        <v>0.01494307400379507</v>
+      </c>
+      <c r="AA9">
+        <v>0.008396584440227705</v>
+      </c>
+      <c r="AB9">
+        <v>0.06775453724282197</v>
+      </c>
+      <c r="AC9">
+        <v>-0.05935795280259427</v>
+      </c>
+      <c r="AD9">
+        <v>19.4</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>19.4</v>
+      </c>
+      <c r="AG9">
+        <v>18.38</v>
+      </c>
+      <c r="AH9">
+        <v>0.5052083333333334</v>
+      </c>
+      <c r="AI9">
+        <v>0.09344894026974951</v>
+      </c>
+      <c r="AJ9">
+        <v>0.4917067950775816</v>
+      </c>
+      <c r="AK9">
+        <v>0.08897279504308259</v>
+      </c>
+      <c r="AL9">
+        <v>1.03</v>
+      </c>
+      <c r="AM9">
+        <v>0.984</v>
+      </c>
+      <c r="AN9">
+        <v>10.89887640449438</v>
+      </c>
+      <c r="AO9">
+        <v>1.718446601941747</v>
+      </c>
+      <c r="AP9">
+        <v>10.32584269662921</v>
+      </c>
+      <c r="AQ9">
+        <v>1.798780487804878</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TOP Financial Group Limited (NasdaqCM:TOP)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>-0.0571</v>
+      </c>
+      <c r="E10">
+        <v>-0.0393</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0.006867522422251631</v>
+      </c>
+      <c r="J10">
+        <v>0.006867522422251631</v>
+      </c>
+      <c r="K10">
+        <v>1.05</v>
+      </c>
+      <c r="L10">
+        <v>0.1305970149253732</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>25.9</v>
+      </c>
+      <c r="V10">
+        <v>0.4567901234567901</v>
+      </c>
+      <c r="W10">
+        <v>0.02916666666666667</v>
+      </c>
+      <c r="X10">
+        <v>0.06569920523137882</v>
+      </c>
+      <c r="Y10">
+        <v>-0.03653253856471215</v>
+      </c>
+      <c r="Z10">
+        <v>0.3977456017027542</v>
+      </c>
+      <c r="AA10">
+        <v>0.002731526838045631</v>
+      </c>
+      <c r="AB10">
+        <v>0.06567089430820638</v>
+      </c>
+      <c r="AC10">
+        <v>-0.06293936747016075</v>
+      </c>
+      <c r="AD10">
+        <v>0.065</v>
+      </c>
+      <c r="AE10">
+        <v>0.06392559862548448</v>
+      </c>
+      <c r="AF10">
+        <v>0.1289255986254845</v>
+      </c>
+      <c r="AG10">
+        <v>-25.77107440137451</v>
+      </c>
+      <c r="AH10">
+        <v>0.00226866155337983</v>
+      </c>
+      <c r="AI10">
+        <v>0.003173246565738527</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.8332353582472908</v>
+      </c>
+      <c r="AK10">
+        <v>-1.749691396620232</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0.9558823529411764</v>
+      </c>
+      <c r="AP10">
+        <v>-378.9863882555075</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Shenwan Hongyuan Group Co., Ltd. (SZSE:000166)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.00466</v>
+      </c>
+      <c r="E11">
+        <v>-0.0602</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>585.8</v>
+      </c>
+      <c r="L11">
+        <v>0.1829595852333062</v>
+      </c>
+      <c r="M11">
+        <v>574.1</v>
+      </c>
+      <c r="N11">
+        <v>0.03325648214658109</v>
+      </c>
+      <c r="O11">
+        <v>0.9800273130761353</v>
+      </c>
+      <c r="P11">
+        <v>574.1</v>
+      </c>
+      <c r="Q11">
+        <v>0.03325648214658109</v>
+      </c>
+      <c r="R11">
+        <v>0.9800273130761353</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>4765.6</v>
+      </c>
+      <c r="V11">
+        <v>0.2760618207938458</v>
+      </c>
+      <c r="W11">
+        <v>0.04289972244802308</v>
+      </c>
+      <c r="X11">
+        <v>0.107883336468175</v>
+      </c>
+      <c r="Y11">
+        <v>-0.06498361402015189</v>
+      </c>
+      <c r="Z11">
+        <v>0.05782835717111003</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.0650389526244281</v>
+      </c>
+      <c r="AC11">
+        <v>-0.0650389526244281</v>
+      </c>
+      <c r="AD11">
+        <v>43949.1</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>43949.1</v>
+      </c>
+      <c r="AG11">
+        <v>39183.5</v>
+      </c>
+      <c r="AH11">
+        <v>0.7179829412254807</v>
+      </c>
+      <c r="AI11">
+        <v>0.7009213436913395</v>
+      </c>
+      <c r="AJ11">
+        <v>0.69417304588609</v>
+      </c>
+      <c r="AK11">
+        <v>0.6763203725470904</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Get Nice Holdings Limited (SEHK:64)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>-0.0413</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>-1.26</v>
+      </c>
+      <c r="L12">
+        <v>-0.02692307692307692</v>
+      </c>
+      <c r="M12">
+        <v>12.4</v>
+      </c>
+      <c r="N12">
+        <v>0.07974276527331189</v>
+      </c>
+      <c r="O12">
+        <v>-9.841269841269842</v>
+      </c>
+      <c r="P12">
+        <v>12.4</v>
+      </c>
+      <c r="Q12">
+        <v>0.07974276527331189</v>
+      </c>
+      <c r="R12">
+        <v>-9.841269841269842</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>349.2</v>
+      </c>
+      <c r="V12">
+        <v>2.245659163987138</v>
+      </c>
+      <c r="W12">
+        <v>-0.001689687541906933</v>
+      </c>
+      <c r="X12">
+        <v>0.06566149540634604</v>
+      </c>
+      <c r="Y12">
+        <v>-0.06735118294825297</v>
+      </c>
+      <c r="Z12">
+        <v>0.1190022122206118</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.06566149540634604</v>
+      </c>
+      <c r="AC12">
+        <v>-0.06566149540634604</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>-349.2</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>1.802787816210635</v>
+      </c>
+      <c r="AK12">
+        <v>-0.6392092257001648</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CLSA Premium Limited (SEHK:6877)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>1.192</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1.35</v>
+      </c>
+      <c r="L13">
+        <v>0.09375</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>-0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>3.79</v>
+      </c>
+      <c r="V13">
+        <v>0.1474708171206226</v>
+      </c>
+      <c r="W13">
+        <v>0.04485049833887043</v>
+      </c>
+      <c r="X13">
+        <v>0.06566149540634604</v>
+      </c>
+      <c r="Y13">
+        <v>-0.02081099706747561</v>
+      </c>
+      <c r="Z13">
+        <v>0.5489897064430042</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.06566149540634604</v>
+      </c>
+      <c r="AC13">
+        <v>-0.06566149540634604</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>-3.79</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>-0.1729803742583295</v>
+      </c>
+      <c r="AK13">
+        <v>-0.1367737278960664</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Pinestone Capital Limited (SEHK:804)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>-0.253</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>-3.27</v>
+      </c>
+      <c r="L14">
+        <v>-4.711815561959654</v>
+      </c>
+      <c r="M14">
+        <v>-0</v>
+      </c>
+      <c r="N14">
+        <v>-0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>-0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>1.62</v>
+      </c>
+      <c r="V14">
+        <v>0.1446428571428572</v>
+      </c>
+      <c r="W14">
+        <v>-0.1557142857142857</v>
+      </c>
+      <c r="X14">
+        <v>0.06568518733300932</v>
+      </c>
+      <c r="Y14">
+        <v>-0.221399473047295</v>
+      </c>
+      <c r="Z14">
+        <v>0.04339669834917459</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.06566740543226782</v>
+      </c>
+      <c r="AC14">
+        <v>-0.06566740543226782</v>
+      </c>
+      <c r="AD14">
+        <v>0.016</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0.016</v>
+      </c>
+      <c r="AG14">
+        <v>-1.604</v>
+      </c>
+      <c r="AH14">
+        <v>0.001426533523537803</v>
+      </c>
+      <c r="AI14">
+        <v>0.0007367839381101493</v>
+      </c>
+      <c r="AJ14">
+        <v>-0.1671529804085035</v>
+      </c>
+      <c r="AK14">
+        <v>-0.07981687898089172</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fu Shek Financial Holdings Limited (SEHK:2263)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0.423</v>
+      </c>
+      <c r="L15">
+        <v>0.08041825095057034</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>28.6</v>
+      </c>
+      <c r="V15">
+        <v>1.588888888888889</v>
+      </c>
+      <c r="W15">
+        <v>0.009358407079646016</v>
+      </c>
+      <c r="X15">
+        <v>0.06575731608751754</v>
+      </c>
+      <c r="Y15">
+        <v>-0.05639890900787153</v>
+      </c>
+      <c r="Z15">
+        <v>0.2758837721598656</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.06568529481696257</v>
+      </c>
+      <c r="AC15">
+        <v>-0.06568529481696257</v>
+      </c>
+      <c r="AD15">
+        <v>0.104</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0.104</v>
+      </c>
+      <c r="AG15">
+        <v>-28.496</v>
+      </c>
+      <c r="AH15">
+        <v>0.005744586831639416</v>
+      </c>
+      <c r="AI15">
+        <v>0.00226067298495783</v>
+      </c>
+      <c r="AJ15">
+        <v>2.714939024390243</v>
+      </c>
+      <c r="AK15">
+        <v>-1.637324752930361</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Get Nice Financial Group Limited (SEHK:1469)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.0134</v>
+      </c>
+      <c r="E16">
+        <v>0.00201</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>17.8</v>
+      </c>
+      <c r="L16">
+        <v>0.4129930394431555</v>
+      </c>
+      <c r="M16">
+        <v>19.3</v>
+      </c>
+      <c r="N16">
+        <v>0.06662064204349327</v>
+      </c>
+      <c r="O16">
+        <v>1.084269662921348</v>
+      </c>
+      <c r="P16">
+        <v>19.3</v>
+      </c>
+      <c r="Q16">
+        <v>0.06662064204349327</v>
+      </c>
+      <c r="R16">
+        <v>1.084269662921348</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>319.2</v>
+      </c>
+      <c r="V16">
+        <v>1.101829478771142</v>
+      </c>
+      <c r="W16">
+        <v>0.03204897371263954</v>
+      </c>
+      <c r="X16">
+        <v>0.06577484373342685</v>
+      </c>
+      <c r="Y16">
+        <v>-0.03372587002078731</v>
+      </c>
+      <c r="Z16">
+        <v>0.1729520629850483</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.06568961868452387</v>
+      </c>
+      <c r="AC16">
+        <v>-0.06568961868452387</v>
+      </c>
+      <c r="AD16">
+        <v>1.98</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>1.98</v>
+      </c>
+      <c r="AG16">
+        <v>-317.22</v>
+      </c>
+      <c r="AH16">
+        <v>0.006788261108063631</v>
+      </c>
+      <c r="AI16">
+        <v>0.003532686268912361</v>
+      </c>
+      <c r="AJ16">
+        <v>11.52688953488373</v>
+      </c>
+      <c r="AK16">
+        <v>-1.314738063660477</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GoFintech Innovation Limited (SEHK:290)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>-0.0975</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>-3.11</v>
+      </c>
+      <c r="L17">
+        <v>-0.5016129032258064</v>
+      </c>
+      <c r="M17">
+        <v>-0</v>
+      </c>
+      <c r="N17">
+        <v>-0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>-0</v>
+      </c>
+      <c r="Q17">
+        <v>-0</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>15.6</v>
+      </c>
+      <c r="V17">
+        <v>0.02056419720537833</v>
+      </c>
+      <c r="W17">
+        <v>-0.07493975903614458</v>
+      </c>
+      <c r="X17">
+        <v>0.06571505677495601</v>
+      </c>
+      <c r="Y17">
+        <v>-0.1406548158111006</v>
+      </c>
+      <c r="Z17">
+        <v>0.2089652847994607</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0.06572321759808029</v>
+      </c>
+      <c r="AC17">
+        <v>-0.06572321759808029</v>
+      </c>
+      <c r="AD17">
+        <v>2.45</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>2.45</v>
+      </c>
+      <c r="AG17">
+        <v>-13.15</v>
+      </c>
+      <c r="AH17">
+        <v>0.003219236581039354</v>
+      </c>
+      <c r="AI17">
+        <v>0.01794214573416331</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.01764035146555771</v>
+      </c>
+      <c r="AK17">
+        <v>-0.1087226126498553</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Imagi International Holdings Limited (SEHK:585)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>-0.169</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>-3.63</v>
+      </c>
+      <c r="L18">
+        <v>-0.9758064516129031</v>
+      </c>
+      <c r="M18">
+        <v>-0</v>
+      </c>
+      <c r="N18">
+        <v>-0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>-0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>2.35</v>
+      </c>
+      <c r="V18">
+        <v>0.07208588957055215</v>
+      </c>
+      <c r="W18">
+        <v>-0.03874066168623266</v>
+      </c>
+      <c r="X18">
+        <v>0.06602624933249028</v>
+      </c>
+      <c r="Y18">
+        <v>-0.1047669110187229</v>
+      </c>
+      <c r="Z18">
+        <v>0.04663582684568807</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.06575065347876337</v>
+      </c>
+      <c r="AC18">
+        <v>-0.06575065347876337</v>
+      </c>
+      <c r="AD18">
+        <v>0.717</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0.717</v>
+      </c>
+      <c r="AG18">
+        <v>-1.633</v>
+      </c>
+      <c r="AH18">
+        <v>0.02152054506708287</v>
+      </c>
+      <c r="AI18">
+        <v>0.007826058482596024</v>
+      </c>
+      <c r="AJ18">
+        <v>-0.05273355507475699</v>
+      </c>
+      <c r="AK18">
+        <v>-0.01829343430383008</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Innovax Holdings Limited (SEHK:2680)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.0303</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>-3.91</v>
+      </c>
+      <c r="L19">
+        <v>-0.2659863945578231</v>
+      </c>
+      <c r="M19">
+        <v>-0</v>
+      </c>
+      <c r="N19">
+        <v>-0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>10.7</v>
+      </c>
+      <c r="V19">
+        <v>1.154261057173678</v>
+      </c>
+      <c r="W19">
+        <v>-0.1406474820143885</v>
+      </c>
+      <c r="X19">
+        <v>0.06608728558780269</v>
+      </c>
+      <c r="Y19">
+        <v>-0.2067347676021912</v>
+      </c>
+      <c r="Z19">
+        <v>1.093912784640571</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0.06576519932985658</v>
+      </c>
+      <c r="AC19">
+        <v>-0.06576519932985658</v>
+      </c>
+      <c r="AD19">
+        <v>0.238</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0.238</v>
+      </c>
+      <c r="AG19">
+        <v>-10.462</v>
+      </c>
+      <c r="AH19">
+        <v>0.02503155237694573</v>
+      </c>
+      <c r="AI19">
+        <v>0.009778946503410303</v>
+      </c>
+      <c r="AJ19">
+        <v>8.776845637583891</v>
+      </c>
+      <c r="AK19">
+        <v>-0.7671212787798797</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Emperor Capital Group Limited (SEHK:717)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>-0.0646</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="L20">
+        <v>0.175</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>-0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>-0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>162.3</v>
+      </c>
+      <c r="V20">
+        <v>3.40251572327044</v>
+      </c>
+      <c r="W20">
+        <v>0.01973197781885397</v>
+      </c>
+      <c r="X20">
+        <v>0.06621778383114432</v>
+      </c>
+      <c r="Y20">
+        <v>-0.04648580601229035</v>
+      </c>
+      <c r="Z20">
+        <v>0.145933014354067</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0.0657959514930371</v>
+      </c>
+      <c r="AC20">
+        <v>-0.0657959514930371</v>
+      </c>
+      <c r="AD20">
+        <v>1.6</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>1.6</v>
+      </c>
+      <c r="AG20">
+        <v>-160.7</v>
+      </c>
+      <c r="AH20">
+        <v>0.03245436105476673</v>
+      </c>
+      <c r="AI20">
+        <v>0.003584229390681004</v>
+      </c>
+      <c r="AJ20">
+        <v>1.42212389380531</v>
+      </c>
+      <c r="AK20">
+        <v>-0.5656458993312214</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CL Group (Holdings) Limited (SEHK:8098)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>-0.0228</v>
+      </c>
+      <c r="E21">
+        <v>0.178</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>2.99</v>
+      </c>
+      <c r="L21">
+        <v>0.5761078998073218</v>
+      </c>
+      <c r="M21">
+        <v>-0</v>
+      </c>
+      <c r="N21">
+        <v>-0</v>
+      </c>
+      <c r="O21">
+        <v>-0</v>
+      </c>
+      <c r="P21">
+        <v>-0</v>
+      </c>
+      <c r="Q21">
+        <v>-0</v>
+      </c>
+      <c r="R21">
+        <v>-0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0.132</v>
+      </c>
+      <c r="V21">
+        <v>0.009924812030075189</v>
+      </c>
+      <c r="W21">
+        <v>0.1272340425531915</v>
+      </c>
+      <c r="X21">
+        <v>0.06655804778902505</v>
+      </c>
+      <c r="Y21">
+        <v>0.06067599476416646</v>
+      </c>
+      <c r="Z21">
+        <v>0.2196360558611934</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0.06587397599376812</v>
+      </c>
+      <c r="AC21">
+        <v>-0.06587397599376812</v>
+      </c>
+      <c r="AD21">
+        <v>0.719</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0.719</v>
+      </c>
+      <c r="AG21">
+        <v>0.587</v>
+      </c>
+      <c r="AH21">
+        <v>0.05128753834082317</v>
+      </c>
+      <c r="AI21">
+        <v>0.02631867930744171</v>
+      </c>
+      <c r="AJ21">
+        <v>0.04226974868582127</v>
+      </c>
+      <c r="AK21">
+        <v>0.02159120167727223</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>KOALA Financial Group Limited (SEHK:8226)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>-0.0451</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>-2.27</v>
+      </c>
+      <c r="L22">
+        <v>-0.6376404494382022</v>
+      </c>
+      <c r="M22">
+        <v>-0</v>
+      </c>
+      <c r="N22">
+        <v>-0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>-0</v>
+      </c>
+      <c r="Q22">
+        <v>-0</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>10.2</v>
+      </c>
+      <c r="V22">
+        <v>1.493411420204978</v>
+      </c>
+      <c r="W22">
+        <v>-0.04613821138211382</v>
+      </c>
+      <c r="X22">
+        <v>0.0665914815759546</v>
+      </c>
+      <c r="Y22">
+        <v>-0.1127296929580684</v>
+      </c>
+      <c r="Z22">
+        <v>0.1047952665508816</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0.06588147897622787</v>
+      </c>
+      <c r="AC22">
+        <v>-0.06588147897622787</v>
+      </c>
+      <c r="AD22">
+        <v>0.383</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0.383</v>
+      </c>
+      <c r="AG22">
+        <v>-9.817</v>
+      </c>
+      <c r="AH22">
+        <v>0.05309857202273673</v>
+      </c>
+      <c r="AI22">
+        <v>0.007867222644454943</v>
+      </c>
+      <c r="AJ22">
+        <v>3.28657515902243</v>
+      </c>
+      <c r="AK22">
+        <v>-0.2550996543928488</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Shenwan Hongyuan (H.K.) Limited (SEHK:218)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>-0.0687</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0.001522469125227108</v>
+      </c>
+      <c r="J23">
+        <v>0.001522469125227108</v>
+      </c>
+      <c r="K23">
+        <v>-20.3</v>
+      </c>
+      <c r="L23">
+        <v>-0.384469696969697</v>
+      </c>
+      <c r="M23">
+        <v>-0</v>
+      </c>
+      <c r="N23">
+        <v>-0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>-0</v>
+      </c>
+      <c r="Q23">
+        <v>-0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="V23">
+        <v>0.2347374847374847</v>
+      </c>
+      <c r="W23">
+        <v>-0.05464333781965007</v>
+      </c>
+      <c r="X23">
+        <v>0.06729123004245327</v>
+      </c>
+      <c r="Y23">
+        <v>-0.1219345678621033</v>
+      </c>
+      <c r="Z23">
+        <v>0.09666911405292453</v>
+      </c>
+      <c r="AA23">
+        <v>0.0001471757415086355</v>
+      </c>
+      <c r="AB23">
+        <v>0.06603219062191627</v>
+      </c>
+      <c r="AC23">
+        <v>-0.06588501488040764</v>
+      </c>
+      <c r="AD23">
+        <v>32.1</v>
+      </c>
+      <c r="AE23">
+        <v>0.09306815094004357</v>
+      </c>
+      <c r="AF23">
+        <v>32.19306815094004</v>
+      </c>
+      <c r="AG23">
+        <v>-44.70693184905996</v>
+      </c>
+      <c r="AH23">
+        <v>0.08947662142683203</v>
+      </c>
+      <c r="AI23">
+        <v>0.08368507471600349</v>
+      </c>
+      <c r="AJ23">
+        <v>-0.1580347377943039</v>
+      </c>
+      <c r="AK23">
+        <v>-0.1452499632874641</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>324.2424242424242</v>
+      </c>
+      <c r="AP23">
+        <v>-451.5851701925249</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Minerva Group Holding Limited (SEHK:397)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>-0.0132</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>-10.7</v>
+      </c>
+      <c r="L24">
+        <v>-1.289156626506024</v>
+      </c>
+      <c r="M24">
+        <v>4.91</v>
+      </c>
+      <c r="N24">
+        <v>0.1747330960854092</v>
+      </c>
+      <c r="O24">
+        <v>-0.4588785046728973</v>
+      </c>
+      <c r="P24">
+        <v>-0</v>
+      </c>
+      <c r="Q24">
+        <v>-0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>4.91</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>21.5</v>
+      </c>
+      <c r="V24">
+        <v>0.7651245551601423</v>
+      </c>
+      <c r="W24">
+        <v>-0.06065759637188208</v>
+      </c>
+      <c r="X24">
+        <v>0.06761502544473855</v>
+      </c>
+      <c r="Y24">
+        <v>-0.1282726218166206</v>
+      </c>
+      <c r="Z24">
+        <v>0.05413408294906831</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0.06609807904998083</v>
+      </c>
+      <c r="AC24">
+        <v>-0.06609807904998083</v>
+      </c>
+      <c r="AD24">
+        <v>3.31</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>3.31</v>
+      </c>
+      <c r="AG24">
+        <v>-18.19</v>
+      </c>
+      <c r="AH24">
+        <v>0.1053804520853232</v>
+      </c>
+      <c r="AI24">
+        <v>0.0200593903399794</v>
+      </c>
+      <c r="AJ24">
+        <v>-1.835519677093845</v>
+      </c>
+      <c r="AK24">
+        <v>-0.1267507490767194</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Victory Securities (Holdings) Company Limited (SEHK:8540)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>-0.04650000000000001</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>-3.43</v>
+      </c>
+      <c r="L25">
+        <v>-0.5384615384615384</v>
+      </c>
+      <c r="M25">
+        <v>0.314</v>
+      </c>
+      <c r="N25">
+        <v>0.003663943990665111</v>
+      </c>
+      <c r="O25">
+        <v>-0.09154518950437317</v>
+      </c>
+      <c r="P25">
+        <v>0.314</v>
+      </c>
+      <c r="Q25">
+        <v>0.003663943990665111</v>
+      </c>
+      <c r="R25">
+        <v>-0.09154518950437317</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>0</v>
+      </c>
+      <c r="U25">
+        <v>4.63</v>
+      </c>
+      <c r="V25">
+        <v>0.05402567094515753</v>
+      </c>
+      <c r="W25">
+        <v>-0.1465811965811966</v>
+      </c>
+      <c r="X25">
+        <v>0.06831266899678823</v>
+      </c>
+      <c r="Y25">
+        <v>-0.2148938655779848</v>
+      </c>
+      <c r="Z25">
+        <v>0.1837853433352568</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0.06623250260901217</v>
+      </c>
+      <c r="AC25">
+        <v>-0.06623250260901217</v>
+      </c>
+      <c r="AD25">
+        <v>13.7</v>
+      </c>
+      <c r="AE25">
+        <v>0</v>
+      </c>
+      <c r="AF25">
+        <v>13.7</v>
+      </c>
+      <c r="AG25">
+        <v>9.07</v>
+      </c>
+      <c r="AH25">
+        <v>0.1378269617706237</v>
+      </c>
+      <c r="AI25">
+        <v>0.3816155988857939</v>
+      </c>
+      <c r="AJ25">
+        <v>0.09570539200168829</v>
+      </c>
+      <c r="AK25">
+        <v>0.290054365206268</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>First Shanghai Investments Limited (SEHK:227)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>-0.0548</v>
+      </c>
+      <c r="E26">
+        <v>0.151</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>7.37</v>
+      </c>
+      <c r="L26">
+        <v>0.1738207547169811</v>
+      </c>
+      <c r="M26">
+        <v>-0</v>
+      </c>
+      <c r="N26">
+        <v>-0</v>
+      </c>
+      <c r="O26">
+        <v>-0</v>
+      </c>
+      <c r="P26">
+        <v>-0</v>
+      </c>
+      <c r="Q26">
+        <v>-0</v>
+      </c>
+      <c r="R26">
+        <v>-0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="U26">
+        <v>31.6</v>
+      </c>
+      <c r="V26">
+        <v>0.4647058823529412</v>
+      </c>
+      <c r="W26">
+        <v>0.02518796992481203</v>
+      </c>
+      <c r="X26">
+        <v>0.07122212995849334</v>
+      </c>
+      <c r="Y26">
+        <v>-0.04603416003368131</v>
+      </c>
+      <c r="Z26">
+        <v>0.1458548331613347</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0.06670179014536201</v>
+      </c>
+      <c r="AC26">
+        <v>-0.06670179014536201</v>
+      </c>
+      <c r="AD26">
+        <v>22.8</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>22.8</v>
+      </c>
+      <c r="AG26">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="AH26">
+        <v>0.2511013215859031</v>
+      </c>
+      <c r="AI26">
+        <v>0.06739580254212238</v>
+      </c>
+      <c r="AJ26">
+        <v>-0.1486486486486487</v>
+      </c>
+      <c r="AK26">
+        <v>-0.02869253342028041</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>-13.6</v>
+      </c>
+      <c r="AQ26">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LFG Investment Holdings Limited (SEHK:3938)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>-0.186</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>-4.18</v>
+      </c>
+      <c r="L27">
+        <v>-0.8799999999999999</v>
+      </c>
+      <c r="M27">
+        <v>2.59</v>
+      </c>
+      <c r="N27">
+        <v>0.2916666666666666</v>
+      </c>
+      <c r="O27">
+        <v>-0.6196172248803827</v>
+      </c>
+      <c r="P27">
+        <v>1.31</v>
+      </c>
+      <c r="Q27">
+        <v>0.1475225225225225</v>
+      </c>
+      <c r="R27">
+        <v>-0.3133971291866029</v>
+      </c>
+      <c r="S27">
+        <v>1.28</v>
+      </c>
+      <c r="T27">
+        <v>0.4942084942084942</v>
+      </c>
+      <c r="U27">
+        <v>4.34</v>
+      </c>
+      <c r="V27">
+        <v>0.4887387387387387</v>
+      </c>
+      <c r="W27">
+        <v>-0.2069306930693069</v>
+      </c>
+      <c r="X27">
+        <v>0.07184327401882684</v>
+      </c>
+      <c r="Y27">
+        <v>-0.2787739670881337</v>
+      </c>
+      <c r="Z27">
+        <v>0.2461139896373057</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0.06678644144790215</v>
+      </c>
+      <c r="AC27">
+        <v>-0.06678644144790215</v>
+      </c>
+      <c r="AD27">
+        <v>3.31</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>3.31</v>
+      </c>
+      <c r="AG27">
+        <v>-1.03</v>
+      </c>
+      <c r="AH27">
+        <v>0.2715340442986054</v>
+      </c>
+      <c r="AI27">
+        <v>0.1807755324959039</v>
+      </c>
+      <c r="AJ27">
+        <v>-0.1312101910828025</v>
+      </c>
+      <c r="AK27">
+        <v>-0.07372942018611309</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Value Convergence Holdings Limited (SEHK:821)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>0.119</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>-28.1</v>
+      </c>
+      <c r="L28">
+        <v>-3.101545253863135</v>
+      </c>
+      <c r="M28">
+        <v>-0</v>
+      </c>
+      <c r="N28">
+        <v>-0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>-0</v>
+      </c>
+      <c r="Q28">
+        <v>-0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>2.07</v>
+      </c>
+      <c r="V28">
+        <v>0.18</v>
+      </c>
+      <c r="W28">
+        <v>-0.3263646922183508</v>
+      </c>
+      <c r="X28">
+        <v>0.07265576419085472</v>
+      </c>
+      <c r="Y28">
+        <v>-0.3990204564092055</v>
+      </c>
+      <c r="Z28">
+        <v>0.1048125867653864</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0.06689043740207504</v>
+      </c>
+      <c r="AC28">
+        <v>-0.06689043740207504</v>
+      </c>
+      <c r="AD28">
+        <v>4.85</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>4.85</v>
+      </c>
+      <c r="AG28">
+        <v>2.78</v>
+      </c>
+      <c r="AH28">
+        <v>0.2966360856269113</v>
+      </c>
+      <c r="AI28">
+        <v>0.07803700724054706</v>
+      </c>
+      <c r="AJ28">
+        <v>0.1946778711484594</v>
+      </c>
+      <c r="AK28">
+        <v>0.04627163781624501</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sunwah Kingsway Capital Holdings Limited (SEHK:188)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>-0.353</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>-7.26</v>
+      </c>
+      <c r="L29">
+        <v>-3.704081632653061</v>
+      </c>
+      <c r="M29">
+        <v>1.75</v>
+      </c>
+      <c r="N29">
+        <v>0.07847533632286995</v>
+      </c>
+      <c r="O29">
+        <v>-0.2410468319559229</v>
+      </c>
+      <c r="P29">
+        <v>1.75</v>
+      </c>
+      <c r="Q29">
+        <v>0.07847533632286995</v>
+      </c>
+      <c r="R29">
+        <v>-0.2410468319559229</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>13.9</v>
+      </c>
+      <c r="V29">
+        <v>0.6233183856502242</v>
+      </c>
+      <c r="W29">
+        <v>-0.07069133398247322</v>
+      </c>
+      <c r="X29">
+        <v>0.07267451818232537</v>
+      </c>
+      <c r="Y29">
+        <v>-0.1433658521647986</v>
+      </c>
+      <c r="Z29">
+        <v>0.02129971745272766</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>0.06689275329018224</v>
+      </c>
+      <c r="AC29">
+        <v>-0.06689275329018224</v>
+      </c>
+      <c r="AD29">
+        <v>9.43</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>9.43</v>
+      </c>
+      <c r="AG29">
+        <v>-4.470000000000001</v>
+      </c>
+      <c r="AH29">
+        <v>0.2971950835171762</v>
+      </c>
+      <c r="AI29">
+        <v>0.09398983354928733</v>
+      </c>
+      <c r="AJ29">
+        <v>-0.2507010656197421</v>
+      </c>
+      <c r="AK29">
+        <v>-0.05171815341895176</v>
+      </c>
+      <c r="AL29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CASH Financial Services Group Limited (SEHK:510)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>-0.201</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>-11.4</v>
+      </c>
+      <c r="L30">
+        <v>-2.676056338028169</v>
+      </c>
+      <c r="M30">
+        <v>-0</v>
+      </c>
+      <c r="N30">
+        <v>-0</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>-0</v>
+      </c>
+      <c r="Q30">
+        <v>-0</v>
+      </c>
+      <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>16.7</v>
+      </c>
+      <c r="V30">
+        <v>0.7522522522522522</v>
+      </c>
+      <c r="W30">
+        <v>-0.2976501305483029</v>
+      </c>
+      <c r="X30">
+        <v>0.0758212765700607</v>
+      </c>
+      <c r="Y30">
+        <v>-0.3734714071183636</v>
+      </c>
+      <c r="Z30">
+        <v>0.1106493506493507</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0.06723534521438784</v>
+      </c>
+      <c r="AC30">
+        <v>-0.06723534521438784</v>
+      </c>
+      <c r="AD30">
+        <v>13.6</v>
+      </c>
+      <c r="AE30">
+        <v>0</v>
+      </c>
+      <c r="AF30">
+        <v>13.6</v>
+      </c>
+      <c r="AG30">
+        <v>-3.1</v>
+      </c>
+      <c r="AH30">
+        <v>0.3798882681564246</v>
+      </c>
+      <c r="AI30">
+        <v>0.3140877598152425</v>
+      </c>
+      <c r="AJ30">
+        <v>-0.1623036649214659</v>
+      </c>
+      <c r="AK30">
+        <v>-0.1165413533834586</v>
+      </c>
+      <c r="AL30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Gaoyu Finance Group Limited (SEHK:8221)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>-0.0808</v>
+      </c>
+      <c r="E31">
+        <v>-0.345</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>0.157</v>
+      </c>
+      <c r="L31">
+        <v>0.03340425531914894</v>
+      </c>
+      <c r="M31">
+        <v>-0</v>
+      </c>
+      <c r="N31">
+        <v>-0</v>
+      </c>
+      <c r="O31">
+        <v>-0</v>
+      </c>
+      <c r="P31">
+        <v>-0</v>
+      </c>
+      <c r="Q31">
+        <v>-0</v>
+      </c>
+      <c r="R31">
+        <v>-0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="U31">
+        <v>2.63</v>
+      </c>
+      <c r="V31">
+        <v>0.3902077151335311</v>
+      </c>
+      <c r="W31">
+        <v>0.008722222222222221</v>
+      </c>
+      <c r="X31">
+        <v>0.07599595599834241</v>
+      </c>
+      <c r="Y31">
+        <v>-0.0672737337761202</v>
+      </c>
+      <c r="Z31">
+        <v>0.2640449438202247</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0.06725201627644743</v>
+      </c>
+      <c r="AC31">
+        <v>-0.06725201627644743</v>
+      </c>
+      <c r="AD31">
+        <v>4.2</v>
+      </c>
+      <c r="AE31">
+        <v>0</v>
+      </c>
+      <c r="AF31">
+        <v>4.2</v>
+      </c>
+      <c r="AG31">
+        <v>1.57</v>
+      </c>
+      <c r="AH31">
+        <v>0.3839122486288848</v>
+      </c>
+      <c r="AI31">
+        <v>0.1802575107296137</v>
+      </c>
+      <c r="AJ31">
+        <v>0.1889290012033694</v>
+      </c>
+      <c r="AK31">
+        <v>0.07595549104983068</v>
+      </c>
+      <c r="AL31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bright Smart Securities &amp; Commodities Group Limited (SEHK:1428)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>0.0253</v>
+      </c>
+      <c r="E32">
+        <v>0.0663</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>73</v>
+      </c>
+      <c r="L32">
+        <v>0.5712050078247262</v>
+      </c>
+      <c r="M32">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="N32">
+        <v>0.1447209955841028</v>
+      </c>
+      <c r="O32">
+        <v>0.9876712328767122</v>
+      </c>
+      <c r="P32">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="Q32">
+        <v>0.1447209955841028</v>
+      </c>
+      <c r="R32">
+        <v>0.9876712328767122</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>0</v>
+      </c>
+      <c r="U32">
+        <v>81.7</v>
+      </c>
+      <c r="V32">
+        <v>0.1639903653151345</v>
+      </c>
+      <c r="W32">
+        <v>0.4808959156785244</v>
+      </c>
+      <c r="X32">
+        <v>0.07925986238620576</v>
+      </c>
+      <c r="Y32">
+        <v>0.4016360532923186</v>
+      </c>
+      <c r="Z32">
+        <v>0.1666232073011734</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0.06752802916384298</v>
+      </c>
+      <c r="AC32">
+        <v>-0.06752802916384298</v>
+      </c>
+      <c r="AD32">
+        <v>408.5</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>408.5</v>
+      </c>
+      <c r="AG32">
+        <v>326.8</v>
+      </c>
+      <c r="AH32">
+        <v>0.4505349068048968</v>
+      </c>
+      <c r="AI32">
+        <v>0.7262222222222222</v>
+      </c>
+      <c r="AJ32">
+        <v>0.3961212121212122</v>
+      </c>
+      <c r="AK32">
+        <v>0.6797004991680533</v>
+      </c>
+      <c r="AL32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Huatai Securities Co., Ltd. (SHSE:601688)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>0.147</v>
+      </c>
+      <c r="E33">
+        <v>0.175</v>
+      </c>
+      <c r="F33">
+        <v>0.108</v>
+      </c>
+      <c r="G33">
+        <v>0.05474912956452996</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>2236.3</v>
+      </c>
+      <c r="L33">
+        <v>0.3761458631187661</v>
+      </c>
+      <c r="M33">
+        <v>2141.59</v>
+      </c>
+      <c r="N33">
+        <v>0.1055131571816386</v>
+      </c>
+      <c r="O33">
+        <v>0.9576487948844072</v>
+      </c>
+      <c r="P33">
+        <v>2140.5</v>
+      </c>
+      <c r="Q33">
+        <v>0.1054594543994403</v>
+      </c>
+      <c r="R33">
+        <v>0.9571613826409694</v>
+      </c>
+      <c r="S33">
+        <v>1.090000000000146</v>
+      </c>
+      <c r="T33">
+        <v>0.0005089676361956049</v>
+      </c>
+      <c r="U33">
+        <v>7949</v>
+      </c>
+      <c r="V33">
+        <v>0.3916361611871763</v>
+      </c>
+      <c r="W33">
+        <v>0.09482276119402985</v>
+      </c>
+      <c r="X33">
+        <v>0.1033955889149962</v>
+      </c>
+      <c r="Y33">
+        <v>-0.008572827720966375</v>
+      </c>
+      <c r="Z33">
+        <v>0.08899483571588954</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0.06772743248424663</v>
+      </c>
+      <c r="AC33">
+        <v>-0.06772743248424663</v>
+      </c>
+      <c r="AD33">
+        <v>46181.2</v>
+      </c>
+      <c r="AE33">
+        <v>0</v>
+      </c>
+      <c r="AF33">
+        <v>46181.2</v>
+      </c>
+      <c r="AG33">
+        <v>38232.2</v>
+      </c>
+      <c r="AH33">
+        <v>0.6946829106126678</v>
+      </c>
+      <c r="AI33">
+        <v>0.6354595954244795</v>
+      </c>
+      <c r="AJ33">
+        <v>0.6532169467837367</v>
+      </c>
+      <c r="AK33">
+        <v>0.5906894894839219</v>
+      </c>
+      <c r="AL33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Guotai Junan International Holdings Limited (SEHK:1788)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D34">
         <v>-0.0352</v>
       </c>
-      <c r="E5">
+      <c r="E34">
         <v>-0.217</v>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
         <v>35.4</v>
       </c>
-      <c r="L5">
+      <c r="L34">
         <v>0.1367323290845887</v>
       </c>
-      <c r="M5">
+      <c r="M34">
         <v>25.6</v>
       </c>
-      <c r="N5">
+      <c r="N34">
         <v>0.01861276719499782</v>
       </c>
-      <c r="O5">
+      <c r="O34">
         <v>0.7231638418079097</v>
       </c>
-      <c r="P5">
+      <c r="P34">
         <v>25.6</v>
       </c>
-      <c r="Q5">
+      <c r="Q34">
         <v>0.01861276719499782</v>
       </c>
-      <c r="R5">
+      <c r="R34">
         <v>0.7231638418079097</v>
       </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
         <v>1546.2</v>
       </c>
-      <c r="V5">
+      <c r="V34">
         <v>1.124182056129126</v>
       </c>
-      <c r="W5">
+      <c r="W34">
         <v>0.01868961512063777</v>
       </c>
-      <c r="X5">
-        <v>0.1962976529610532</v>
-      </c>
-      <c r="Y5">
-        <v>-0.1776080378404154</v>
-      </c>
-      <c r="Z5">
+      <c r="X34">
+        <v>0.1962273690733725</v>
+      </c>
+      <c r="Y34">
+        <v>-0.1775377539527347</v>
+      </c>
+      <c r="Z34">
         <v>0.03001391143055877</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.06830817263333325</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06830817263333325</v>
-      </c>
-      <c r="AD5">
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0.06830025139148724</v>
+      </c>
+      <c r="AC34">
+        <v>-0.06830025139148724</v>
+      </c>
+      <c r="AD34">
         <v>10828.3</v>
       </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
+      <c r="AE34">
+        <v>0</v>
+      </c>
+      <c r="AF34">
         <v>10828.3</v>
       </c>
-      <c r="AG5">
+      <c r="AG34">
         <v>9282.099999999999</v>
       </c>
-      <c r="AH5">
+      <c r="AH34">
         <v>0.8872964756590215</v>
       </c>
-      <c r="AI5">
+      <c r="AI34">
         <v>0.8488922686150614</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ34">
         <v>0.8709453436547032</v>
       </c>
-      <c r="AK5">
+      <c r="AK34">
         <v>0.8280491721381673</v>
       </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hatcher Group Limited (SEHK:8365)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>0.0977</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>-9.92</v>
+      </c>
+      <c r="L35">
+        <v>-1.128555176336747</v>
+      </c>
+      <c r="M35">
+        <v>-0</v>
+      </c>
+      <c r="N35">
+        <v>-0</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>-0</v>
+      </c>
+      <c r="Q35">
+        <v>-0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>1.13</v>
+      </c>
+      <c r="V35">
+        <v>0.60427807486631</v>
+      </c>
+      <c r="W35">
+        <v>-0.4592592592592592</v>
+      </c>
+      <c r="X35">
+        <v>0.1031758242031292</v>
+      </c>
+      <c r="Y35">
+        <v>-0.5624350834623884</v>
+      </c>
+      <c r="Z35">
+        <v>0.7152156224572823</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0.06853437838405821</v>
+      </c>
+      <c r="AC35">
+        <v>-0.06853437838405821</v>
+      </c>
+      <c r="AD35">
+        <v>4.23</v>
+      </c>
+      <c r="AE35">
+        <v>0</v>
+      </c>
+      <c r="AF35">
+        <v>4.23</v>
+      </c>
+      <c r="AG35">
+        <v>3.100000000000001</v>
+      </c>
+      <c r="AH35">
+        <v>0.6934426229508197</v>
+      </c>
+      <c r="AI35">
+        <v>0.1530944625407166</v>
+      </c>
+      <c r="AJ35">
+        <v>0.6237424547283702</v>
+      </c>
+      <c r="AK35">
+        <v>0.1169811320754717</v>
+      </c>
+      <c r="AL35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Huarong International Financial Holdings Limited (SEHK:993)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>4.37</v>
+      </c>
+      <c r="L36">
+        <v>0.2061320754716981</v>
+      </c>
+      <c r="M36">
+        <v>57.3</v>
+      </c>
+      <c r="N36">
+        <v>0.3317892298784019</v>
+      </c>
+      <c r="O36">
+        <v>13.11212814645309</v>
+      </c>
+      <c r="P36">
+        <v>57.3</v>
+      </c>
+      <c r="Q36">
+        <v>0.3317892298784019</v>
+      </c>
+      <c r="R36">
+        <v>13.11212814645309</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.4655471916618414</v>
+      </c>
+      <c r="W36">
+        <v>-0.02604290822407628</v>
+      </c>
+      <c r="X36">
+        <v>0.1166725319464479</v>
+      </c>
+      <c r="Y36">
+        <v>-0.1427154401705242</v>
+      </c>
+      <c r="Z36">
+        <v>0.07099799062290689</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0.06878796712750658</v>
+      </c>
+      <c r="AC36">
+        <v>-0.06878796712750658</v>
+      </c>
+      <c r="AD36">
+        <v>531.2</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>531.2</v>
+      </c>
+      <c r="AG36">
+        <v>450.8000000000001</v>
+      </c>
+      <c r="AH36">
+        <v>0.7546526495240801</v>
+      </c>
+      <c r="AI36">
+        <v>1.703109971144598</v>
+      </c>
+      <c r="AJ36">
+        <v>0.7230152365677628</v>
+      </c>
+      <c r="AK36">
+        <v>1.947300215982721</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cinda International Holdings Limited (SEHK:111)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>-0.127</v>
+      </c>
+      <c r="E37">
+        <v>-0.8370000000000001</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0.001</v>
+      </c>
+      <c r="L37">
+        <v>6.024096385542168E-05</v>
+      </c>
+      <c r="M37">
+        <v>-0</v>
+      </c>
+      <c r="N37">
+        <v>-0</v>
+      </c>
+      <c r="O37">
+        <v>-0</v>
+      </c>
+      <c r="P37">
+        <v>-0</v>
+      </c>
+      <c r="Q37">
+        <v>-0</v>
+      </c>
+      <c r="R37">
+        <v>-0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>66.5</v>
+      </c>
+      <c r="V37">
+        <v>3.036529680365297</v>
+      </c>
+      <c r="W37">
+        <v>8.333333333333334E-06</v>
+      </c>
+      <c r="X37">
+        <v>0.131241613868825</v>
+      </c>
+      <c r="Y37">
+        <v>-0.1312332805354916</v>
+      </c>
+      <c r="Z37">
+        <v>0.1402027027027027</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0.06896820120932506</v>
+      </c>
+      <c r="AC37">
+        <v>-0.06896820120932506</v>
+      </c>
+      <c r="AD37">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="AG37">
+        <v>20.09999999999999</v>
+      </c>
+      <c r="AH37">
+        <v>0.7981566820276497</v>
+      </c>
+      <c r="AI37">
+        <v>0.4185596906718221</v>
+      </c>
+      <c r="AJ37">
+        <v>0.4785714285714285</v>
+      </c>
+      <c r="AK37">
+        <v>0.1431623931623932</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CMBC Capital Holdings Limited (SEHK:1141)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>-0.642</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>-31</v>
+      </c>
+      <c r="L38">
+        <v>-74.51923076923077</v>
+      </c>
+      <c r="M38">
+        <v>1.08</v>
+      </c>
+      <c r="N38">
+        <v>0.0152542372881356</v>
+      </c>
+      <c r="O38">
+        <v>-0.03483870967741936</v>
+      </c>
+      <c r="P38">
+        <v>-0</v>
+      </c>
+      <c r="Q38">
+        <v>-0</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>1.08</v>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+      <c r="U38">
+        <v>39.4</v>
+      </c>
+      <c r="V38">
+        <v>0.556497175141243</v>
+      </c>
+      <c r="W38">
+        <v>-0.1641079936474325</v>
+      </c>
+      <c r="X38">
+        <v>0.1315538298592739</v>
+      </c>
+      <c r="Y38">
+        <v>-0.2956618235067064</v>
+      </c>
+      <c r="Z38">
+        <v>0.0004974232043141897</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0.06897136673423529</v>
+      </c>
+      <c r="AC38">
+        <v>-0.06897136673423529</v>
+      </c>
+      <c r="AD38">
+        <v>281.3</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>281.3</v>
+      </c>
+      <c r="AG38">
+        <v>241.9</v>
+      </c>
+      <c r="AH38">
+        <v>0.7989207611474013</v>
+      </c>
+      <c r="AI38">
+        <v>0.6124537339429567</v>
+      </c>
+      <c r="AJ38">
+        <v>0.7735849056603774</v>
+      </c>
+      <c r="AK38">
+        <v>0.5760895451297928</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Well Link Securities Holdings Limited (SEHK:8350)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>-0.171</v>
+      </c>
+      <c r="E39">
+        <v>-0.176</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0.709</v>
+      </c>
+      <c r="L39">
+        <v>0.3042918454935622</v>
+      </c>
+      <c r="M39">
+        <v>-0</v>
+      </c>
+      <c r="N39">
+        <v>-0</v>
+      </c>
+      <c r="O39">
+        <v>-0</v>
+      </c>
+      <c r="P39">
+        <v>-0</v>
+      </c>
+      <c r="Q39">
+        <v>-0</v>
+      </c>
+      <c r="R39">
+        <v>-0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>1.6</v>
+      </c>
+      <c r="V39">
+        <v>0.06639004149377593</v>
+      </c>
+      <c r="W39">
+        <v>5.582677165354331</v>
+      </c>
+      <c r="X39">
+        <v>0.06927426845562278</v>
+      </c>
+      <c r="Y39">
+        <v>5.513402896898707</v>
+      </c>
+      <c r="Z39">
+        <v>0.4693795326349718</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0.06909106518142735</v>
+      </c>
+      <c r="AC39">
+        <v>-0.06909106518142735</v>
+      </c>
+      <c r="AD39">
+        <v>5.25</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>5.25</v>
+      </c>
+      <c r="AG39">
+        <v>3.65</v>
+      </c>
+      <c r="AH39">
+        <v>0.1788756388415673</v>
+      </c>
+      <c r="AI39">
+        <v>0.8624938393297191</v>
+      </c>
+      <c r="AJ39">
+        <v>0.1315315315315315</v>
+      </c>
+      <c r="AK39">
+        <v>0.8134611098729663</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Arta TechFin Corporation Limited (SEHK:279)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>-4.85</v>
+      </c>
+      <c r="L40">
+        <v>-1.197530864197531</v>
+      </c>
+      <c r="M40">
+        <v>-0</v>
+      </c>
+      <c r="N40">
+        <v>-0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>-0</v>
+      </c>
+      <c r="Q40">
+        <v>-0</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.1001127395715896</v>
+      </c>
+      <c r="W40">
+        <v>-1.46969696969697</v>
+      </c>
+      <c r="X40">
+        <v>0.06676649541317814</v>
+      </c>
+      <c r="Y40">
+        <v>-1.536463465110148</v>
+      </c>
+      <c r="Z40">
+        <v>0.8620689655172414</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0.06909161469068817</v>
+      </c>
+      <c r="AC40">
+        <v>-0.06909161469068817</v>
+      </c>
+      <c r="AD40">
+        <v>5.91</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>5.91</v>
+      </c>
+      <c r="AG40">
+        <v>-2.970000000000001</v>
+      </c>
+      <c r="AH40">
+        <v>0.06246696966494028</v>
+      </c>
+      <c r="AI40">
+        <v>0.4440270473328324</v>
+      </c>
+      <c r="AJ40">
+        <v>-0.03464364866441153</v>
+      </c>
+      <c r="AK40">
+        <v>-0.6704288939051921</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>South China Financial Holdings Limited (SEHK:619)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>-0.253</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>-18.2</v>
+      </c>
+      <c r="L41">
+        <v>-3.339449541284404</v>
+      </c>
+      <c r="M41">
+        <v>-0</v>
+      </c>
+      <c r="N41">
+        <v>-0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>-0</v>
+      </c>
+      <c r="Q41">
+        <v>-0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>5.92</v>
+      </c>
+      <c r="V41">
+        <v>0.7064439140811455</v>
+      </c>
+      <c r="W41">
+        <v>-0.4959128065395095</v>
+      </c>
+      <c r="X41">
+        <v>0.1889556388175422</v>
+      </c>
+      <c r="Y41">
+        <v>-0.6848684453570517</v>
+      </c>
+      <c r="Z41">
+        <v>0.06026761030631427</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0.06931322750968248</v>
+      </c>
+      <c r="AC41">
+        <v>-0.06931322750968248</v>
+      </c>
+      <c r="AD41">
+        <v>62.3</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>62.3</v>
+      </c>
+      <c r="AG41">
+        <v>56.38</v>
+      </c>
+      <c r="AH41">
+        <v>0.8814374646293153</v>
+      </c>
+      <c r="AI41">
+        <v>0.7372781065088757</v>
+      </c>
+      <c r="AJ41">
+        <v>0.8705991352686844</v>
+      </c>
+      <c r="AK41">
+        <v>0.7174853652328836</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>China Industrial Securities International Financial Group Limited (SEHK:6058)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>-0.0572</v>
+      </c>
+      <c r="E42">
+        <v>-0.18</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>10.4</v>
+      </c>
+      <c r="L42">
+        <v>0.161741835147745</v>
+      </c>
+      <c r="M42">
+        <v>2.02</v>
+      </c>
+      <c r="N42">
+        <v>0.01759581881533101</v>
+      </c>
+      <c r="O42">
+        <v>0.1942307692307692</v>
+      </c>
+      <c r="P42">
+        <v>2.02</v>
+      </c>
+      <c r="Q42">
+        <v>0.01759581881533101</v>
+      </c>
+      <c r="R42">
+        <v>0.1942307692307692</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
+        <v>191.5</v>
+      </c>
+      <c r="V42">
+        <v>1.668118466898955</v>
+      </c>
+      <c r="W42">
+        <v>0.01997694967345371</v>
+      </c>
+      <c r="X42">
+        <v>0.2146606000436103</v>
+      </c>
+      <c r="Y42">
+        <v>-0.1946836503701566</v>
+      </c>
+      <c r="Z42">
+        <v>0.05430743243243243</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0.06938948015223992</v>
+      </c>
+      <c r="AC42">
+        <v>-0.06938948015223992</v>
+      </c>
+      <c r="AD42">
+        <v>1031.4</v>
+      </c>
+      <c r="AE42">
+        <v>0</v>
+      </c>
+      <c r="AF42">
+        <v>1031.4</v>
+      </c>
+      <c r="AG42">
+        <v>839.9000000000001</v>
+      </c>
+      <c r="AH42">
+        <v>0.8998429593439191</v>
+      </c>
+      <c r="AI42">
+        <v>0.6552315608919382</v>
+      </c>
+      <c r="AJ42">
+        <v>0.8797528019273071</v>
+      </c>
+      <c r="AK42">
+        <v>0.6074786633878201</v>
+      </c>
+      <c r="AL42">
+        <v>0</v>
+      </c>
+      <c r="AM42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BOCOM International Holdings Company Limited (SEHK:3329)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="K43">
+        <v>-185.9</v>
+      </c>
+      <c r="M43">
+        <v>-0</v>
+      </c>
+      <c r="N43">
+        <v>-0</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>-0</v>
+      </c>
+      <c r="Q43">
+        <v>-0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>203.8</v>
+      </c>
+      <c r="V43">
+        <v>1.837691614066727</v>
+      </c>
+      <c r="W43">
+        <v>-0.6368619390202125</v>
+      </c>
+      <c r="X43">
+        <v>0.316044042016685</v>
+      </c>
+      <c r="Y43">
+        <v>-0.9529059810368974</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>5.472704923787835E-06</v>
+      </c>
+      <c r="AB43">
+        <v>0.06954705921325122</v>
+      </c>
+      <c r="AC43">
+        <v>-0.06954158650832742</v>
+      </c>
+      <c r="AD43">
+        <v>1674.3</v>
+      </c>
+      <c r="AE43">
+        <v>0.01504131732364341</v>
+      </c>
+      <c r="AF43">
+        <v>1674.315041317324</v>
+      </c>
+      <c r="AG43">
+        <v>1470.515041317324</v>
+      </c>
+      <c r="AH43">
+        <v>0.9378786323029376</v>
+      </c>
+      <c r="AI43">
+        <v>0.8922470667445039</v>
+      </c>
+      <c r="AJ43">
+        <v>0.9298729320876953</v>
+      </c>
+      <c r="AK43">
+        <v>0.8791186813022497</v>
+      </c>
+      <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
+        <v>0</v>
+      </c>
+      <c r="AN43">
+        <v>104643.75</v>
+      </c>
+      <c r="AP43">
+        <v>91907.19008233273</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Future World Holdings Limited (SEHK:572)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>-0.0337</v>
+      </c>
+      <c r="G44">
+        <v>-0.1241860465116279</v>
+      </c>
+      <c r="H44">
+        <v>-0.1241860465116279</v>
+      </c>
+      <c r="I44">
+        <v>0.4488372093023256</v>
+      </c>
+      <c r="J44">
+        <v>0.4488372093023256</v>
+      </c>
+      <c r="K44">
+        <v>-10.1</v>
+      </c>
+      <c r="L44">
+        <v>-2.348837209302326</v>
+      </c>
+      <c r="M44">
+        <v>-0</v>
+      </c>
+      <c r="N44">
+        <v>-0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>-0</v>
+      </c>
+      <c r="Q44">
+        <v>-0</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="U44">
+        <v>17.3</v>
+      </c>
+      <c r="V44">
+        <v>0.9105263157894737</v>
+      </c>
+      <c r="W44">
+        <v>-0.09412861136999068</v>
+      </c>
+      <c r="X44">
+        <v>0.113145104213602</v>
+      </c>
+      <c r="Y44">
+        <v>-0.2072737155835926</v>
+      </c>
+      <c r="Z44">
+        <v>0.02698428635975702</v>
+      </c>
+      <c r="AA44">
+        <v>0.01211155178472815</v>
+      </c>
+      <c r="AB44">
+        <v>0.08865915334247121</v>
+      </c>
+      <c r="AC44">
+        <v>-0.07654760155774305</v>
+      </c>
+      <c r="AD44">
+        <v>54.4</v>
+      </c>
+      <c r="AE44">
+        <v>0</v>
+      </c>
+      <c r="AF44">
+        <v>54.4</v>
+      </c>
+      <c r="AG44">
+        <v>37.09999999999999</v>
+      </c>
+      <c r="AH44">
+        <v>0.7411444141689373</v>
+      </c>
+      <c r="AI44">
+        <v>0.3432176656151419</v>
+      </c>
+      <c r="AJ44">
+        <v>0.6613190730837789</v>
+      </c>
+      <c r="AK44">
+        <v>0.2627478753541077</v>
+      </c>
+      <c r="AL44">
+        <v>2.41</v>
+      </c>
+      <c r="AM44">
+        <v>2.207</v>
+      </c>
+      <c r="AN44">
+        <v>27.47474747474747</v>
+      </c>
+      <c r="AO44">
+        <v>0.8008298755186721</v>
+      </c>
+      <c r="AP44">
+        <v>18.73737373737373</v>
+      </c>
+      <c r="AQ44">
+        <v>0.8744902582691435</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>mF International Limited (NasdaqCM:MFI)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G45">
+        <v>0.2288659793814433</v>
+      </c>
+      <c r="H45">
+        <v>0.225</v>
+      </c>
+      <c r="I45">
+        <v>-0.04158258013862813</v>
+      </c>
+      <c r="J45">
+        <v>-0.04158258013862813</v>
+      </c>
+      <c r="K45">
+        <v>-0.146</v>
+      </c>
+      <c r="L45">
+        <v>-0.03762886597938144</v>
+      </c>
+      <c r="M45">
+        <v>0.359</v>
+      </c>
+      <c r="N45">
+        <v>0.04033707865168539</v>
+      </c>
+      <c r="O45">
+        <v>-2.458904109589041</v>
+      </c>
+      <c r="P45">
+        <v>0.359</v>
+      </c>
+      <c r="Q45">
+        <v>0.04033707865168539</v>
+      </c>
+      <c r="R45">
+        <v>-2.458904109589041</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>3.91</v>
+      </c>
+      <c r="V45">
+        <v>0.4393258426966292</v>
+      </c>
+      <c r="W45">
+        <v>-0.1131782945736434</v>
+      </c>
+      <c r="X45">
+        <v>0.06832934327807211</v>
+      </c>
+      <c r="Y45">
+        <v>-0.1815076378517155</v>
+      </c>
+      <c r="Z45">
+        <v>1.671907857434684</v>
+      </c>
+      <c r="AA45">
+        <v>-0.06952224246617981</v>
+      </c>
+      <c r="AB45">
+        <v>0.06623559624120325</v>
+      </c>
+      <c r="AC45">
+        <v>-0.1357578387073831</v>
+      </c>
+      <c r="AD45">
+        <v>1.07</v>
+      </c>
+      <c r="AE45">
+        <v>0.3617020546893856</v>
+      </c>
+      <c r="AF45">
+        <v>1.431702054689386</v>
+      </c>
+      <c r="AG45">
+        <v>-2.478297945310614</v>
+      </c>
+      <c r="AH45">
+        <v>0.1385736877729222</v>
+      </c>
+      <c r="AI45">
+        <v>0.1809600569880907</v>
+      </c>
+      <c r="AJ45">
+        <v>-0.3859254017400046</v>
+      </c>
+      <c r="AK45">
+        <v>-0.6193109610462942</v>
+      </c>
+      <c r="AL45">
+        <v>0.032</v>
+      </c>
+      <c r="AM45">
+        <v>0.032</v>
+      </c>
+      <c r="AN45">
+        <v>-13.375</v>
+      </c>
+      <c r="AO45">
+        <v>-8.78125</v>
+      </c>
+      <c r="AP45">
+        <v>30.97872431638267</v>
+      </c>
+      <c r="AQ45">
+        <v>-8.78125</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Kingwisoft Technology Group Company Limited (SEHK:8295)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G46">
+        <v>0.07599337748344372</v>
+      </c>
+      <c r="H46">
+        <v>0.03598233995584989</v>
+      </c>
+      <c r="I46">
+        <v>-0.05149006622516557</v>
+      </c>
+      <c r="J46">
+        <v>-0.05149006622516557</v>
+      </c>
+      <c r="K46">
+        <v>-37.2</v>
+      </c>
+      <c r="L46">
+        <v>-0.2052980132450331</v>
+      </c>
+      <c r="M46">
+        <v>-0</v>
+      </c>
+      <c r="N46">
+        <v>-0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>-0</v>
+      </c>
+      <c r="Q46">
+        <v>-0</v>
+      </c>
+      <c r="R46">
+        <v>0</v>
+      </c>
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="U46">
+        <v>12.3</v>
+      </c>
+      <c r="V46">
+        <v>0.4767441860465116</v>
+      </c>
+      <c r="W46">
+        <v>-0.2645803698435278</v>
+      </c>
+      <c r="X46">
+        <v>0.09304495482879313</v>
+      </c>
+      <c r="Y46">
+        <v>-0.3576253246723209</v>
+      </c>
+      <c r="Z46">
+        <v>1.398148148148148</v>
+      </c>
+      <c r="AA46">
+        <v>-0.07199074074074074</v>
+      </c>
+      <c r="AB46">
+        <v>0.09986040681119682</v>
+      </c>
+      <c r="AC46">
+        <v>-0.1718511475519376</v>
+      </c>
+      <c r="AD46">
+        <v>42.6</v>
+      </c>
+      <c r="AE46">
+        <v>0</v>
+      </c>
+      <c r="AF46">
+        <v>42.6</v>
+      </c>
+      <c r="AG46">
+        <v>30.3</v>
+      </c>
+      <c r="AH46">
+        <v>0.6228070175438596</v>
+      </c>
+      <c r="AI46">
+        <v>0.2795275590551181</v>
+      </c>
+      <c r="AJ46">
+        <v>0.5401069518716578</v>
+      </c>
+      <c r="AK46">
+        <v>0.2162740899357602</v>
+      </c>
+      <c r="AL46">
+        <v>3.27</v>
+      </c>
+      <c r="AM46">
+        <v>3.114</v>
+      </c>
+      <c r="AN46">
+        <v>-62.00873362445414</v>
+      </c>
+      <c r="AO46">
+        <v>-2.853211009174312</v>
+      </c>
+      <c r="AP46">
+        <v>-44.10480349344978</v>
+      </c>
+      <c r="AQ46">
+        <v>-2.996146435452794</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Renze Harvest International Limited (SEHK:1282)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>-0.211</v>
+      </c>
+      <c r="G47">
+        <v>-0.8131212723658052</v>
+      </c>
+      <c r="H47">
+        <v>-0.8131212723658052</v>
+      </c>
+      <c r="I47">
+        <v>-1.000994035785288</v>
+      </c>
+      <c r="J47">
+        <v>-1.000994035785288</v>
+      </c>
+      <c r="K47">
+        <v>-80.2</v>
+      </c>
+      <c r="L47">
+        <v>-0.7972166998011929</v>
+      </c>
+      <c r="M47">
+        <v>-0</v>
+      </c>
+      <c r="N47">
+        <v>-0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>-0</v>
+      </c>
+      <c r="Q47">
+        <v>-0</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="U47">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="V47">
+        <v>1.997435897435898</v>
+      </c>
+      <c r="W47">
+        <v>-0.1180800942285041</v>
+      </c>
+      <c r="X47">
+        <v>0.1497313859430615</v>
+      </c>
+      <c r="Y47">
+        <v>-0.2678114801715656</v>
+      </c>
+      <c r="Z47">
+        <v>0.1292394655704008</v>
+      </c>
+      <c r="AA47">
+        <v>-0.1293679342240493</v>
+      </c>
+      <c r="AB47">
+        <v>0.06912181183828556</v>
+      </c>
+      <c r="AC47">
+        <v>-0.1984897460623349</v>
+      </c>
+      <c r="AD47">
+        <v>197.7</v>
+      </c>
+      <c r="AE47">
+        <v>0</v>
+      </c>
+      <c r="AF47">
+        <v>197.7</v>
+      </c>
+      <c r="AG47">
+        <v>119.8</v>
+      </c>
+      <c r="AH47">
+        <v>0.835234474017744</v>
+      </c>
+      <c r="AI47">
+        <v>0.1835143414090782</v>
+      </c>
+      <c r="AJ47">
+        <v>0.7544080604534005</v>
+      </c>
+      <c r="AK47">
+        <v>0.1198719231538923</v>
+      </c>
+      <c r="AL47">
+        <v>13.6</v>
+      </c>
+      <c r="AM47">
+        <v>1.4</v>
+      </c>
+      <c r="AN47">
+        <v>-1.969123505976095</v>
+      </c>
+      <c r="AO47">
+        <v>-7.404411764705883</v>
+      </c>
+      <c r="AP47">
+        <v>-1.193227091633466</v>
+      </c>
+      <c r="AQ47">
+        <v>-71.92857142857142</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Amasse Capital Holdings Limited (SEHK:8168)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>-0.058</v>
+      </c>
+      <c r="G48">
+        <v>-1.027522935779817</v>
+      </c>
+      <c r="H48">
+        <v>-1.027522935779817</v>
+      </c>
+      <c r="I48">
+        <v>-1.036697247706422</v>
+      </c>
+      <c r="J48">
+        <v>-1.036697247706422</v>
+      </c>
+      <c r="K48">
+        <v>-1.14</v>
+      </c>
+      <c r="L48">
+        <v>-1.045871559633027</v>
+      </c>
+      <c r="M48">
+        <v>-0</v>
+      </c>
+      <c r="N48">
+        <v>-0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>-0</v>
+      </c>
+      <c r="Q48">
+        <v>-0</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>2.27</v>
+      </c>
+      <c r="V48">
+        <v>0.1513333333333333</v>
+      </c>
+      <c r="W48">
+        <v>-0.2992125984251968</v>
+      </c>
+      <c r="X48">
+        <v>0.06579969831188187</v>
+      </c>
+      <c r="Y48">
+        <v>-0.3650122967370787</v>
+      </c>
+      <c r="Z48">
+        <v>0.2294736842105263</v>
+      </c>
+      <c r="AA48">
+        <v>-0.2378947368421052</v>
+      </c>
+      <c r="AB48">
+        <v>0.06569573448214083</v>
+      </c>
+      <c r="AC48">
+        <v>-0.3035904713242461</v>
+      </c>
+      <c r="AD48">
+        <v>0.125</v>
+      </c>
+      <c r="AE48">
+        <v>0</v>
+      </c>
+      <c r="AF48">
+        <v>0.125</v>
+      </c>
+      <c r="AG48">
+        <v>-2.145</v>
+      </c>
+      <c r="AH48">
+        <v>0.008264462809917356</v>
+      </c>
+      <c r="AI48">
+        <v>0.04317789291882556</v>
+      </c>
+      <c r="AJ48">
+        <v>-0.1668611435239206</v>
+      </c>
+      <c r="AK48">
+        <v>-3.432</v>
+      </c>
+      <c r="AL48">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AM48">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="AN48">
+        <v>-0.1116071428571428</v>
+      </c>
+      <c r="AO48">
+        <v>-125.5555555555556</v>
+      </c>
+      <c r="AP48">
+        <v>1.915178571428571</v>
+      </c>
+      <c r="AQ48">
+        <v>-125.5555555555556</v>
       </c>
     </row>
   </sheetData>
